--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7004A53A-686B-40D1-B67F-25EB4762B319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B33496-9F31-4AB5-B4E6-3461C9254E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="480" windowWidth="26460" windowHeight="14130" activeTab="1" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-27060" yWindow="810" windowWidth="26460" windowHeight="14130" activeTab="1" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Exposure C" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2758,4 +2759,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8320E2-F01C-4F60-9B3D-82EC74076ADF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B33496-9F31-4AB5-B4E6-3461C9254E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD34F51-3A1E-4FA5-93C5-538BA445BC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27060" yWindow="810" windowWidth="26460" windowHeight="14130" activeTab="1" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-28245" yWindow="660" windowWidth="26460" windowHeight="14130" activeTab="1" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Exposure C" sheetId="1" r:id="rId1"/>
@@ -2535,18 +2535,18 @@
         <v>45</v>
       </c>
       <c r="E14">
-        <v>0.26100000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="F14">
-        <v>-2.5</v>
+        <v>-2.5499999999999998</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>10.861776000000001</v>
+        <v>9.5716800000000006</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>-104.03999999999999</v>
+        <v>-106.12079999999999</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
@@ -2558,11 +2558,11 @@
       </c>
       <c r="L14">
         <f t="shared" si="4"/>
-        <v>18.352656</v>
+        <v>17.062560000000001</v>
       </c>
       <c r="M14">
         <f t="shared" si="5"/>
-        <v>-111.53088</v>
+        <v>-113.61167999999999</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15">

--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD34F51-3A1E-4FA5-93C5-538BA445BC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2DD4F0-07D7-4BE5-B945-01A560988780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28245" yWindow="660" windowWidth="26460" windowHeight="14130" activeTab="1" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-27540" yWindow="285" windowWidth="26460" windowHeight="14130" activeTab="2" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Exposure C" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="40x60 FLAT ASCE7-16" sheetId="2" r:id="rId2"/>
+    <sheet name="40x60 GABLE ASCE7-16" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="108">
   <si>
     <t>TDI Data Values</t>
   </si>
@@ -259,12 +260,6 @@
     <t>ROOF</t>
   </si>
   <si>
-    <t>END WALL</t>
-  </si>
-  <si>
-    <t>SIDE WALL</t>
-  </si>
-  <si>
     <t>(L-2a)H</t>
   </si>
   <si>
@@ -314,6 +309,60 @@
   </si>
   <si>
     <t>Net Max -</t>
+  </si>
+  <si>
+    <t>15'</t>
+  </si>
+  <si>
+    <t>30'</t>
+  </si>
+  <si>
+    <t>FLAT VERIFICATION - ASCE 7-16</t>
+  </si>
+  <si>
+    <t>GABLE VERIFICATION - ASCE7-16</t>
+  </si>
+  <si>
+    <t>slope</t>
+  </si>
+  <si>
+    <t>3e</t>
+  </si>
+  <si>
+    <t>3r</t>
+  </si>
+  <si>
+    <t>2n_B</t>
+  </si>
+  <si>
+    <t>2e</t>
+  </si>
+  <si>
+    <t>2r</t>
+  </si>
+  <si>
+    <t>a*a</t>
+  </si>
+  <si>
+    <t>(B/2-2a)*a</t>
+  </si>
+  <si>
+    <t>(L-2a)*a</t>
+  </si>
+  <si>
+    <t>(L * B/2) - 2*A3e-2*A3r-2*A2n-A2e-A2r</t>
+  </si>
+  <si>
+    <t>20'</t>
+  </si>
+  <si>
+    <t>(H+H+a*tan(slope))*a</t>
+  </si>
+  <si>
+    <t>"L" Dimension Wall</t>
+  </si>
+  <si>
+    <t>"B" Dimension Wall</t>
   </si>
 </sst>
 </file>
@@ -395,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -403,6 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2173,137 +2223,116 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4176C027-713D-42A8-A3F2-4BC71F239850}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.125" customWidth="1"/>
     <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
         <v>62</v>
       </c>
-      <c r="K1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L1" s="5">
+      <c r="K2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="5">
         <v>0.18</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>59</v>
       </c>
-      <c r="K2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15">
-      <c r="A3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="5">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3">
-        <f>MIN(H3,H4)</f>
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3">
-        <f>0.4*B6</f>
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" s="5">
         <v>0.85</v>
       </c>
-      <c r="M3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1">
-      <c r="A4" t="s">
-        <v>48</v>
+    </row>
+    <row r="4" spans="1:15" ht="15">
+      <c r="A4" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B4" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4">
+        <f>MIN(H4,H5)</f>
+        <v>4</v>
+      </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H4">
-        <f>0.1*MIN(B3,B4)</f>
-        <v>4</v>
+        <f>0.4*B7</f>
+        <v>6</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1">
+      <c r="K4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="M4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4">
+        <v>0.85</v>
+      </c>
+      <c r="O4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="5">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5">
-        <f>MAX(H5:H6)</f>
-        <v>3</v>
-      </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H5">
-        <f>0.04*MIN(B3,B4)</f>
-        <v>1.6</v>
+        <f>0.1*MIN(B4,B5)</f>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="L5" s="4">
-        <f>0.00256*B7*B7*L3*L2</f>
-        <v>41.616</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" thickBot="1">
+      <c r="N5">
+        <v>0.96</v>
+      </c>
+      <c r="O5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" thickBot="1">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B6" s="5">
         <v>15</v>
@@ -2311,242 +2340,238 @@
       <c r="C6" t="s">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <f>MAX(H6:H7)</f>
         <v>3</v>
       </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
       <c r="H6">
-        <v>3</v>
+        <f>0.04*MIN(B4,B5)</f>
+        <v>1.6</v>
       </c>
       <c r="I6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1">
+      <c r="K6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="4">
+        <f>0.00256*B8*B8*L4*L3</f>
+        <v>41.616</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickBot="1">
       <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="5">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" thickBot="1">
+      <c r="A8" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="5">
         <v>150</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="4">
-        <f>MAX(F5,F3)</f>
+      <c r="F8" s="4">
+        <f>MAX(F6,F4)</f>
         <v>4</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:15" ht="15">
+      <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" t="s">
         <v>82</v>
       </c>
-      <c r="H9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="L10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" t="s">
         <v>83</v>
       </c>
-      <c r="J9" t="s">
-        <v>84</v>
-      </c>
-      <c r="L9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="J11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="L11" t="s">
         <v>40</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>68</v>
       </c>
-      <c r="C11">
-        <f>($B$4-2.4*$B$6)*($B$3-2.4*$B$6)</f>
+      <c r="C12">
+        <f>($B$5-2.4*$B$7)*($B$4-2.4*$B$7)</f>
         <v>96</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>0.20399999999999999</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>-0.9</v>
       </c>
-      <c r="G11">
-        <f>$L$5*E11</f>
+      <c r="G12">
+        <f>$L$6*E12</f>
         <v>8.4896639999999994</v>
       </c>
-      <c r="H11">
-        <f>$L$5*F11</f>
+      <c r="H12">
+        <f>$L$6*F12</f>
         <v>-37.4544</v>
       </c>
-      <c r="I11">
-        <f>$L$5*$L$1</f>
+      <c r="I12">
+        <f>$L$6*$L$2</f>
         <v>7.4908799999999998</v>
       </c>
-      <c r="J11">
-        <f>-$L$5*$L$1</f>
+      <c r="J12">
+        <f>-$L$6*$L$2</f>
         <v>-7.4908799999999998</v>
       </c>
-      <c r="L11">
-        <f>G11+I11</f>
+      <c r="L12">
+        <f>G12+I12</f>
         <v>15.980543999999998</v>
       </c>
-      <c r="M11">
-        <f>H11+J11</f>
+      <c r="M12">
+        <f>H12+J12</f>
         <v>-44.945279999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12">
+    <row r="13" spans="1:15">
+      <c r="A13">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="C12">
-        <f>($B$4-1.2*$B$6)*($B$3-1.2*$B$6)-C11</f>
+      <c r="C13">
+        <f>($B$5-1.2*$B$7)*($B$4-1.2*$B$7)-C12</f>
         <v>828</v>
-      </c>
-      <c r="E12">
-        <v>0.2</v>
-      </c>
-      <c r="F12">
-        <v>-1</v>
-      </c>
-      <c r="G12">
-        <f t="shared" ref="G12:G14" si="0">$L$5*E12</f>
-        <v>8.3231999999999999</v>
-      </c>
-      <c r="H12">
-        <f t="shared" ref="H12:H14" si="1">$L$5*F12</f>
-        <v>-41.616</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ref="I12:I14" si="2">$L$5*$L$1</f>
-        <v>7.4908799999999998</v>
-      </c>
-      <c r="J12">
-        <f t="shared" ref="J12:J14" si="3">-$L$5*$L$1</f>
-        <v>-7.4908799999999998</v>
-      </c>
-      <c r="L12">
-        <f t="shared" ref="L12:L14" si="4">G12+I12</f>
-        <v>15.814080000000001</v>
-      </c>
-      <c r="M12">
-        <f t="shared" ref="M12:M14" si="5">H12+J12</f>
-        <v>-49.106879999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13">
-        <f>B3*B4-C11-C12-4*C14</f>
-        <v>1296</v>
       </c>
       <c r="E13">
         <v>0.2</v>
       </c>
       <c r="F13">
+        <v>-1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" ref="G13:G15" si="0">$L$6*E13</f>
+        <v>8.3231999999999999</v>
+      </c>
+      <c r="H13">
+        <f t="shared" ref="H13:H15" si="1">$L$6*F13</f>
+        <v>-41.616</v>
+      </c>
+      <c r="I13">
+        <f t="shared" ref="I13:I15" si="2">$L$6*$L$2</f>
+        <v>7.4908799999999998</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ref="J13:J15" si="3">-$L$6*$L$2</f>
+        <v>-7.4908799999999998</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L15" si="4">G13+I13</f>
+        <v>15.814080000000001</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M15" si="5">H13+J13</f>
+        <v>-49.106879999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14">
+        <f>B4*B5-C12-C13-4*C15</f>
+        <v>1296</v>
+      </c>
+      <c r="E14">
+        <v>0.2</v>
+      </c>
+      <c r="F14">
         <v>-1.4</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>8.3231999999999999</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <f t="shared" si="1"/>
         <v>-58.262399999999992</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="2"/>
-        <v>7.4908799999999998</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="3"/>
-        <v>-7.4908799999999998</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="4"/>
-        <v>15.814080000000001</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="5"/>
-        <v>-65.75327999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14">
-        <f>0.2*$B$6*$B$6</f>
-        <v>45</v>
-      </c>
-      <c r="E14">
-        <v>0.23</v>
-      </c>
-      <c r="F14">
-        <v>-2.5499999999999998</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>9.5716800000000006</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="1"/>
-        <v>-106.12079999999999</v>
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
@@ -2558,202 +2583,244 @@
       </c>
       <c r="L14">
         <f t="shared" si="4"/>
-        <v>17.062560000000001</v>
+        <v>15.814080000000001</v>
       </c>
       <c r="M14">
         <f t="shared" si="5"/>
+        <v>-65.75327999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <f>0.2*$B$7*$B$7</f>
+        <v>45</v>
+      </c>
+      <c r="E15">
+        <v>0.23</v>
+      </c>
+      <c r="F15">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>9.5716800000000006</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-106.12079999999999</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>7.4908799999999998</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>-7.4908799999999998</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>17.062560000000001</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="5"/>
         <v>-113.61167999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15">
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="1:15" ht="15">
+      <c r="B16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="1">
-        <f>C11+C12+C13+4*C14</f>
+      <c r="C16" s="1">
+        <f>C12+C13+C14+4*C15</f>
         <v>2400</v>
       </c>
-      <c r="D15" t="str">
-        <f>IF(C15=B3*B4,"OK","ERROR")</f>
+      <c r="D16" t="str">
+        <f>IF(C16=B4*B5,"OK","ERROR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:13" ht="15">
+      <c r="A19" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18">
-        <f>($B$3-2*$F$7)*($B$5)</f>
-        <v>480</v>
-      </c>
-      <c r="E18">
-        <v>0.72</v>
-      </c>
-      <c r="F18">
-        <v>-0.81</v>
-      </c>
-      <c r="G18">
-        <f t="shared" ref="G18:G19" si="6">$L$5*E18</f>
-        <v>29.963519999999999</v>
-      </c>
-      <c r="H18">
-        <f t="shared" ref="H18:H19" si="7">$L$5*F18</f>
-        <v>-33.708960000000005</v>
-      </c>
-      <c r="I18">
-        <f t="shared" ref="I18:I19" si="8">$L$5*$L$1</f>
+      <c r="C20">
+        <f>($B$5-2*$F$8)*($B$6)</f>
+        <v>780</v>
+      </c>
+      <c r="E20">
+        <v>0.71</v>
+      </c>
+      <c r="F20">
+        <v>-0.8</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ref="G20:G21" si="6">$L$6*E20</f>
+        <v>29.547359999999998</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H20:H21" si="7">$L$6*F20</f>
+        <v>-33.2928</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ref="I20:I21" si="8">$L$6*$L$2</f>
         <v>7.4908799999999998</v>
       </c>
-      <c r="J18">
-        <f t="shared" ref="J18:J19" si="9">-$L$5*$L$1</f>
+      <c r="J20">
+        <f t="shared" ref="J20:J21" si="9">-$L$6*$L$2</f>
         <v>-7.4908799999999998</v>
       </c>
-      <c r="L18">
-        <f t="shared" ref="L18" si="10">G18+I18</f>
-        <v>37.4544</v>
-      </c>
-      <c r="M18">
-        <f>H18+J18</f>
-        <v>-41.199840000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19">
+      <c r="L20">
+        <f t="shared" ref="L20:L21" si="10">G20+I20</f>
+        <v>37.038239999999995</v>
+      </c>
+      <c r="M20">
+        <f>H20+J20</f>
+        <v>-40.783679999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
         <v>5</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="C19">
-        <f>$F$7*B5</f>
-        <v>60</v>
-      </c>
-      <c r="E19">
+      <c r="C21">
+        <f>F8*B6</f>
+        <v>60</v>
+      </c>
+      <c r="E21">
         <v>0.83</v>
       </c>
-      <c r="F19">
-        <v>-1.18</v>
-      </c>
-      <c r="G19">
+      <c r="F21">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="6"/>
         <v>34.54128</v>
       </c>
-      <c r="H19">
+      <c r="H21">
         <f t="shared" si="7"/>
-        <v>-49.106879999999997</v>
-      </c>
-      <c r="I19">
+        <v>-47.858399999999996</v>
+      </c>
+      <c r="I21">
         <f t="shared" si="8"/>
         <v>7.4908799999999998</v>
       </c>
-      <c r="J19">
+      <c r="J21">
         <f t="shared" si="9"/>
         <v>-7.4908799999999998</v>
       </c>
-      <c r="L19">
-        <f t="shared" ref="L19" si="11">G19+I19</f>
+      <c r="L21">
+        <f t="shared" si="10"/>
         <v>42.032159999999998</v>
       </c>
-      <c r="M19">
-        <f>H19+J19</f>
-        <v>-56.597759999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15">
-      <c r="A21" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22">
+      <c r="M21">
+        <f>H21+J21</f>
+        <v>-55.349279999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15">
+      <c r="A23" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
         <v>4</v>
       </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22">
-        <f>($B$4-2*$F$7)*($B$5)</f>
-        <v>780</v>
-      </c>
-      <c r="E22">
-        <v>0.7</v>
-      </c>
-      <c r="F22">
-        <v>-0.8</v>
-      </c>
-      <c r="G22">
-        <f t="shared" ref="G22:G23" si="12">$L$5*E22</f>
-        <v>29.131199999999996</v>
-      </c>
-      <c r="H22">
-        <f t="shared" ref="H22:H23" si="13">$L$5*F22</f>
-        <v>-33.2928</v>
-      </c>
-      <c r="I22">
-        <f t="shared" ref="I22:I23" si="14">$L$5*$L$1</f>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24">
+        <f>($B$4-2*$F$8)*($B$6)</f>
+        <v>480</v>
+      </c>
+      <c r="E24">
+        <v>0.71</v>
+      </c>
+      <c r="F24">
+        <v>-0.81</v>
+      </c>
+      <c r="G24">
+        <f t="shared" ref="G24:G25" si="11">$L$6*E24</f>
+        <v>29.547359999999998</v>
+      </c>
+      <c r="H24">
+        <f t="shared" ref="H24:H25" si="12">$L$6*F24</f>
+        <v>-33.708960000000005</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ref="I24:I25" si="13">$L$6*$L$2</f>
         <v>7.4908799999999998</v>
       </c>
-      <c r="J22">
-        <f t="shared" ref="J22:J23" si="15">-$L$5*$L$1</f>
+      <c r="J24">
+        <f t="shared" ref="J24:J25" si="14">-$L$6*$L$2</f>
         <v>-7.4908799999999998</v>
       </c>
-      <c r="L22">
-        <f t="shared" ref="L22:L23" si="16">G22+I22</f>
-        <v>36.622079999999997</v>
-      </c>
-      <c r="M22">
-        <f>H22+J22</f>
-        <v>-40.783679999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23">
+      <c r="L24">
+        <f t="shared" ref="L24" si="15">G24+I24</f>
+        <v>37.038239999999995</v>
+      </c>
+      <c r="M24">
+        <f>H24+J24</f>
+        <v>-41.199840000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
         <v>5</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="C23">
-        <f>F7*B5</f>
-        <v>60</v>
-      </c>
-      <c r="E23">
+      <c r="C25">
+        <f>$F$8*B6</f>
+        <v>60</v>
+      </c>
+      <c r="E25">
         <v>0.83</v>
       </c>
-      <c r="F23">
-        <v>-1.18</v>
-      </c>
-      <c r="G23">
+      <c r="F25">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="11"/>
+        <v>34.54128</v>
+      </c>
+      <c r="H25">
         <f t="shared" si="12"/>
-        <v>34.54128</v>
-      </c>
-      <c r="H23">
+        <v>-47.858399999999996</v>
+      </c>
+      <c r="I25">
         <f t="shared" si="13"/>
-        <v>-49.106879999999997</v>
-      </c>
-      <c r="I23">
+        <v>7.4908799999999998</v>
+      </c>
+      <c r="J25">
         <f t="shared" si="14"/>
-        <v>7.4908799999999998</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="15"/>
         <v>-7.4908799999999998</v>
       </c>
-      <c r="L23">
-        <f t="shared" si="16"/>
+      <c r="L25">
+        <f t="shared" ref="L25" si="16">G25+I25</f>
         <v>42.032159999999998</v>
       </c>
-      <c r="M23">
-        <f>H23+J23</f>
-        <v>-56.597759999999994</v>
+      <c r="M25">
+        <f>H25+J25</f>
+        <v>-55.349279999999993</v>
       </c>
     </row>
   </sheetData>
@@ -2762,6 +2829,722 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1C204F-B815-41FF-8AD4-130B8F24A18C}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15">
+      <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="5">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4">
+        <f>MIN(H4,H5)</f>
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
+        <f>0.4*B7</f>
+        <v>8.1424555792624798</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N4">
+        <v>0.85</v>
+      </c>
+      <c r="O4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="5">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5">
+        <f>0.1*MIN(B4,B5)</f>
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.91</v>
+      </c>
+      <c r="O5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" thickBot="1">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="5">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <f>MAX(H6:H7)</f>
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6">
+        <f>0.04*MIN(B4,B5)</f>
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="4">
+        <f>0.00256*B9*B9*L4*L3</f>
+        <v>44.553600000000003</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>0.96</v>
+      </c>
+      <c r="O6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickBot="1">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="7">
+        <f>$B$6+TAN($B$8 * 6.28 / 360)*$B$4/2</f>
+        <v>20.356138948156197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" thickBot="1">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="5">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="4">
+        <f>MAX(F6,F4)</f>
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="5">
+        <v>150</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" ht="15">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <f>F8*F8</f>
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>0.48</v>
+      </c>
+      <c r="F13">
+        <v>-2.74</v>
+      </c>
+      <c r="G13">
+        <f>$L$6*E13</f>
+        <v>21.385728</v>
+      </c>
+      <c r="H13">
+        <f>$L$6*F13</f>
+        <v>-122.07686400000001</v>
+      </c>
+      <c r="I13">
+        <f>$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J13">
+        <f>-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L13">
+        <f>G13+I13</f>
+        <v>29.405376</v>
+      </c>
+      <c r="M13">
+        <f>H13+J13</f>
+        <v>-130.09651200000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <f>F8*F8</f>
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+      <c r="F14">
+        <v>-3.35</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ref="G14:G18" si="0">$L$6*E14</f>
+        <v>22.276800000000001</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:H18" si="1">$L$6*F14</f>
+        <v>-149.25456000000003</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ref="I14:I18" si="2">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J14">
+        <f t="shared" ref="J14:J18" si="3">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:L18" si="4">G14+I14</f>
+        <v>30.296448000000002</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14:M18" si="5">H14+J14</f>
+        <v>-157.27420800000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15">
+        <f>(B4/2-2*F8)*F8</f>
+        <v>48</v>
+      </c>
+      <c r="E15">
+        <v>0.38</v>
+      </c>
+      <c r="F15">
+        <v>-2.02</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>16.930368000000001</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-89.998272</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>24.950016000000002</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="5"/>
+        <v>-98.017920000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16">
+        <f>(B5-2*F8)*F8</f>
+        <v>208</v>
+      </c>
+      <c r="E16">
+        <v>0.3</v>
+      </c>
+      <c r="F16">
+        <v>-0.5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>-22.276800000000001</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="4"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="5"/>
+        <v>-30.296448000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17">
+        <f>(B5-2*$F$8)*$F$8</f>
+        <v>208</v>
+      </c>
+      <c r="E17">
+        <v>0.3</v>
+      </c>
+      <c r="F17">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>-49.008960000000009</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="4"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="5"/>
+        <v>-57.028608000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18">
+        <f>($B$5*$B$4/2)-2*C13-2*C14-2*C15-C16-C17</f>
+        <v>624</v>
+      </c>
+      <c r="E18">
+        <v>0.3</v>
+      </c>
+      <c r="F18">
+        <v>-0.5</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>-22.276800000000001</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="5"/>
+        <v>-30.296448000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15">
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1">
+        <f>C18+2*C13+2*C14+2*C15+C16+C17</f>
+        <v>1200</v>
+      </c>
+      <c r="D19" t="str">
+        <f>IF(C19=B4*B5/2,"OK","ERROR")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15">
+      <c r="A21" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22">
+        <f>F8*B6</f>
+        <v>60</v>
+      </c>
+      <c r="E22">
+        <v>0.83</v>
+      </c>
+      <c r="F22">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="G22">
+        <f>$L$6*E22</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="H22">
+        <f>$L$6*F22</f>
+        <v>-50.345568</v>
+      </c>
+      <c r="I22">
+        <f t="shared" ref="I22:I24" si="6">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J22">
+        <f t="shared" ref="J22:J24" si="7">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L22">
+        <f>G22+I22</f>
+        <v>44.999136000000007</v>
+      </c>
+      <c r="M22">
+        <f>H22+J22</f>
+        <v>-58.365216000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23">
+        <f>($B$5-2*$F$8)*($B$6)</f>
+        <v>780</v>
+      </c>
+      <c r="E23">
+        <v>0.71</v>
+      </c>
+      <c r="F23">
+        <v>-0.8</v>
+      </c>
+      <c r="G23">
+        <f>$L$6*E23</f>
+        <v>31.633056</v>
+      </c>
+      <c r="H23">
+        <f>$L$6*F23</f>
+        <v>-35.642880000000005</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="6"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="7"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L23">
+        <f>G23+I23</f>
+        <v>39.652704</v>
+      </c>
+      <c r="M23">
+        <f>H23+J23</f>
+        <v>-43.662528000000009</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15">
+      <c r="A25" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
+        <f>0.5*($B$6+$B$6+$F$8*TAN(RADIANS($B$8)))*$F$8</f>
+        <v>62.143593539448979</v>
+      </c>
+      <c r="E26">
+        <v>0.83</v>
+      </c>
+      <c r="F26">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="G26">
+        <f>$L$6*E26</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="H26">
+        <f>$L$6*F26</f>
+        <v>-50.345568</v>
+      </c>
+      <c r="I26">
+        <f t="shared" ref="I26:I28" si="8">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ref="J26:J28" si="9">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L26">
+        <f>G26+I26</f>
+        <v>44.999136000000007</v>
+      </c>
+      <c r="M26">
+        <f>H26+J26</f>
+        <v>-58.365216000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <f>($B$6*$B$4)+0.5*$B$4/2*TAN(RADIANS(B8))*$B$4  - 2*C26</f>
+        <v>582.8924898935511</v>
+      </c>
+      <c r="E27">
+        <v>0.7</v>
+      </c>
+      <c r="F27">
+        <v>-0.8</v>
+      </c>
+      <c r="G27">
+        <f>$L$6*E27</f>
+        <v>31.187519999999999</v>
+      </c>
+      <c r="H27">
+        <f>$L$6*F27</f>
+        <v>-35.642880000000005</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="8"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="9"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L27">
+        <f>G27+I27</f>
+        <v>39.207167999999996</v>
+      </c>
+      <c r="M27">
+        <f>H27+J27</f>
+        <v>-43.662528000000009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="B30">
+        <f>TAN($B$8*6.28/360)</f>
+        <v>0.2678069474078098</v>
+      </c>
+      <c r="C30">
+        <f>B30*F8</f>
+        <v>1.0712277896312392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8320E2-F01C-4F60-9B3D-82EC74076ADF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2DD4F0-07D7-4BE5-B945-01A560988780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E668DF37-2661-40C7-A2D7-57252180E9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27540" yWindow="285" windowWidth="26460" windowHeight="14130" activeTab="2" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-23985" yWindow="285" windowWidth="22905" windowHeight="14130" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Exposure C" sheetId="1" r:id="rId1"/>
-    <sheet name="40x60 FLAT ASCE7-16" sheetId="2" r:id="rId2"/>
-    <sheet name="40x60 GABLE ASCE7-16" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="ASCE7-16 ExpC" sheetId="1" r:id="rId1"/>
+    <sheet name="ASCE7-22 ExpC" sheetId="5" r:id="rId2"/>
+    <sheet name="40x60 FLAT ASCE7-16" sheetId="2" r:id="rId3"/>
+    <sheet name="40x60 GABLE ASCE7-16" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="117">
   <si>
     <t>TDI Data Values</t>
   </si>
@@ -92,6 +93,9 @@
     <t>RoofStyle</t>
   </si>
   <si>
+    <t>ASCE7-22</t>
+  </si>
+  <si>
     <t>a (ft)</t>
   </si>
   <si>
@@ -363,13 +367,37 @@
   </si>
   <si>
     <t>"B" Dimension Wall</t>
+  </si>
+  <si>
+    <t>"L" Walls</t>
+  </si>
+  <si>
+    <t>"B" Walls</t>
+  </si>
+  <si>
+    <t>Zone 2 areas may be slightly off</t>
+  </si>
+  <si>
+    <t>Zone 3r+</t>
+  </si>
+  <si>
+    <t>Zone 3r-</t>
+  </si>
+  <si>
+    <t>Zone 3e+</t>
+  </si>
+  <si>
+    <t>Zone 3e-</t>
+  </si>
+  <si>
+    <t>&lt;--- EXCEEDS 60 ft forChapter30 Figures</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,8 +419,15 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,6 +437,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -453,6 +494,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -787,66 +832,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F035135-BEB2-4F94-BA52-74AFC5FDF7DD}">
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:BL81"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="2" customFormat="1" ht="20.25">
+    <row r="1" spans="1:64" s="2" customFormat="1" ht="23.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:41" ht="15">
+      <c r="D1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+    </row>
+    <row r="2" spans="1:64" ht="15">
       <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41">
+        <v>27</v>
+      </c>
+      <c r="BI2" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64">
       <c r="A3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64">
       <c r="A4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64" ht="15">
       <c r="A5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" ht="15">
-      <c r="M7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="BF5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64" ht="15">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-    </row>
-    <row r="8" spans="1:41">
+      <c r="Z7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="BI7" s="10"/>
+      <c r="BJ7" s="10"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+    </row>
+    <row r="8" spans="1:64">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -854,7 +926,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -863,28 +935,31 @@
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="W8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="s">
         <v>36</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AE8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP8" t="s">
         <v>37</v>
       </c>
-      <c r="AM8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41">
+      <c r="BG8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -895,103 +970,133 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>114</v>
+      </c>
+      <c r="T9" t="s">
+        <v>115</v>
+      </c>
+      <c r="U9" t="s">
+        <v>112</v>
+      </c>
+      <c r="V9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" t="s">
+      <c r="BF9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BG9" t="s">
         <v>5</v>
       </c>
-      <c r="M9" t="s">
+      <c r="BH9" t="s">
         <v>6</v>
       </c>
-      <c r="N9" t="s">
+      <c r="BI9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O9" t="s">
+      <c r="BJ9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="P9" t="s">
+      <c r="BK9" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="BL9" t="s">
         <v>11</v>
       </c>
-      <c r="T9" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" t="s">
-        <v>6</v>
-      </c>
-      <c r="V9" t="s">
-        <v>28</v>
-      </c>
-      <c r="W9" t="s">
-        <v>29</v>
-      </c>
-      <c r="X9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41">
+    </row>
+    <row r="10" spans="1:64">
       <c r="A10">
         <v>40</v>
       </c>
@@ -1005,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>15</v>
@@ -1013,32 +1118,56 @@
       <c r="H10">
         <v>41.6</v>
       </c>
-      <c r="J10">
-        <v>16</v>
-      </c>
-      <c r="K10">
+      <c r="Y10">
+        <v>41.8</v>
+      </c>
+      <c r="Z10">
+        <v>-54.4</v>
+      </c>
+      <c r="AA10">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="AB10">
+        <v>-40.9</v>
+      </c>
+      <c r="AD10">
+        <v>41.8</v>
+      </c>
+      <c r="AE10">
+        <v>36.6</v>
+      </c>
+      <c r="AF10">
+        <v>41.8</v>
+      </c>
+      <c r="AG10">
+        <v>-54.4</v>
+      </c>
+      <c r="BE10">
+        <v>15.9</v>
+      </c>
+      <c r="BF10">
         <v>-44.9</v>
       </c>
-      <c r="L10">
+      <c r="BG10">
         <v>15.8</v>
       </c>
-      <c r="M10">
+      <c r="BH10">
         <v>-49</v>
       </c>
-      <c r="N10">
+      <c r="BI10" s="9">
         <v>15.8</v>
       </c>
-      <c r="O10">
+      <c r="BJ10" s="9">
         <v>-65.7</v>
       </c>
-      <c r="P10">
-        <v>18.3</v>
-      </c>
-      <c r="Q10">
-        <v>-135.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41">
+      <c r="BK10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>-113.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:64">
       <c r="A11">
         <v>40</v>
       </c>
@@ -1052,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11">
         <v>30</v>
@@ -1060,32 +1189,56 @@
       <c r="H11">
         <v>48.1</v>
       </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11">
-        <v>18.5</v>
-      </c>
-      <c r="M11">
-        <v>-84.5</v>
-      </c>
-      <c r="N11">
+      <c r="Y11">
+        <v>47.3</v>
+      </c>
+      <c r="Z11">
+        <v>-58</v>
+      </c>
+      <c r="AA11">
+        <v>42.3</v>
+      </c>
+      <c r="AB11">
+        <v>-47.1</v>
+      </c>
+      <c r="AD11">
+        <v>47.3</v>
+      </c>
+      <c r="AE11">
+        <v>-58</v>
+      </c>
+      <c r="AF11">
+        <v>42.3</v>
+      </c>
+      <c r="AG11">
+        <v>-47.1</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG11">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="BH11">
+        <v>-71.099999999999994</v>
+      </c>
+      <c r="BI11" s="9">
         <v>18.3</v>
       </c>
-      <c r="O11">
+      <c r="BJ11" s="9">
         <v>-76</v>
       </c>
-      <c r="P11">
+      <c r="BK11">
         <v>18.3</v>
       </c>
-      <c r="Q11">
-        <v>-132.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41">
+      <c r="BL11">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:64">
       <c r="A12">
         <v>40</v>
       </c>
@@ -1099,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>45</v>
@@ -1107,32 +1260,56 @@
       <c r="H12">
         <v>52.4</v>
       </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12">
+      <c r="Y12">
+        <v>50.6</v>
+      </c>
+      <c r="Z12">
+        <v>-59.4</v>
+      </c>
+      <c r="AA12">
+        <v>46.1</v>
+      </c>
+      <c r="AB12">
+        <v>-51.3</v>
+      </c>
+      <c r="AD12">
+        <v>50.6</v>
+      </c>
+      <c r="AE12">
+        <v>-59.4</v>
+      </c>
+      <c r="AF12">
+        <v>46.1</v>
+      </c>
+      <c r="AG12">
+        <v>-51.3</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI12" s="9">
         <v>19.899999999999999</v>
       </c>
-      <c r="O12">
+      <c r="BJ12" s="9">
         <v>-82.8</v>
       </c>
-      <c r="P12">
+      <c r="BK12">
         <v>19.899999999999999</v>
       </c>
-      <c r="Q12">
-        <v>-101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41">
+      <c r="BL12">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:64">
       <c r="A13">
         <v>40</v>
       </c>
@@ -1146,10 +1323,79 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41">
+        <v>23</v>
+      </c>
+      <c r="G13">
+        <v>20.36</v>
+      </c>
+      <c r="H13">
+        <v>44.3</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="K13">
+        <v>21.3</v>
+      </c>
+      <c r="L13">
+        <v>-30.1</v>
+      </c>
+      <c r="M13">
+        <v>21.3</v>
+      </c>
+      <c r="N13">
+        <v>-30.1</v>
+      </c>
+      <c r="O13">
+        <v>25</v>
+      </c>
+      <c r="P13">
+        <v>-98.3</v>
+      </c>
+      <c r="Q13">
+        <v>21.3</v>
+      </c>
+      <c r="R13">
+        <v>-56</v>
+      </c>
+      <c r="S13">
+        <v>29.3</v>
+      </c>
+      <c r="T13">
+        <v>-129.5</v>
+      </c>
+      <c r="U13">
+        <v>29.3</v>
+      </c>
+      <c r="V13">
+        <v>-152.9</v>
+      </c>
+      <c r="Y13">
+        <v>44.5</v>
+      </c>
+      <c r="Z13">
+        <v>-57.9</v>
+      </c>
+      <c r="AA13">
+        <v>39</v>
+      </c>
+      <c r="AB13">
+        <v>-43.4</v>
+      </c>
+      <c r="AD13">
+        <v>44.6</v>
+      </c>
+      <c r="AE13">
+        <v>-58.1</v>
+      </c>
+      <c r="AF13">
+        <v>39</v>
+      </c>
+      <c r="AG13">
+        <v>-43.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:64">
       <c r="A14">
         <v>40</v>
       </c>
@@ -1163,10 +1409,79 @@
         <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41">
+        <v>23</v>
+      </c>
+      <c r="G14">
+        <v>26.55</v>
+      </c>
+      <c r="H14">
+        <v>46.9</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>31.9</v>
+      </c>
+      <c r="L14">
+        <v>-45.9</v>
+      </c>
+      <c r="M14">
+        <v>31.9</v>
+      </c>
+      <c r="N14">
+        <v>-45.9</v>
+      </c>
+      <c r="O14">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="P14">
+        <v>-77.400000000000006</v>
+      </c>
+      <c r="Q14">
+        <v>31.9</v>
+      </c>
+      <c r="R14">
+        <v>-45.9</v>
+      </c>
+      <c r="S14">
+        <v>47.8</v>
+      </c>
+      <c r="T14">
+        <v>-117.2</v>
+      </c>
+      <c r="U14">
+        <v>47.8</v>
+      </c>
+      <c r="V14">
+        <v>-95.7</v>
+      </c>
+      <c r="Y14">
+        <v>47.1</v>
+      </c>
+      <c r="Z14">
+        <v>-61</v>
+      </c>
+      <c r="AA14">
+        <v>41.2</v>
+      </c>
+      <c r="AB14">
+        <v>-45.9</v>
+      </c>
+      <c r="AD14">
+        <v>47.2</v>
+      </c>
+      <c r="AE14">
+        <v>-61.4</v>
+      </c>
+      <c r="AF14">
+        <v>41.2</v>
+      </c>
+      <c r="AG14">
+        <v>-45.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:64">
       <c r="A15">
         <v>40</v>
       </c>
@@ -1180,10 +1495,79 @@
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41">
+        <v>23</v>
+      </c>
+      <c r="G15">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>49.7</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="L15">
+        <v>-48.7</v>
+      </c>
+      <c r="M15">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="N15">
+        <v>-48.7</v>
+      </c>
+      <c r="O15">
+        <v>39.4</v>
+      </c>
+      <c r="P15">
+        <v>-82</v>
+      </c>
+      <c r="Q15">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="R15">
+        <v>-48.7</v>
+      </c>
+      <c r="S15">
+        <v>50.7</v>
+      </c>
+      <c r="T15">
+        <v>-124.2</v>
+      </c>
+      <c r="U15">
+        <v>50.7</v>
+      </c>
+      <c r="V15">
+        <v>-101.4</v>
+      </c>
+      <c r="Y15">
+        <v>49.8</v>
+      </c>
+      <c r="Z15">
+        <v>-64.3</v>
+      </c>
+      <c r="AA15">
+        <v>43.7</v>
+      </c>
+      <c r="AB15">
+        <v>-48.7</v>
+      </c>
+      <c r="AD15">
+        <v>50</v>
+      </c>
+      <c r="AE15">
+        <v>-65.099999999999994</v>
+      </c>
+      <c r="AF15">
+        <v>43.7</v>
+      </c>
+      <c r="AG15">
+        <v>-48.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:64">
       <c r="A16">
         <v>40</v>
       </c>
@@ -1197,10 +1581,79 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G16">
+        <v>35.36</v>
+      </c>
+      <c r="H16">
+        <v>49.8</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>23.9</v>
+      </c>
+      <c r="L16">
+        <v>-33.9</v>
+      </c>
+      <c r="M16">
+        <v>23.9</v>
+      </c>
+      <c r="N16">
+        <v>-33.9</v>
+      </c>
+      <c r="O16">
+        <v>28.1</v>
+      </c>
+      <c r="P16">
+        <v>-110.4</v>
+      </c>
+      <c r="Q16">
+        <v>23.9</v>
+      </c>
+      <c r="R16">
+        <v>-62.9</v>
+      </c>
+      <c r="S16">
+        <v>33</v>
+      </c>
+      <c r="T16">
+        <v>-145.5</v>
+      </c>
+      <c r="U16">
+        <v>33</v>
+      </c>
+      <c r="V16">
+        <v>-171.8</v>
+      </c>
+      <c r="Y16">
+        <v>49</v>
+      </c>
+      <c r="Z16">
+        <v>-59.9</v>
+      </c>
+      <c r="AA16">
+        <v>43.8</v>
+      </c>
+      <c r="AB16">
+        <v>-48.8</v>
+      </c>
+      <c r="AD16">
+        <v>49</v>
+      </c>
+      <c r="AE16">
+        <v>-60</v>
+      </c>
+      <c r="AF16">
+        <v>43.8</v>
+      </c>
+      <c r="AG16">
+        <v>-48.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17">
         <v>40</v>
       </c>
@@ -1214,10 +1667,79 @@
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G17">
+        <v>41.55</v>
+      </c>
+      <c r="H17">
+        <v>51.5</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>35</v>
+      </c>
+      <c r="L17">
+        <v>-50.5</v>
+      </c>
+      <c r="M17">
+        <v>35</v>
+      </c>
+      <c r="N17">
+        <v>-50.5</v>
+      </c>
+      <c r="O17">
+        <v>40.9</v>
+      </c>
+      <c r="P17">
+        <v>-85</v>
+      </c>
+      <c r="Q17">
+        <v>35</v>
+      </c>
+      <c r="R17">
+        <v>-50.5</v>
+      </c>
+      <c r="S17">
+        <v>52.5</v>
+      </c>
+      <c r="T17">
+        <v>-128.80000000000001</v>
+      </c>
+      <c r="U17">
+        <v>52.5</v>
+      </c>
+      <c r="V17">
+        <v>-105.2</v>
+      </c>
+      <c r="Y17">
+        <v>50.6</v>
+      </c>
+      <c r="Z17">
+        <v>-61.8</v>
+      </c>
+      <c r="AA17">
+        <v>45.3</v>
+      </c>
+      <c r="AB17">
+        <v>-50.5</v>
+      </c>
+      <c r="AD17">
+        <v>50.7</v>
+      </c>
+      <c r="AE17">
+        <v>-62.1</v>
+      </c>
+      <c r="AF17">
+        <v>45.3</v>
+      </c>
+      <c r="AG17">
+        <v>-50.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18">
         <v>40</v>
       </c>
@@ -1231,10 +1753,79 @@
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>53.6</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>36.4</v>
+      </c>
+      <c r="L18">
+        <v>-52.5</v>
+      </c>
+      <c r="M18">
+        <v>36.4</v>
+      </c>
+      <c r="N18">
+        <v>-52.5</v>
+      </c>
+      <c r="O18">
+        <v>42.5</v>
+      </c>
+      <c r="P18">
+        <v>-88.4</v>
+      </c>
+      <c r="Q18">
+        <v>36.4</v>
+      </c>
+      <c r="R18">
+        <v>-52.5</v>
+      </c>
+      <c r="S18">
+        <v>54.6</v>
+      </c>
+      <c r="T18">
+        <v>-133.9</v>
+      </c>
+      <c r="U18">
+        <v>54.6</v>
+      </c>
+      <c r="V18">
+        <v>-109.4</v>
+      </c>
+      <c r="Y18">
+        <v>52.6</v>
+      </c>
+      <c r="Z18">
+        <v>-64.099999999999994</v>
+      </c>
+      <c r="AA18">
+        <v>47.1</v>
+      </c>
+      <c r="AB18">
+        <v>-52.5</v>
+      </c>
+      <c r="AD18">
+        <v>52.7</v>
+      </c>
+      <c r="AE18">
+        <v>-64.599999999999994</v>
+      </c>
+      <c r="AF18">
+        <v>47.1</v>
+      </c>
+      <c r="AG18">
+        <v>-52.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19">
         <v>40</v>
       </c>
@@ -1248,10 +1839,79 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G19">
+        <v>50.36</v>
+      </c>
+      <c r="H19">
+        <v>53.6</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>25.7</v>
+      </c>
+      <c r="L19">
+        <v>-36.5</v>
+      </c>
+      <c r="M19">
+        <v>25.7</v>
+      </c>
+      <c r="N19">
+        <v>-36.5</v>
+      </c>
+      <c r="O19">
+        <v>30.3</v>
+      </c>
+      <c r="P19">
+        <v>-119</v>
+      </c>
+      <c r="Q19">
+        <v>25.7</v>
+      </c>
+      <c r="R19">
+        <v>-67.8</v>
+      </c>
+      <c r="S19">
+        <v>35.5</v>
+      </c>
+      <c r="T19">
+        <v>-156.69999999999999</v>
+      </c>
+      <c r="U19">
+        <v>35.5</v>
+      </c>
+      <c r="V19">
+        <v>-185</v>
+      </c>
+      <c r="Y19">
+        <v>51.8</v>
+      </c>
+      <c r="Z19">
+        <v>-60.7</v>
+      </c>
+      <c r="AA19">
+        <v>47.2</v>
+      </c>
+      <c r="AB19">
+        <v>-52.6</v>
+      </c>
+      <c r="AD19">
+        <v>51.8</v>
+      </c>
+      <c r="AE19">
+        <v>-60.8</v>
+      </c>
+      <c r="AF19">
+        <v>47.2</v>
+      </c>
+      <c r="AG19">
+        <v>-52.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20">
         <v>40</v>
       </c>
@@ -1265,10 +1925,79 @@
         <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G20">
+        <v>56.55</v>
+      </c>
+      <c r="H20">
+        <v>55</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>37.4</v>
+      </c>
+      <c r="L20">
+        <v>-53.9</v>
+      </c>
+      <c r="M20">
+        <v>37.4</v>
+      </c>
+      <c r="N20">
+        <v>-53.9</v>
+      </c>
+      <c r="O20">
+        <v>43.6</v>
+      </c>
+      <c r="P20">
+        <v>-90.8</v>
+      </c>
+      <c r="Q20">
+        <v>37.4</v>
+      </c>
+      <c r="R20">
+        <v>-53.9</v>
+      </c>
+      <c r="S20">
+        <v>56.1</v>
+      </c>
+      <c r="T20">
+        <v>-137.4</v>
+      </c>
+      <c r="U20">
+        <v>56.1</v>
+      </c>
+      <c r="V20">
+        <v>-112.2</v>
+      </c>
+      <c r="Y20">
+        <v>53</v>
+      </c>
+      <c r="Z20">
+        <v>-62</v>
+      </c>
+      <c r="AA20">
+        <v>48.4</v>
+      </c>
+      <c r="AB20">
+        <v>-53.9</v>
+      </c>
+      <c r="AD20">
+        <v>53.1</v>
+      </c>
+      <c r="AE20">
+        <v>-62.3</v>
+      </c>
+      <c r="AF20">
+        <v>48.4</v>
+      </c>
+      <c r="AG20">
+        <v>-53.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21">
         <v>40</v>
       </c>
@@ -1282,10 +2011,16 @@
         <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>23</v>
+      </c>
+      <c r="G21">
+        <v>65</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22">
         <v>40</v>
       </c>
@@ -1293,49 +2028,61 @@
         <v>60</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
       <c r="G22">
-        <v>23</v>
-      </c>
-      <c r="H22">
-        <v>45.5</v>
+        <v>60</v>
+      </c>
+      <c r="H22" s="6">
+        <v>55.6</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
+      <c r="K22">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="L22">
+        <v>-54.5</v>
+      </c>
+      <c r="M22">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="N22">
+        <v>-54.5</v>
+      </c>
+      <c r="O22">
+        <v>44.1</v>
+      </c>
+      <c r="P22">
+        <v>-91.9</v>
+      </c>
+      <c r="Q22">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="R22">
+        <v>-54.5</v>
+      </c>
+      <c r="S22">
+        <v>56.8</v>
+      </c>
       <c r="T22">
-        <v>21.8</v>
+        <v>-139.1</v>
       </c>
       <c r="U22">
-        <v>-53.7</v>
-      </c>
-      <c r="X22">
-        <v>21.8</v>
-      </c>
-      <c r="Y22">
-        <v>-80.8</v>
-      </c>
-      <c r="Z22">
-        <v>21.8</v>
-      </c>
-      <c r="AA22">
-        <v>-75.900000000000006</v>
-      </c>
-      <c r="AB22">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="AC22">
-        <v>-98.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>56.8</v>
+      </c>
+      <c r="V22">
+        <v>-113.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23">
         <v>40</v>
       </c>
@@ -1346,46 +2093,13 @@
         <v>15</v>
       </c>
       <c r="D23">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="H23">
-        <v>48.9</v>
-      </c>
-      <c r="I23">
-        <v>4</v>
-      </c>
-      <c r="T23">
-        <v>23.4</v>
-      </c>
-      <c r="U23">
-        <v>-50.4</v>
-      </c>
-      <c r="X23">
-        <v>23.4</v>
-      </c>
-      <c r="Y23">
-        <v>-57.6</v>
-      </c>
-      <c r="Z23">
-        <v>23.4</v>
-      </c>
-      <c r="AA23">
-        <v>-47.9</v>
-      </c>
-      <c r="AB23">
-        <v>48.8</v>
-      </c>
-      <c r="AC23">
-        <v>-153.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24">
         <v>40</v>
       </c>
@@ -1396,13 +2110,13 @@
         <v>15</v>
       </c>
       <c r="D24">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25">
         <v>40</v>
       </c>
@@ -1410,49 +2124,16 @@
         <v>60</v>
       </c>
       <c r="C25">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25">
-        <v>38</v>
-      </c>
-      <c r="H25">
-        <v>50.6</v>
-      </c>
-      <c r="I25">
-        <v>4</v>
-      </c>
-      <c r="T25">
-        <v>24.3</v>
-      </c>
-      <c r="U25">
-        <v>-59.7</v>
-      </c>
-      <c r="X25">
-        <v>24.3</v>
-      </c>
-      <c r="Y25">
-        <v>-89.7</v>
-      </c>
-      <c r="Z25">
-        <v>24.3</v>
-      </c>
-      <c r="AA25">
-        <v>-79.900000000000006</v>
-      </c>
-      <c r="AB25">
-        <v>43.1</v>
-      </c>
-      <c r="AC25">
-        <v>-138.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26">
         <v>40</v>
       </c>
@@ -1463,13 +2144,13 @@
         <v>30</v>
       </c>
       <c r="D26">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27">
         <v>40</v>
       </c>
@@ -1480,13 +2161,13 @@
         <v>30</v>
       </c>
       <c r="D27">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28">
         <v>40</v>
       </c>
@@ -1494,49 +2175,16 @@
         <v>60</v>
       </c>
       <c r="C28">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28">
-        <v>53</v>
-      </c>
-      <c r="H28">
-        <v>54.2</v>
-      </c>
-      <c r="I28">
-        <v>4</v>
-      </c>
-      <c r="T28">
-        <v>26</v>
-      </c>
-      <c r="U28">
-        <v>-64</v>
-      </c>
-      <c r="X28">
-        <v>26</v>
-      </c>
-      <c r="Y28">
-        <v>-96.3</v>
-      </c>
-      <c r="Z28">
-        <v>26</v>
-      </c>
-      <c r="AA28">
-        <v>-110.3</v>
-      </c>
-      <c r="AB28">
-        <v>46.3</v>
-      </c>
-      <c r="AC28">
-        <v>-148.69999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29">
         <v>40</v>
       </c>
@@ -1547,13 +2195,13 @@
         <v>45</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30">
         <v>40</v>
       </c>
@@ -1564,64 +2212,208 @@
         <v>45</v>
       </c>
       <c r="D30">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>50</v>
-      </c>
-      <c r="B33">
-        <v>70</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
+      <c r="A31">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>60</v>
+      </c>
+      <c r="C31">
+        <v>45</v>
+      </c>
+      <c r="D31">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:64">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>50</v>
-      </c>
-      <c r="B34">
-        <v>70</v>
-      </c>
-      <c r="C34">
-        <v>15</v>
-      </c>
-      <c r="D34">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="M34" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:64">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" t="s">
+        <v>6</v>
+      </c>
+      <c r="M35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35" t="s">
+        <v>35</v>
+      </c>
+      <c r="O35" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" t="s">
+        <v>114</v>
+      </c>
+      <c r="T35" t="s">
+        <v>115</v>
+      </c>
+      <c r="U35" t="s">
+        <v>112</v>
+      </c>
+      <c r="V35" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS35" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU35" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE35" t="s">
+        <v>21</v>
+      </c>
+      <c r="BF35" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>50</v>
-      </c>
-      <c r="B35">
-        <v>70</v>
-      </c>
-      <c r="C35">
-        <v>15</v>
-      </c>
-      <c r="D35">
-        <v>30</v>
-      </c>
-      <c r="E35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="BG35" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH35" t="s">
+        <v>6</v>
+      </c>
+      <c r="BI35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ35" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK35" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:64">
       <c r="A36">
         <v>50</v>
       </c>
@@ -1632,13 +2424,67 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>41.6</v>
+      </c>
+      <c r="Y36">
+        <v>41.6</v>
+      </c>
+      <c r="Z36">
+        <v>-53.2</v>
+      </c>
+      <c r="AA36">
+        <v>36.6</v>
+      </c>
+      <c r="AB36">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AD36">
+        <v>41.6</v>
+      </c>
+      <c r="AE36">
+        <v>-53.2</v>
+      </c>
+      <c r="AF36">
+        <v>36.6</v>
+      </c>
+      <c r="AG36">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="BE36">
+        <v>15.8</v>
+      </c>
+      <c r="BF36">
+        <v>-25.3</v>
+      </c>
+      <c r="BG36">
+        <v>15.8</v>
+      </c>
+      <c r="BH36">
+        <v>-49</v>
+      </c>
+      <c r="BI36" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="BJ36" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="BK36">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BL36">
+        <v>-113.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:64">
       <c r="A37">
         <v>50</v>
       </c>
@@ -1649,13 +2495,67 @@
         <v>30</v>
       </c>
       <c r="D37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <v>30</v>
+      </c>
+      <c r="H37">
+        <v>48.1</v>
+      </c>
+      <c r="Y37">
+        <v>46.9</v>
+      </c>
+      <c r="Z37">
+        <v>-56.3</v>
+      </c>
+      <c r="AA37">
+        <v>42.3</v>
+      </c>
+      <c r="AB37">
+        <v>-47.1</v>
+      </c>
+      <c r="AD37">
+        <v>46.9</v>
+      </c>
+      <c r="AE37">
+        <v>-56.3</v>
+      </c>
+      <c r="AF37">
+        <v>42.3</v>
+      </c>
+      <c r="AG37">
+        <v>-47.1</v>
+      </c>
+      <c r="BE37" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF37" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG37">
+        <v>18.3</v>
+      </c>
+      <c r="BH37">
+        <v>-57.4</v>
+      </c>
+      <c r="BI37" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="BJ37" s="9">
+        <v>-76</v>
+      </c>
+      <c r="BK37">
+        <v>18.3</v>
+      </c>
+      <c r="BL37">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:64">
       <c r="A38">
         <v>50</v>
       </c>
@@ -1663,16 +2563,70 @@
         <v>70</v>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G38">
+        <v>45</v>
+      </c>
+      <c r="H38">
+        <v>52.4</v>
+      </c>
+      <c r="Y38">
+        <v>49.9</v>
+      </c>
+      <c r="Z38">
+        <v>-57.6</v>
+      </c>
+      <c r="AA38">
+        <v>46.1</v>
+      </c>
+      <c r="AB38">
+        <v>-51.3</v>
+      </c>
+      <c r="AD38">
+        <v>49.9</v>
+      </c>
+      <c r="AE38">
+        <v>-57.6</v>
+      </c>
+      <c r="AF38">
+        <v>46.1</v>
+      </c>
+      <c r="AG38">
+        <v>-51.3</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF38" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG38" t="s">
+        <v>42</v>
+      </c>
+      <c r="BH38" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI38" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BJ38" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="BK38">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BL38">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:64">
       <c r="A39">
         <v>50</v>
       </c>
@@ -1680,16 +2634,85 @@
         <v>70</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="G39">
+        <v>21.7</v>
+      </c>
+      <c r="H39">
+        <v>44.9</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>21.6</v>
+      </c>
+      <c r="L39">
+        <v>-30.5</v>
+      </c>
+      <c r="M39">
+        <v>21.6</v>
+      </c>
+      <c r="N39">
+        <v>-30.5</v>
+      </c>
+      <c r="O39">
+        <v>23.4</v>
+      </c>
+      <c r="P39">
+        <v>-88.9</v>
+      </c>
+      <c r="Q39">
+        <v>21.6</v>
+      </c>
+      <c r="R39">
+        <v>-53</v>
+      </c>
+      <c r="S39">
+        <v>27.8</v>
+      </c>
+      <c r="T39">
+        <v>-119.3</v>
+      </c>
+      <c r="U39">
+        <v>27.8</v>
+      </c>
+      <c r="V39">
+        <v>-139.80000000000001</v>
+      </c>
+      <c r="Y39">
+        <v>44.9</v>
+      </c>
+      <c r="Z39">
+        <v>57.2</v>
+      </c>
+      <c r="AA39">
+        <v>39.5</v>
+      </c>
+      <c r="AB39">
+        <v>-44</v>
+      </c>
+      <c r="AD39">
+        <v>44.9</v>
+      </c>
+      <c r="AE39">
+        <v>-57.2</v>
+      </c>
+      <c r="AF39">
+        <v>39.5</v>
+      </c>
+      <c r="AG39">
+        <v>-44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:64">
       <c r="A40">
         <v>50</v>
       </c>
@@ -1697,16 +2720,85 @@
         <v>70</v>
       </c>
       <c r="C40">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="G40">
+        <v>29.43</v>
+      </c>
+      <c r="H40">
+        <v>47.9</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="K40">
+        <v>32.6</v>
+      </c>
+      <c r="L40">
+        <v>-46.9</v>
+      </c>
+      <c r="M40">
+        <v>32.6</v>
+      </c>
+      <c r="N40">
+        <v>-46.9</v>
+      </c>
+      <c r="O40">
+        <v>35</v>
+      </c>
+      <c r="P40">
+        <v>-72.8</v>
+      </c>
+      <c r="Q40">
+        <v>32.6</v>
+      </c>
+      <c r="R40">
+        <v>-46.9</v>
+      </c>
+      <c r="S40">
+        <v>45.3</v>
+      </c>
+      <c r="T40">
+        <v>-110.8</v>
+      </c>
+      <c r="U40">
+        <v>45.3</v>
+      </c>
+      <c r="V40">
+        <v>-90.8</v>
+      </c>
+      <c r="Y40">
+        <v>47.8</v>
+      </c>
+      <c r="Z40">
+        <v>-60.6</v>
+      </c>
+      <c r="AA40">
+        <v>42.2</v>
+      </c>
+      <c r="AB40">
+        <v>-46.9</v>
+      </c>
+      <c r="AD40">
+        <v>47.9</v>
+      </c>
+      <c r="AE40">
+        <v>-61.3</v>
+      </c>
+      <c r="AF40">
+        <v>42.2</v>
+      </c>
+      <c r="AG40">
+        <v>-46.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:64">
       <c r="A41">
         <v>50</v>
       </c>
@@ -1714,16 +2806,85 @@
         <v>70</v>
       </c>
       <c r="C41">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="G41">
+        <v>40</v>
+      </c>
+      <c r="H41">
+        <v>51.1</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
+      </c>
+      <c r="K41">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="L41">
+        <v>-50.1</v>
+      </c>
+      <c r="M41">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="N41">
+        <v>-50.1</v>
+      </c>
+      <c r="O41">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="P41">
+        <v>-77.7</v>
+      </c>
+      <c r="Q41">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="R41">
+        <v>-50.1</v>
+      </c>
+      <c r="S41">
+        <v>48.4</v>
+      </c>
+      <c r="T41">
+        <v>-118.2</v>
+      </c>
+      <c r="U41">
+        <v>48.4</v>
+      </c>
+      <c r="V41">
+        <v>-96.9</v>
+      </c>
+      <c r="Y41">
+        <v>50.8</v>
+      </c>
+      <c r="Z41">
+        <v>-64.099999999999994</v>
+      </c>
+      <c r="AA41">
+        <v>45</v>
+      </c>
+      <c r="AB41">
+        <v>-50.1</v>
+      </c>
+      <c r="AD41">
+        <v>51.1</v>
+      </c>
+      <c r="AE41">
+        <v>-65.400000000000006</v>
+      </c>
+      <c r="AF41">
+        <v>45</v>
+      </c>
+      <c r="AG41">
+        <v>-50.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:64">
       <c r="A42">
         <v>50</v>
       </c>
@@ -1731,16 +2892,85 @@
         <v>70</v>
       </c>
       <c r="C42">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D42">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="G42">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="H42">
+        <v>50.2</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="K42">
+        <v>24.1</v>
+      </c>
+      <c r="L42">
+        <v>-34.1</v>
+      </c>
+      <c r="M42">
+        <v>24.1</v>
+      </c>
+      <c r="N42">
+        <v>-34.1</v>
+      </c>
+      <c r="O42">
+        <v>26.1</v>
+      </c>
+      <c r="P42">
+        <v>-99.3</v>
+      </c>
+      <c r="Q42">
+        <v>24.1</v>
+      </c>
+      <c r="R42">
+        <v>-59.2</v>
+      </c>
+      <c r="S42">
+        <v>31</v>
+      </c>
+      <c r="T42">
+        <v>-133.19999999999999</v>
+      </c>
+      <c r="U42">
+        <v>31</v>
+      </c>
+      <c r="V42">
+        <v>-156.1</v>
+      </c>
+      <c r="Y42">
+        <v>48.9</v>
+      </c>
+      <c r="Z42">
+        <v>-58.5</v>
+      </c>
+      <c r="AA42">
+        <v>44.2</v>
+      </c>
+      <c r="AB42">
+        <v>-49.2</v>
+      </c>
+      <c r="AD42">
+        <v>48.9</v>
+      </c>
+      <c r="AE42">
+        <v>-58.7</v>
+      </c>
+      <c r="AF42">
+        <v>44.2</v>
+      </c>
+      <c r="AG42">
+        <v>-49.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:64">
       <c r="A43">
         <v>50</v>
       </c>
@@ -1748,16 +2978,85 @@
         <v>70</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="G43">
+        <v>44.43</v>
+      </c>
+      <c r="H43">
+        <v>52.2</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="K43">
+        <v>35.5</v>
+      </c>
+      <c r="L43">
+        <v>-51.2</v>
+      </c>
+      <c r="M43">
+        <v>35.5</v>
+      </c>
+      <c r="N43">
+        <v>-51.2</v>
+      </c>
+      <c r="O43">
+        <v>38.1</v>
+      </c>
+      <c r="P43">
+        <v>-79.400000000000006</v>
+      </c>
+      <c r="Q43">
+        <v>35.5</v>
+      </c>
+      <c r="R43">
+        <v>-51.2</v>
+      </c>
+      <c r="S43">
+        <v>49.5</v>
+      </c>
+      <c r="T43">
+        <v>-120.8</v>
+      </c>
+      <c r="U43">
+        <v>49.5</v>
+      </c>
+      <c r="V43">
+        <v>-99.1</v>
+      </c>
+      <c r="Y43">
+        <v>50.8</v>
+      </c>
+      <c r="Z43">
+        <v>-60.7</v>
+      </c>
+      <c r="AA43">
+        <v>46</v>
+      </c>
+      <c r="AB43">
+        <v>-51.2</v>
+      </c>
+      <c r="AD43">
+        <v>50.9</v>
+      </c>
+      <c r="AE43">
+        <v>-61.1</v>
+      </c>
+      <c r="AF43">
+        <v>46</v>
+      </c>
+      <c r="AG43">
+        <v>-51.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:64">
       <c r="A44">
         <v>50</v>
       </c>
@@ -1765,16 +3064,85 @@
         <v>70</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="G44">
+        <v>55</v>
+      </c>
+      <c r="H44">
+        <v>54.6</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="K44">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="L44">
+        <v>-53.5</v>
+      </c>
+      <c r="M44">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="N44">
+        <v>-53.5</v>
+      </c>
+      <c r="O44">
+        <v>39.9</v>
+      </c>
+      <c r="P44">
+        <v>-83</v>
+      </c>
+      <c r="Q44">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="R44">
+        <v>-53.5</v>
+      </c>
+      <c r="S44">
+        <v>51.7</v>
+      </c>
+      <c r="T44">
+        <v>-126.4</v>
+      </c>
+      <c r="U44">
+        <v>51.7</v>
+      </c>
+      <c r="V44">
+        <v>-103.6</v>
+      </c>
+      <c r="Y44">
+        <v>53.1</v>
+      </c>
+      <c r="Z44">
+        <v>-63.1</v>
+      </c>
+      <c r="AA44">
+        <v>48.1</v>
+      </c>
+      <c r="AB44">
+        <v>-53.5</v>
+      </c>
+      <c r="AD44">
+        <v>53.3</v>
+      </c>
+      <c r="AE44">
+        <v>-63.9</v>
+      </c>
+      <c r="AF44">
+        <v>48.1</v>
+      </c>
+      <c r="AG44">
+        <v>-53.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:64">
       <c r="A45">
         <v>50</v>
       </c>
@@ -1782,16 +3150,85 @@
         <v>70</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D45">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="G45">
+        <v>51.7</v>
+      </c>
+      <c r="H45">
+        <v>53.9</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="K45">
+        <v>25.9</v>
+      </c>
+      <c r="L45">
+        <v>-36.700000000000003</v>
+      </c>
+      <c r="M45">
+        <v>25.9</v>
+      </c>
+      <c r="N45">
+        <v>-36.700000000000003</v>
+      </c>
+      <c r="O45">
+        <v>28</v>
+      </c>
+      <c r="P45">
+        <v>-106.8</v>
+      </c>
+      <c r="Q45">
+        <v>25.9</v>
+      </c>
+      <c r="R45">
+        <v>-63.6</v>
+      </c>
+      <c r="S45">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T45">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="U45">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="V45">
+        <v>-167.8</v>
+      </c>
+      <c r="Y45">
+        <v>51.4</v>
+      </c>
+      <c r="Z45">
+        <v>-59.2</v>
+      </c>
+      <c r="AA45">
+        <v>47.5</v>
+      </c>
+      <c r="AB45">
+        <v>-52.9</v>
+      </c>
+      <c r="AD45">
+        <v>51.4</v>
+      </c>
+      <c r="AE45">
+        <v>-59.3</v>
+      </c>
+      <c r="AF45">
+        <v>47.5</v>
+      </c>
+      <c r="AG45">
+        <v>-52.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:64">
       <c r="A46">
         <v>50</v>
       </c>
@@ -1799,16 +3236,85 @@
         <v>70</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="G46">
+        <v>59.43</v>
+      </c>
+      <c r="H46">
+        <v>55.5</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="K46">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="L46">
+        <v>-54.4</v>
+      </c>
+      <c r="M46">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="N46">
+        <v>-54.4</v>
+      </c>
+      <c r="O46">
+        <v>40.5</v>
+      </c>
+      <c r="P46">
+        <v>-84.4</v>
+      </c>
+      <c r="Q46">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="R46">
+        <v>-54.4</v>
+      </c>
+      <c r="S46">
+        <v>52.6</v>
+      </c>
+      <c r="T46">
+        <v>-128.5</v>
+      </c>
+      <c r="U46">
+        <v>52.6</v>
+      </c>
+      <c r="V46">
+        <v>-105.3</v>
+      </c>
+      <c r="Y46">
+        <v>52.8</v>
+      </c>
+      <c r="Z46">
+        <v>-60.9</v>
+      </c>
+      <c r="AA46">
+        <v>48.9</v>
+      </c>
+      <c r="AB46">
+        <v>-54.4</v>
+      </c>
+      <c r="AD46">
+        <v>52.9</v>
+      </c>
+      <c r="AE46">
+        <v>-61</v>
+      </c>
+      <c r="AF46">
+        <v>48.9</v>
+      </c>
+      <c r="AG46">
+        <v>-54.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:64">
       <c r="A47">
         <v>50</v>
       </c>
@@ -1816,16 +3322,22 @@
         <v>70</v>
       </c>
       <c r="C47">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="G47">
+        <v>70</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:64">
       <c r="A48">
         <v>50</v>
       </c>
@@ -1833,16 +3345,16 @@
         <v>70</v>
       </c>
       <c r="C48">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D48">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:64">
       <c r="A49">
         <v>50</v>
       </c>
@@ -1850,16 +3362,16 @@
         <v>70</v>
       </c>
       <c r="C49">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:64">
       <c r="A50">
         <v>50</v>
       </c>
@@ -1867,16 +3379,16 @@
         <v>70</v>
       </c>
       <c r="C50">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:64">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1884,135 +3396,279 @@
         <v>70</v>
       </c>
       <c r="C51">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:64">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>70</v>
+      </c>
+      <c r="C52">
+        <v>30</v>
+      </c>
+      <c r="D52">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:64">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>70</v>
+      </c>
+      <c r="C53">
+        <v>30</v>
+      </c>
+      <c r="D53">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:64">
       <c r="A54">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B54">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:64">
+      <c r="A55">
+        <v>50</v>
+      </c>
+      <c r="B55">
+        <v>70</v>
+      </c>
+      <c r="C55">
+        <v>45</v>
+      </c>
+      <c r="D55">
+        <v>30</v>
+      </c>
+      <c r="E55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:64">
+      <c r="A56">
+        <v>50</v>
+      </c>
+      <c r="B56">
+        <v>70</v>
+      </c>
+      <c r="C56">
+        <v>45</v>
+      </c>
+      <c r="D56">
+        <v>45</v>
+      </c>
+      <c r="E56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:64">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55">
-        <v>60</v>
-      </c>
-      <c r="B55">
-        <v>80</v>
-      </c>
-      <c r="C55">
-        <v>15</v>
-      </c>
-      <c r="D55">
-        <v>15</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="M59" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG59" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:64">
+      <c r="A60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" t="s">
+        <v>46</v>
+      </c>
+      <c r="H60" t="s">
+        <v>41</v>
+      </c>
+      <c r="I60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K60" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" t="s">
+        <v>6</v>
+      </c>
+      <c r="M60" t="s">
+        <v>34</v>
+      </c>
+      <c r="N60" t="s">
+        <v>35</v>
+      </c>
+      <c r="O60" t="s">
+        <v>29</v>
+      </c>
+      <c r="P60" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>31</v>
+      </c>
+      <c r="R60" t="s">
+        <v>32</v>
+      </c>
+      <c r="S60" t="s">
+        <v>114</v>
+      </c>
+      <c r="T60" t="s">
+        <v>115</v>
+      </c>
+      <c r="U60" t="s">
+        <v>112</v>
+      </c>
+      <c r="V60" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO60" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ60" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR60" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU60" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE60" t="s">
+        <v>21</v>
+      </c>
+      <c r="BF60" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56">
-        <v>60</v>
-      </c>
-      <c r="B56">
-        <v>80</v>
-      </c>
-      <c r="C56">
-        <v>15</v>
-      </c>
-      <c r="D56">
-        <v>30</v>
-      </c>
-      <c r="E56" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57">
-        <v>60</v>
-      </c>
-      <c r="B57">
-        <v>80</v>
-      </c>
-      <c r="C57">
-        <v>15</v>
-      </c>
-      <c r="D57">
-        <v>45</v>
-      </c>
-      <c r="E57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58">
-        <v>60</v>
-      </c>
-      <c r="B58">
-        <v>80</v>
-      </c>
-      <c r="C58">
-        <v>30</v>
-      </c>
-      <c r="D58">
-        <v>15</v>
-      </c>
-      <c r="E58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59">
-        <v>60</v>
-      </c>
-      <c r="B59">
-        <v>80</v>
-      </c>
-      <c r="C59">
-        <v>30</v>
-      </c>
-      <c r="D59">
-        <v>30</v>
-      </c>
-      <c r="E59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60">
-        <v>60</v>
-      </c>
-      <c r="B60">
-        <v>80</v>
-      </c>
-      <c r="C60">
-        <v>30</v>
-      </c>
-      <c r="D60">
-        <v>45</v>
-      </c>
-      <c r="E60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="BG60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH60" t="s">
+        <v>6</v>
+      </c>
+      <c r="BI60" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ60" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:64">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2020,16 +3676,70 @@
         <v>80</v>
       </c>
       <c r="C61">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G61">
+        <v>15</v>
+      </c>
+      <c r="H61">
+        <v>41.6</v>
+      </c>
+      <c r="Y61">
+        <v>41.3</v>
+      </c>
+      <c r="Z61">
+        <v>-52</v>
+      </c>
+      <c r="AA61">
+        <v>36.6</v>
+      </c>
+      <c r="AB61">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AD61">
+        <v>41.3</v>
+      </c>
+      <c r="AE61">
+        <v>-52</v>
+      </c>
+      <c r="AF61">
+        <v>36.6</v>
+      </c>
+      <c r="AG61">
+        <v>-52</v>
+      </c>
+      <c r="BE61">
+        <v>15.8</v>
+      </c>
+      <c r="BF61">
+        <v>-24.1</v>
+      </c>
+      <c r="BG61">
+        <v>15.8</v>
+      </c>
+      <c r="BH61">
+        <v>-49</v>
+      </c>
+      <c r="BI61" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="BJ61" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="BK61">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BL61">
+        <v>-113.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:64">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2037,16 +3747,70 @@
         <v>80</v>
       </c>
       <c r="C62">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D62">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G62">
+        <v>30</v>
+      </c>
+      <c r="H62">
+        <v>48.1</v>
+      </c>
+      <c r="Y62">
+        <v>46.5</v>
+      </c>
+      <c r="Z62">
+        <v>-54.5</v>
+      </c>
+      <c r="AA62">
+        <v>42.3</v>
+      </c>
+      <c r="AB62">
+        <v>-47.1</v>
+      </c>
+      <c r="AD62">
+        <v>46.5</v>
+      </c>
+      <c r="AE62">
+        <v>-54.5</v>
+      </c>
+      <c r="AF62">
+        <v>42.3</v>
+      </c>
+      <c r="AG62">
+        <v>-47.1</v>
+      </c>
+      <c r="BE62" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG62">
+        <v>18.3</v>
+      </c>
+      <c r="BH62">
+        <v>-56.7</v>
+      </c>
+      <c r="BI62" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="BJ62" s="9">
+        <v>-76</v>
+      </c>
+      <c r="BK62">
+        <v>18.3</v>
+      </c>
+      <c r="BL62">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:64">
       <c r="A63">
         <v>60</v>
       </c>
@@ -2057,13 +3821,67 @@
         <v>45</v>
       </c>
       <c r="D63">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <v>45</v>
+      </c>
+      <c r="H63">
+        <v>52.4</v>
+      </c>
+      <c r="Y63">
+        <v>49.3</v>
+      </c>
+      <c r="Z63">
+        <v>-56.5</v>
+      </c>
+      <c r="AA63">
+        <v>46.1</v>
+      </c>
+      <c r="AB63">
+        <v>-51.3</v>
+      </c>
+      <c r="AD63">
+        <v>49.3</v>
+      </c>
+      <c r="AE63">
+        <v>-56.5</v>
+      </c>
+      <c r="AF63">
+        <v>46.1</v>
+      </c>
+      <c r="AG63">
+        <v>-51.3</v>
+      </c>
+      <c r="BE63" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG63">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BH63">
+        <v>-73.8</v>
+      </c>
+      <c r="BI63" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BJ63" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="BK63">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BL63">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:64">
       <c r="A64">
         <v>60</v>
       </c>
@@ -2079,8 +3897,77 @@
       <c r="E64" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="G64">
+        <v>23.04</v>
+      </c>
+      <c r="H64">
+        <v>45.5</v>
+      </c>
+      <c r="I64">
+        <v>6</v>
+      </c>
+      <c r="K64">
+        <v>21.8</v>
+      </c>
+      <c r="L64">
+        <v>-30.9</v>
+      </c>
+      <c r="M64">
+        <v>21.8</v>
+      </c>
+      <c r="N64">
+        <v>-30.9</v>
+      </c>
+      <c r="O64">
+        <v>21.8</v>
+      </c>
+      <c r="P64">
+        <v>-79.2</v>
+      </c>
+      <c r="Q64">
+        <v>21.8</v>
+      </c>
+      <c r="R64">
+        <v>-53.7</v>
+      </c>
+      <c r="S64">
+        <v>27</v>
+      </c>
+      <c r="T64">
+        <v>-111.3</v>
+      </c>
+      <c r="U64">
+        <v>27</v>
+      </c>
+      <c r="V64">
+        <v>-129.69999999999999</v>
+      </c>
+      <c r="Y64">
+        <v>45.1</v>
+      </c>
+      <c r="Z64">
+        <v>-56.4</v>
+      </c>
+      <c r="AA64">
+        <v>40</v>
+      </c>
+      <c r="AB64">
+        <v>-44.6</v>
+      </c>
+      <c r="AD64">
+        <v>45.2</v>
+      </c>
+      <c r="AE64">
+        <v>-56.9</v>
+      </c>
+      <c r="AF64">
+        <v>40</v>
+      </c>
+      <c r="AG64">
+        <v>-44.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33">
       <c r="A65">
         <v>60</v>
       </c>
@@ -2096,8 +3983,77 @@
       <c r="E65" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="G65">
+        <v>32.32</v>
+      </c>
+      <c r="H65">
+        <v>48.9</v>
+      </c>
+      <c r="I65">
+        <v>6</v>
+      </c>
+      <c r="K65">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="L65">
+        <v>-47.9</v>
+      </c>
+      <c r="M65">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="N65">
+        <v>-47.9</v>
+      </c>
+      <c r="O65">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="P65">
+        <v>-68</v>
+      </c>
+      <c r="Q65">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="R65">
+        <v>-47.9</v>
+      </c>
+      <c r="S65">
+        <v>42.7</v>
+      </c>
+      <c r="T65">
+        <v>-105.8</v>
+      </c>
+      <c r="U65">
+        <v>42.7</v>
+      </c>
+      <c r="V65">
+        <v>-86.9</v>
+      </c>
+      <c r="Y65">
+        <v>48.4</v>
+      </c>
+      <c r="Z65">
+        <v>-60.1</v>
+      </c>
+      <c r="AA65">
+        <v>43</v>
+      </c>
+      <c r="AB65">
+        <v>-47.9</v>
+      </c>
+      <c r="AD65">
+        <v>48.6</v>
+      </c>
+      <c r="AE65">
+        <v>-61.1</v>
+      </c>
+      <c r="AF65">
+        <v>43</v>
+      </c>
+      <c r="AG65">
+        <v>-47.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33">
       <c r="A66">
         <v>60</v>
       </c>
@@ -2113,8 +4069,77 @@
       <c r="E66" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="G66">
+        <v>45</v>
+      </c>
+      <c r="H66">
+        <v>52.4</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
+      </c>
+      <c r="K66">
+        <v>35.6</v>
+      </c>
+      <c r="L66">
+        <v>-72.900000000000006</v>
+      </c>
+      <c r="M66">
+        <v>35.6</v>
+      </c>
+      <c r="N66">
+        <v>-51.3</v>
+      </c>
+      <c r="O66">
+        <v>35.6</v>
+      </c>
+      <c r="P66">
+        <v>-72.900000000000006</v>
+      </c>
+      <c r="Q66">
+        <v>35.6</v>
+      </c>
+      <c r="R66">
+        <v>-51.3</v>
+      </c>
+      <c r="S66">
+        <v>45.7</v>
+      </c>
+      <c r="T66">
+        <v>-113.5</v>
+      </c>
+      <c r="U66">
+        <v>45.7</v>
+      </c>
+      <c r="V66">
+        <v>-93.2</v>
+      </c>
+      <c r="Y66">
+        <v>51.7</v>
+      </c>
+      <c r="Z66">
+        <v>-63.9</v>
+      </c>
+      <c r="AA66">
+        <v>46.1</v>
+      </c>
+      <c r="AB66">
+        <v>-51.3</v>
+      </c>
+      <c r="AD66">
+        <v>52.1</v>
+      </c>
+      <c r="AE66">
+        <v>-65.5</v>
+      </c>
+      <c r="AF66">
+        <v>46.1</v>
+      </c>
+      <c r="AG66">
+        <v>-51.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33">
       <c r="A67">
         <v>60</v>
       </c>
@@ -2130,8 +4155,77 @@
       <c r="E67" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="G67">
+        <v>38.04</v>
+      </c>
+      <c r="H67">
+        <v>50.6</v>
+      </c>
+      <c r="I67">
+        <v>6</v>
+      </c>
+      <c r="K67">
+        <v>24.3</v>
+      </c>
+      <c r="L67">
+        <v>-34.4</v>
+      </c>
+      <c r="M67">
+        <v>24.3</v>
+      </c>
+      <c r="N67">
+        <v>-34.4</v>
+      </c>
+      <c r="O67">
+        <v>24.3</v>
+      </c>
+      <c r="P67">
+        <v>-88</v>
+      </c>
+      <c r="Q67">
+        <v>24.3</v>
+      </c>
+      <c r="R67">
+        <v>-59.7</v>
+      </c>
+      <c r="S67">
+        <v>30</v>
+      </c>
+      <c r="T67">
+        <v>-123.7</v>
+      </c>
+      <c r="U67">
+        <v>30</v>
+      </c>
+      <c r="V67">
+        <v>-144.19999999999999</v>
+      </c>
+      <c r="Y67">
+        <v>48.8</v>
+      </c>
+      <c r="Z67">
+        <v>-57</v>
+      </c>
+      <c r="AA67">
+        <v>44.5</v>
+      </c>
+      <c r="AB67">
+        <v>-49.5</v>
+      </c>
+      <c r="AD67">
+        <v>48.8</v>
+      </c>
+      <c r="AE67">
+        <v>-57.3</v>
+      </c>
+      <c r="AF67">
+        <v>44.5</v>
+      </c>
+      <c r="AG67">
+        <v>-49.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33">
       <c r="A68">
         <v>60</v>
       </c>
@@ -2147,8 +4241,77 @@
       <c r="E68" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="G68">
+        <v>47.32</v>
+      </c>
+      <c r="H68">
+        <v>52.9</v>
+      </c>
+      <c r="I68">
+        <v>6</v>
+      </c>
+      <c r="K68">
+        <v>36</v>
+      </c>
+      <c r="L68">
+        <v>-51.9</v>
+      </c>
+      <c r="M68">
+        <v>36</v>
+      </c>
+      <c r="N68">
+        <v>-51.9</v>
+      </c>
+      <c r="O68">
+        <v>36</v>
+      </c>
+      <c r="P68">
+        <v>-73.7</v>
+      </c>
+      <c r="Q68">
+        <v>36</v>
+      </c>
+      <c r="R68">
+        <v>-51.9</v>
+      </c>
+      <c r="S68">
+        <v>46.2</v>
+      </c>
+      <c r="T68">
+        <v>-114.7</v>
+      </c>
+      <c r="U68">
+        <v>46.2</v>
+      </c>
+      <c r="V68">
+        <v>-94.2</v>
+      </c>
+      <c r="Y68">
+        <v>51</v>
+      </c>
+      <c r="Z68">
+        <v>-59.4</v>
+      </c>
+      <c r="AA68">
+        <v>46.6</v>
+      </c>
+      <c r="AB68">
+        <v>-51.9</v>
+      </c>
+      <c r="AD68">
+        <v>51.1</v>
+      </c>
+      <c r="AE68">
+        <v>-60</v>
+      </c>
+      <c r="AF68">
+        <v>46.6</v>
+      </c>
+      <c r="AG68">
+        <v>-51.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33">
       <c r="A69">
         <v>60</v>
       </c>
@@ -2164,8 +4327,77 @@
       <c r="E69" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="G69">
+        <v>60</v>
+      </c>
+      <c r="H69">
+        <v>55.6</v>
+      </c>
+      <c r="I69">
+        <v>6</v>
+      </c>
+      <c r="K69">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="L69">
+        <v>-54.5</v>
+      </c>
+      <c r="M69">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="N69">
+        <v>-54.5</v>
+      </c>
+      <c r="O69">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="P69">
+        <v>-77.400000000000006</v>
+      </c>
+      <c r="Q69">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="R69">
+        <v>-54.5</v>
+      </c>
+      <c r="S69">
+        <v>48.6</v>
+      </c>
+      <c r="T69">
+        <v>-120.6</v>
+      </c>
+      <c r="U69">
+        <v>48.6</v>
+      </c>
+      <c r="V69">
+        <v>-99</v>
+      </c>
+      <c r="Y69">
+        <v>53.5</v>
+      </c>
+      <c r="Z69">
+        <v>-61.9</v>
+      </c>
+      <c r="AA69">
+        <v>49</v>
+      </c>
+      <c r="AB69">
+        <v>-54.5</v>
+      </c>
+      <c r="AD69">
+        <v>53.8</v>
+      </c>
+      <c r="AE69">
+        <v>-63.1</v>
+      </c>
+      <c r="AF69">
+        <v>49</v>
+      </c>
+      <c r="AG69">
+        <v>-54.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33">
       <c r="A70">
         <v>60</v>
       </c>
@@ -2181,8 +4413,77 @@
       <c r="E70" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="G70">
+        <v>53.04</v>
+      </c>
+      <c r="H70">
+        <v>54.2</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="K70">
+        <v>26</v>
+      </c>
+      <c r="L70">
+        <v>-36.9</v>
+      </c>
+      <c r="M70">
+        <v>26</v>
+      </c>
+      <c r="N70">
+        <v>-36.9</v>
+      </c>
+      <c r="O70">
+        <v>26</v>
+      </c>
+      <c r="P70">
+        <v>-94.3</v>
+      </c>
+      <c r="Q70">
+        <v>26</v>
+      </c>
+      <c r="R70">
+        <v>-64</v>
+      </c>
+      <c r="S70">
+        <v>32.1</v>
+      </c>
+      <c r="T70">
+        <v>-132.6</v>
+      </c>
+      <c r="U70">
+        <v>32.1</v>
+      </c>
+      <c r="V70">
+        <v>-154.6</v>
+      </c>
+      <c r="Y70">
+        <v>51</v>
+      </c>
+      <c r="Z70">
+        <v>-58.4</v>
+      </c>
+      <c r="AA70">
+        <v>47.7</v>
+      </c>
+      <c r="AB70">
+        <v>-53.1</v>
+      </c>
+      <c r="AD70">
+        <v>51</v>
+      </c>
+      <c r="AE70">
+        <v>-58.5</v>
+      </c>
+      <c r="AF70">
+        <v>47.7</v>
+      </c>
+      <c r="AG70">
+        <v>-53.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33">
       <c r="A71">
         <v>60</v>
       </c>
@@ -2198,8 +4499,14 @@
       <c r="E71" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="G71">
+        <v>62.32</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33">
       <c r="A72">
         <v>60</v>
       </c>
@@ -2207,13 +4514,235 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D72">
         <v>45</v>
       </c>
       <c r="E72" t="s">
         <v>23</v>
+      </c>
+      <c r="G72">
+        <v>57.32</v>
+      </c>
+      <c r="H72">
+        <v>55.1</v>
+      </c>
+      <c r="I72">
+        <v>6</v>
+      </c>
+      <c r="K72">
+        <v>37.5</v>
+      </c>
+      <c r="L72">
+        <v>-54</v>
+      </c>
+      <c r="M72">
+        <v>37.5</v>
+      </c>
+      <c r="N72">
+        <v>-54</v>
+      </c>
+      <c r="O72">
+        <v>37.5</v>
+      </c>
+      <c r="P72">
+        <v>-76.7</v>
+      </c>
+      <c r="Q72">
+        <v>37.5</v>
+      </c>
+      <c r="R72">
+        <v>-54</v>
+      </c>
+      <c r="S72">
+        <v>48.1</v>
+      </c>
+      <c r="T72">
+        <v>-119.4</v>
+      </c>
+      <c r="U72">
+        <v>48.1</v>
+      </c>
+      <c r="V72">
+        <v>-98.1</v>
+      </c>
+      <c r="Y72">
+        <v>52.2</v>
+      </c>
+      <c r="Z72">
+        <v>-60</v>
+      </c>
+      <c r="AA72">
+        <v>48.5</v>
+      </c>
+      <c r="AB72">
+        <v>-54</v>
+      </c>
+      <c r="AD72">
+        <v>52.3</v>
+      </c>
+      <c r="AE72">
+        <v>-60.2</v>
+      </c>
+      <c r="AF72">
+        <v>48.5</v>
+      </c>
+      <c r="AG72">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33">
+      <c r="A73">
+        <v>60</v>
+      </c>
+      <c r="B73">
+        <v>80</v>
+      </c>
+      <c r="C73">
+        <v>15</v>
+      </c>
+      <c r="D73">
+        <v>15</v>
+      </c>
+      <c r="E73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33">
+      <c r="A74">
+        <v>60</v>
+      </c>
+      <c r="B74">
+        <v>80</v>
+      </c>
+      <c r="C74">
+        <v>15</v>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33">
+      <c r="A75">
+        <v>60</v>
+      </c>
+      <c r="B75">
+        <v>80</v>
+      </c>
+      <c r="C75">
+        <v>15</v>
+      </c>
+      <c r="D75">
+        <v>45</v>
+      </c>
+      <c r="E75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33">
+      <c r="A76">
+        <v>60</v>
+      </c>
+      <c r="B76">
+        <v>80</v>
+      </c>
+      <c r="C76">
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33">
+      <c r="A77">
+        <v>60</v>
+      </c>
+      <c r="B77">
+        <v>80</v>
+      </c>
+      <c r="C77">
+        <v>30</v>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33">
+      <c r="A78">
+        <v>60</v>
+      </c>
+      <c r="B78">
+        <v>80</v>
+      </c>
+      <c r="C78">
+        <v>30</v>
+      </c>
+      <c r="D78">
+        <v>45</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33">
+      <c r="A79">
+        <v>60</v>
+      </c>
+      <c r="B79">
+        <v>80</v>
+      </c>
+      <c r="C79">
+        <v>45</v>
+      </c>
+      <c r="D79">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33">
+      <c r="A80">
+        <v>60</v>
+      </c>
+      <c r="B80">
+        <v>80</v>
+      </c>
+      <c r="C80">
+        <v>45</v>
+      </c>
+      <c r="D80">
+        <v>30</v>
+      </c>
+      <c r="E80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>60</v>
+      </c>
+      <c r="B81">
+        <v>80</v>
+      </c>
+      <c r="C81">
+        <v>45</v>
+      </c>
+      <c r="D81">
+        <v>45</v>
+      </c>
+      <c r="E81" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2222,6 +4751,1818 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17CC2DC-833F-4AB7-BB6A-AAF773AC0FA2}">
+  <dimension ref="A1:BF76"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" style="9"/>
+    <col min="52" max="52" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:58" s="2" customFormat="1" ht="23.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+    </row>
+    <row r="2" spans="1:58" ht="15">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC2" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58" ht="15">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AZ5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58" ht="15">
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="T7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="BC7" s="10"/>
+      <c r="BD7" s="10"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+    </row>
+    <row r="8" spans="1:58" ht="15">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>37</v>
+      </c>
+      <c r="BA8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:58">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U9" t="s">
+        <v>12</v>
+      </c>
+      <c r="V9" t="s">
+        <v>13</v>
+      </c>
+      <c r="X9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>6</v>
+      </c>
+      <c r="BC9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:58">
+      <c r="A10">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>41.6</v>
+      </c>
+      <c r="S10">
+        <v>41.8</v>
+      </c>
+      <c r="T10">
+        <v>-54.4</v>
+      </c>
+      <c r="U10">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="V10">
+        <v>-40.9</v>
+      </c>
+      <c r="X10">
+        <v>41.8</v>
+      </c>
+      <c r="Y10">
+        <v>-54.4</v>
+      </c>
+      <c r="Z10">
+        <v>36.6</v>
+      </c>
+      <c r="AA10">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AY10">
+        <v>15.9</v>
+      </c>
+      <c r="AZ10">
+        <v>-44.9</v>
+      </c>
+      <c r="BA10">
+        <v>15.8</v>
+      </c>
+      <c r="BB10">
+        <v>-49</v>
+      </c>
+      <c r="BC10" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="BD10" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="BE10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BF10">
+        <v>-112.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58">
+      <c r="A11">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>48.1</v>
+      </c>
+      <c r="S11">
+        <v>47.3</v>
+      </c>
+      <c r="T11">
+        <v>-58</v>
+      </c>
+      <c r="U11">
+        <v>42.3</v>
+      </c>
+      <c r="V11">
+        <v>-47.1</v>
+      </c>
+      <c r="X11">
+        <v>47.3</v>
+      </c>
+      <c r="Y11">
+        <v>-58</v>
+      </c>
+      <c r="Z11">
+        <v>42.3</v>
+      </c>
+      <c r="AA11">
+        <v>-47.1</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA11">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="BB11">
+        <v>-71.099999999999994</v>
+      </c>
+      <c r="BC11" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="BD11" s="9">
+        <v>-76</v>
+      </c>
+      <c r="BE11">
+        <v>18.3</v>
+      </c>
+      <c r="BF11">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58">
+      <c r="A12">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>45</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>52.4</v>
+      </c>
+      <c r="S12">
+        <v>50.6</v>
+      </c>
+      <c r="T12">
+        <v>-59.4</v>
+      </c>
+      <c r="U12">
+        <v>46.1</v>
+      </c>
+      <c r="V12">
+        <v>-51.3</v>
+      </c>
+      <c r="X12">
+        <v>50.6</v>
+      </c>
+      <c r="Y12">
+        <v>-59.4</v>
+      </c>
+      <c r="Z12">
+        <v>46.1</v>
+      </c>
+      <c r="AA12">
+        <v>-51.3</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>42</v>
+      </c>
+      <c r="BC12" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BD12" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="BE12">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
+      <c r="A13">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <v>60</v>
+      </c>
+      <c r="C13">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
+      <c r="A14">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58">
+      <c r="A15">
+        <v>40</v>
+      </c>
+      <c r="B15">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
+      <c r="A16">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>60</v>
+      </c>
+      <c r="C16">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>60</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>40</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>60</v>
+      </c>
+      <c r="C19">
+        <v>45</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>60</v>
+      </c>
+      <c r="C20">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>40</v>
+      </c>
+      <c r="B21">
+        <v>60</v>
+      </c>
+      <c r="C21">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>45</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>40</v>
+      </c>
+      <c r="B22">
+        <v>60</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>40</v>
+      </c>
+      <c r="B23">
+        <v>60</v>
+      </c>
+      <c r="C23">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>40</v>
+      </c>
+      <c r="B24">
+        <v>60</v>
+      </c>
+      <c r="C24">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>40</v>
+      </c>
+      <c r="B25">
+        <v>60</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26">
+        <v>60</v>
+      </c>
+      <c r="C26">
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>40</v>
+      </c>
+      <c r="B27">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>40</v>
+      </c>
+      <c r="B28">
+        <v>60</v>
+      </c>
+      <c r="C28">
+        <v>45</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>60</v>
+      </c>
+      <c r="C29">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>40</v>
+      </c>
+      <c r="B30">
+        <v>60</v>
+      </c>
+      <c r="C30">
+        <v>45</v>
+      </c>
+      <c r="D30">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58">
+      <c r="A33">
+        <v>50</v>
+      </c>
+      <c r="B33">
+        <v>70</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33">
+        <v>15</v>
+      </c>
+      <c r="H33">
+        <v>41.6</v>
+      </c>
+      <c r="S33">
+        <v>41.6</v>
+      </c>
+      <c r="T33">
+        <v>-53.2</v>
+      </c>
+      <c r="U33">
+        <v>36.6</v>
+      </c>
+      <c r="V33">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="X33">
+        <v>41.6</v>
+      </c>
+      <c r="Y33">
+        <v>-53.2</v>
+      </c>
+      <c r="Z33">
+        <v>36.6</v>
+      </c>
+      <c r="AA33">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AY33">
+        <v>15.8</v>
+      </c>
+      <c r="AZ33">
+        <v>-25.3</v>
+      </c>
+      <c r="BA33">
+        <v>15.8</v>
+      </c>
+      <c r="BB33">
+        <v>-49</v>
+      </c>
+      <c r="BC33" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="BD33" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="BE33">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BF33">
+        <v>-112.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:58">
+      <c r="A34">
+        <v>50</v>
+      </c>
+      <c r="B34">
+        <v>70</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>48.1</v>
+      </c>
+      <c r="S34">
+        <v>46.9</v>
+      </c>
+      <c r="T34">
+        <v>-56.3</v>
+      </c>
+      <c r="U34">
+        <v>42.3</v>
+      </c>
+      <c r="V34">
+        <v>-47.1</v>
+      </c>
+      <c r="X34">
+        <v>46.9</v>
+      </c>
+      <c r="Y34">
+        <v>-56.3</v>
+      </c>
+      <c r="Z34">
+        <v>42.3</v>
+      </c>
+      <c r="AA34">
+        <v>-47.1</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ34" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA34">
+        <v>18.3</v>
+      </c>
+      <c r="BB34">
+        <v>-57.4</v>
+      </c>
+      <c r="BC34" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="BD34" s="9">
+        <v>-76</v>
+      </c>
+      <c r="BE34">
+        <v>18.3</v>
+      </c>
+      <c r="BF34">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:58">
+      <c r="A35">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>70</v>
+      </c>
+      <c r="C35">
+        <v>45</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>45</v>
+      </c>
+      <c r="H35">
+        <v>52.4</v>
+      </c>
+      <c r="S35">
+        <v>49.9</v>
+      </c>
+      <c r="T35">
+        <v>-57.6</v>
+      </c>
+      <c r="U35">
+        <v>46.1</v>
+      </c>
+      <c r="V35">
+        <v>-51.3</v>
+      </c>
+      <c r="X35">
+        <v>49.9</v>
+      </c>
+      <c r="Y35">
+        <v>-57.6</v>
+      </c>
+      <c r="Z35">
+        <v>46.1</v>
+      </c>
+      <c r="AA35">
+        <v>-51.3</v>
+      </c>
+      <c r="AY35" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ35" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA35" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB35" t="s">
+        <v>42</v>
+      </c>
+      <c r="BC35" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BD35" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="BE35">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BF35">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:58">
+      <c r="A36">
+        <v>50</v>
+      </c>
+      <c r="B36">
+        <v>70</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:58">
+      <c r="A37">
+        <v>50</v>
+      </c>
+      <c r="B37">
+        <v>70</v>
+      </c>
+      <c r="C37">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:58">
+      <c r="A38">
+        <v>50</v>
+      </c>
+      <c r="B38">
+        <v>70</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:58">
+      <c r="A39">
+        <v>50</v>
+      </c>
+      <c r="B39">
+        <v>70</v>
+      </c>
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:58">
+      <c r="A40">
+        <v>50</v>
+      </c>
+      <c r="B40">
+        <v>70</v>
+      </c>
+      <c r="C40">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:58">
+      <c r="A41">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>70</v>
+      </c>
+      <c r="C41">
+        <v>30</v>
+      </c>
+      <c r="D41">
+        <v>45</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:58">
+      <c r="A42">
+        <v>50</v>
+      </c>
+      <c r="B42">
+        <v>70</v>
+      </c>
+      <c r="C42">
+        <v>45</v>
+      </c>
+      <c r="D42">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:58">
+      <c r="A43">
+        <v>50</v>
+      </c>
+      <c r="B43">
+        <v>70</v>
+      </c>
+      <c r="C43">
+        <v>45</v>
+      </c>
+      <c r="D43">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:58">
+      <c r="A44">
+        <v>50</v>
+      </c>
+      <c r="B44">
+        <v>70</v>
+      </c>
+      <c r="C44">
+        <v>45</v>
+      </c>
+      <c r="D44">
+        <v>45</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:58">
+      <c r="A45">
+        <v>50</v>
+      </c>
+      <c r="B45">
+        <v>70</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:58">
+      <c r="A46">
+        <v>50</v>
+      </c>
+      <c r="B46">
+        <v>70</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:58">
+      <c r="A47">
+        <v>50</v>
+      </c>
+      <c r="B47">
+        <v>70</v>
+      </c>
+      <c r="C47">
+        <v>15</v>
+      </c>
+      <c r="D47">
+        <v>45</v>
+      </c>
+      <c r="E47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:58">
+      <c r="A48">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>70</v>
+      </c>
+      <c r="C48">
+        <v>30</v>
+      </c>
+      <c r="D48">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:58">
+      <c r="A49">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>70</v>
+      </c>
+      <c r="C49">
+        <v>30</v>
+      </c>
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:58">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>70</v>
+      </c>
+      <c r="C50">
+        <v>30</v>
+      </c>
+      <c r="D50">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:58">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>70</v>
+      </c>
+      <c r="C51">
+        <v>45</v>
+      </c>
+      <c r="D51">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:58">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>70</v>
+      </c>
+      <c r="C52">
+        <v>45</v>
+      </c>
+      <c r="D52">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:58">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>70</v>
+      </c>
+      <c r="C53">
+        <v>45</v>
+      </c>
+      <c r="D53">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:58">
+      <c r="A56">
+        <v>60</v>
+      </c>
+      <c r="B56">
+        <v>80</v>
+      </c>
+      <c r="C56">
+        <v>15</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56">
+        <v>15</v>
+      </c>
+      <c r="H56">
+        <v>41.6</v>
+      </c>
+      <c r="S56">
+        <v>41.3</v>
+      </c>
+      <c r="T56">
+        <v>-52</v>
+      </c>
+      <c r="U56">
+        <v>36.6</v>
+      </c>
+      <c r="V56">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="X56">
+        <v>41.3</v>
+      </c>
+      <c r="Y56">
+        <v>-52</v>
+      </c>
+      <c r="Z56">
+        <v>36.6</v>
+      </c>
+      <c r="AA56">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AY56">
+        <v>15.8</v>
+      </c>
+      <c r="AZ56">
+        <v>-24.1</v>
+      </c>
+      <c r="BA56">
+        <v>15.8</v>
+      </c>
+      <c r="BB56">
+        <v>-49</v>
+      </c>
+      <c r="BC56" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="BD56" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="BE56">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="BF56">
+        <v>-112.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:58">
+      <c r="A57">
+        <v>60</v>
+      </c>
+      <c r="B57">
+        <v>80</v>
+      </c>
+      <c r="C57">
+        <v>30</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57">
+        <v>30</v>
+      </c>
+      <c r="H57">
+        <v>48.1</v>
+      </c>
+      <c r="S57">
+        <v>46.5</v>
+      </c>
+      <c r="T57">
+        <v>-54.5</v>
+      </c>
+      <c r="U57">
+        <v>42.3</v>
+      </c>
+      <c r="V57">
+        <v>-47.1</v>
+      </c>
+      <c r="X57">
+        <v>46.5</v>
+      </c>
+      <c r="Y57">
+        <v>-54.5</v>
+      </c>
+      <c r="Z57">
+        <v>42.3</v>
+      </c>
+      <c r="AA57">
+        <v>-47.1</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA57">
+        <v>18.3</v>
+      </c>
+      <c r="BB57">
+        <v>-56.7</v>
+      </c>
+      <c r="BC57" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="BD57" s="9">
+        <v>-76</v>
+      </c>
+      <c r="BE57">
+        <v>18.3</v>
+      </c>
+      <c r="BF57">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:58">
+      <c r="A58">
+        <v>60</v>
+      </c>
+      <c r="B58">
+        <v>80</v>
+      </c>
+      <c r="C58">
+        <v>45</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58">
+        <v>45</v>
+      </c>
+      <c r="H58">
+        <v>52.4</v>
+      </c>
+      <c r="S58">
+        <v>49.3</v>
+      </c>
+      <c r="T58">
+        <v>-56.5</v>
+      </c>
+      <c r="U58">
+        <v>46.1</v>
+      </c>
+      <c r="V58">
+        <v>-51.3</v>
+      </c>
+      <c r="X58">
+        <v>49.3</v>
+      </c>
+      <c r="Y58">
+        <v>-56.5</v>
+      </c>
+      <c r="Z58">
+        <v>46.1</v>
+      </c>
+      <c r="AA58">
+        <v>-51.3</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA58">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BB58">
+        <v>-73.8</v>
+      </c>
+      <c r="BC58" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BD58" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="BE58">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="BF58">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:58">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59">
+        <v>80</v>
+      </c>
+      <c r="C59">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:58">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60">
+        <v>80</v>
+      </c>
+      <c r="C60">
+        <v>15</v>
+      </c>
+      <c r="D60">
+        <v>30</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:58">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>80</v>
+      </c>
+      <c r="C61">
+        <v>15</v>
+      </c>
+      <c r="D61">
+        <v>45</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:58">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>80</v>
+      </c>
+      <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:58">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>80</v>
+      </c>
+      <c r="C63">
+        <v>30</v>
+      </c>
+      <c r="D63">
+        <v>30</v>
+      </c>
+      <c r="E63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:58">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64">
+        <v>80</v>
+      </c>
+      <c r="C64">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>45</v>
+      </c>
+      <c r="E64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>60</v>
+      </c>
+      <c r="B65">
+        <v>80</v>
+      </c>
+      <c r="C65">
+        <v>45</v>
+      </c>
+      <c r="D65">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>60</v>
+      </c>
+      <c r="B66">
+        <v>80</v>
+      </c>
+      <c r="C66">
+        <v>45</v>
+      </c>
+      <c r="D66">
+        <v>30</v>
+      </c>
+      <c r="E66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>60</v>
+      </c>
+      <c r="B67">
+        <v>80</v>
+      </c>
+      <c r="C67">
+        <v>45</v>
+      </c>
+      <c r="D67">
+        <v>45</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>60</v>
+      </c>
+      <c r="B68">
+        <v>80</v>
+      </c>
+      <c r="C68">
+        <v>15</v>
+      </c>
+      <c r="D68">
+        <v>15</v>
+      </c>
+      <c r="E68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>60</v>
+      </c>
+      <c r="B69">
+        <v>80</v>
+      </c>
+      <c r="C69">
+        <v>15</v>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>60</v>
+      </c>
+      <c r="B70">
+        <v>80</v>
+      </c>
+      <c r="C70">
+        <v>15</v>
+      </c>
+      <c r="D70">
+        <v>45</v>
+      </c>
+      <c r="E70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>60</v>
+      </c>
+      <c r="B71">
+        <v>80</v>
+      </c>
+      <c r="C71">
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>60</v>
+      </c>
+      <c r="B72">
+        <v>80</v>
+      </c>
+      <c r="C72">
+        <v>30</v>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+      <c r="E72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>60</v>
+      </c>
+      <c r="B73">
+        <v>80</v>
+      </c>
+      <c r="C73">
+        <v>30</v>
+      </c>
+      <c r="D73">
+        <v>45</v>
+      </c>
+      <c r="E73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>60</v>
+      </c>
+      <c r="B74">
+        <v>80</v>
+      </c>
+      <c r="C74">
+        <v>45</v>
+      </c>
+      <c r="D74">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>60</v>
+      </c>
+      <c r="B75">
+        <v>80</v>
+      </c>
+      <c r="C75">
+        <v>45</v>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>60</v>
+      </c>
+      <c r="B76">
+        <v>80</v>
+      </c>
+      <c r="C76">
+        <v>45</v>
+      </c>
+      <c r="D76">
+        <v>45</v>
+      </c>
+      <c r="E76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4176C027-713D-42A8-A3F2-4BC71F239850}">
   <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2232,15 +6573,15 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L2" s="5">
         <v>0.18</v>
@@ -2248,13 +6589,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" s="5">
         <v>0.85</v>
@@ -2262,7 +6603,7 @@
     </row>
     <row r="4" spans="1:15" ht="15">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5">
         <v>40</v>
@@ -2271,14 +6612,14 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <f>MIN(H4,H5)</f>
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4">
         <f>0.4*B7</f>
@@ -2288,24 +6629,24 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L4" s="5">
         <v>0.85</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N4">
         <v>0.85</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="5">
         <v>60</v>
@@ -2314,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5">
         <f>0.1*MIN(B4,B5)</f>
@@ -2327,12 +6668,12 @@
         <v>0.96</v>
       </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5">
         <v>15</v>
@@ -2341,14 +6682,14 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <f>MAX(H6:H7)</f>
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H6">
         <f>0.04*MIN(B4,B5)</f>
@@ -2358,19 +6699,19 @@
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" s="4">
         <f>0.00256*B8*B8*L4*L3</f>
         <v>41.616</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="5">
         <v>15</v>
@@ -2390,16 +6731,16 @@
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="5">
         <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4">
         <f>MAX(F6,F4)</f>
@@ -2411,65 +6752,65 @@
     </row>
     <row r="10" spans="1:15" ht="15">
       <c r="A10" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" t="s">
         <v>84</v>
       </c>
-      <c r="H11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" t="s">
-        <v>83</v>
-      </c>
       <c r="J11" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <f>($B$5-2.4*$B$7)*($B$4-2.4*$B$7)</f>
@@ -2511,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13">
         <f>($B$5-1.2*$B$7)*($B$4-1.2*$B$7)-C12</f>
@@ -2553,7 +6894,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <f>B4*B5-C12-C13-4*C15</f>
@@ -2595,7 +6936,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <f>0.2*$B$7*$B$7</f>
@@ -2634,7 +6975,7 @@
     </row>
     <row r="16" spans="1:15" ht="15">
       <c r="B16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1">
         <f>C12+C13+C14+4*C15</f>
@@ -2647,7 +6988,7 @@
     </row>
     <row r="19" spans="1:13" ht="15">
       <c r="A19" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2655,7 +6996,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20">
         <f>($B$5-2*$F$8)*($B$6)</f>
@@ -2697,7 +7038,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <f>F8*B6</f>
@@ -2736,7 +7077,7 @@
     </row>
     <row r="23" spans="1:13" ht="15">
       <c r="A23" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2744,7 +7085,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <f>($B$4-2*$F$8)*($B$6)</f>
@@ -2786,7 +7127,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <f>$F$8*B6</f>
@@ -2828,7 +7169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1C204F-B815-41FF-8AD4-130B8F24A18C}">
   <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2839,15 +7180,15 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L2" s="5">
         <v>0.18</v>
@@ -2855,13 +7196,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" s="5">
         <v>0.85</v>
@@ -2869,7 +7210,7 @@
     </row>
     <row r="4" spans="1:15" ht="15">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5">
         <v>40</v>
@@ -2878,14 +7219,14 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <f>MIN(H4,H5)</f>
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4">
         <f>0.4*B7</f>
@@ -2895,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L4" s="5">
         <v>0.91</v>
@@ -2904,12 +7245,12 @@
         <v>0.85</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="5">
         <v>60</v>
@@ -2918,7 +7259,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5">
         <f>0.1*MIN(B4,B5)</f>
@@ -2931,12 +7272,12 @@
         <v>0.91</v>
       </c>
       <c r="O5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5">
         <v>15</v>
@@ -2945,14 +7286,14 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <f>MAX(H6:H7)</f>
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H6">
         <f>0.04*MIN(B4,B5)</f>
@@ -2962,25 +7303,25 @@
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" s="4">
         <f>0.00256*B9*B9*L4*L3</f>
         <v>44.553600000000003</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6">
         <v>0.96</v>
       </c>
       <c r="O6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="7">
         <f>$B$6+TAN($B$8 * 6.28 / 360)*$B$4/2</f>
@@ -3001,16 +7342,16 @@
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" s="5">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4">
         <f>MAX(F6,F4)</f>
@@ -3022,13 +7363,13 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="5">
         <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -3036,65 +7377,65 @@
     </row>
     <row r="11" spans="1:15" ht="15">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" t="s">
         <v>84</v>
       </c>
-      <c r="H12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" t="s">
-        <v>83</v>
-      </c>
       <c r="J12" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <f>F8*F8</f>
@@ -3133,10 +7474,10 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14">
         <f>F8*F8</f>
@@ -3175,10 +7516,10 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15">
         <f>(B4/2-2*F8)*F8</f>
@@ -3217,10 +7558,10 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16">
         <f>(B5-2*F8)*F8</f>
@@ -3259,10 +7600,10 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <f>(B5-2*$F$8)*$F$8</f>
@@ -3304,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18">
         <f>($B$5*$B$4/2)-2*C13-2*C14-2*C15-C16-C17</f>
@@ -3343,7 +7684,7 @@
     </row>
     <row r="19" spans="1:13" ht="15">
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1">
         <f>C18+2*C13+2*C14+2*C15+C16+C17</f>
@@ -3356,7 +7697,7 @@
     </row>
     <row r="21" spans="1:13" ht="15">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -3364,7 +7705,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22">
         <f>F8*B6</f>
@@ -3406,7 +7747,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23">
         <f>($B$5-2*$F$8)*($B$6)</f>
@@ -3445,7 +7786,7 @@
     </row>
     <row r="25" spans="1:13" ht="15">
       <c r="A25" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -3453,7 +7794,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26">
         <f>0.5*($B$6+$B$6+$F$8*TAN(RADIANS($B$8)))*$F$8</f>
@@ -3544,7 +7885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8320E2-F01C-4F60-9B3D-82EC74076ADF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E668DF37-2661-40C7-A2D7-57252180E9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78B4F1C-D5B9-4837-9C78-02618DB4DFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23985" yWindow="285" windowWidth="22905" windowHeight="14130" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-25455" yWindow="645" windowWidth="22905" windowHeight="14130" activeTab="3" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="ASCE7-16 ExpC" sheetId="1" r:id="rId1"/>
     <sheet name="ASCE7-22 ExpC" sheetId="5" r:id="rId2"/>
     <sheet name="40x60 FLAT ASCE7-16" sheetId="2" r:id="rId3"/>
     <sheet name="40x60 GABLE ASCE7-16" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="40x60 HIP ASCE7-16" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="148">
   <si>
     <t>TDI Data Values</t>
   </si>
@@ -391,13 +392,106 @@
   </si>
   <si>
     <t>&lt;--- EXCEEDS 60 ft forChapter30 Figures</t>
+  </si>
+  <si>
+    <t>2e_B</t>
+  </si>
+  <si>
+    <t>2e_L</t>
+  </si>
+  <si>
+    <t>(B-2a)*a</t>
+  </si>
+  <si>
+    <t>2r_L</t>
+  </si>
+  <si>
+    <t>2r_B</t>
+  </si>
+  <si>
+    <t>1_L</t>
+  </si>
+  <si>
+    <t>0.5*(2L-B)*0.5*B</t>
+  </si>
+  <si>
+    <t>b =</t>
+  </si>
+  <si>
+    <t>1.414*a</t>
+  </si>
+  <si>
+    <t>c =</t>
+  </si>
+  <si>
+    <t>B/2-2a</t>
+  </si>
+  <si>
+    <t>Area L-side Trapezoid</t>
+  </si>
+  <si>
+    <t>0.5*(2L-4b-4a-2c)*c</t>
+  </si>
+  <si>
+    <t>A_trap-A3-A2e-A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d = </t>
+  </si>
+  <si>
+    <t>Longside (trapezoid)</t>
+  </si>
+  <si>
+    <t>ShortSide(triangle)</t>
+  </si>
+  <si>
+    <t>B (short side)</t>
+  </si>
+  <si>
+    <t>L (long side)</t>
+  </si>
+  <si>
+    <t>1_B</t>
+  </si>
+  <si>
+    <t>B/2-b-a</t>
+  </si>
+  <si>
+    <t>Area B-side Triangle</t>
+  </si>
+  <si>
+    <t>0.5*B*0.5*B</t>
+  </si>
+  <si>
+    <t>0.5*(B-2a-2b)*d</t>
+  </si>
+  <si>
+    <t>A_tri-A3-A2e-A1</t>
+  </si>
+  <si>
+    <t>SUBTOTAL (2 similar) =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">h/B = </t>
+  </si>
+  <si>
+    <t>HIP VERIFICATION - ASCE7-16</t>
+  </si>
+  <si>
+    <t>17.5'</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,6 +514,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
@@ -427,7 +527,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,8 +546,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -481,11 +587,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -497,7 +612,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2098,6 +2223,9 @@
       <c r="E23" t="s">
         <v>24</v>
       </c>
+      <c r="G23">
+        <v>20.36</v>
+      </c>
     </row>
     <row r="24" spans="1:33">
       <c r="A24">
@@ -7207,6 +7335,12 @@
       <c r="L3" s="5">
         <v>0.85</v>
       </c>
+      <c r="N3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15">
       <c r="A4" s="1" t="s">
@@ -7223,14 +7357,14 @@
       </c>
       <c r="F4">
         <f>MIN(H4,H5)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
       </c>
       <c r="H4">
         <f>0.4*B7</f>
-        <v>8.1424555792624798</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -7239,7 +7373,7 @@
         <v>77</v>
       </c>
       <c r="L4" s="5">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="N4">
         <v>0.85</v>
@@ -7269,10 +7403,10 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1">
@@ -7307,16 +7441,16 @@
       </c>
       <c r="L6" s="4">
         <f>0.00256*B9*B9*L4*L3</f>
-        <v>44.553600000000003</v>
+        <v>43.084800000000001</v>
       </c>
       <c r="M6" t="s">
         <v>41</v>
       </c>
       <c r="N6">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1">
@@ -7324,8 +7458,8 @@
         <v>58</v>
       </c>
       <c r="B7" s="7">
-        <f>$B$6+TAN($B$8 * 6.28 / 360)*$B$4/2</f>
-        <v>20.356138948156197</v>
+        <f>D7</f>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
@@ -7338,6 +7472,12 @@
       </c>
       <c r="I7" t="s">
         <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.96</v>
+      </c>
+      <c r="O7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1">
@@ -7355,7 +7495,7 @@
       </c>
       <c r="F8" s="4">
         <f>MAX(F6,F4)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="s">
         <v>1</v>
@@ -7439,7 +7579,7 @@
       </c>
       <c r="C13">
         <f>F8*F8</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>0.48</v>
@@ -7449,27 +7589,27 @@
       </c>
       <c r="G13">
         <f>$L$6*E13</f>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="H13">
         <f>$L$6*F13</f>
-        <v>-122.07686400000001</v>
+        <v>-118.05235200000001</v>
       </c>
       <c r="I13">
         <f>$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J13">
         <f>-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L13">
         <f>G13+I13</f>
-        <v>29.405376</v>
+        <v>28.435967999999999</v>
       </c>
       <c r="M13">
         <f>H13+J13</f>
-        <v>-130.09651200000002</v>
+        <v>-125.80761600000001</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -7481,7 +7621,7 @@
       </c>
       <c r="C14">
         <f>F8*F8</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>0.5</v>
@@ -7491,27 +7631,27 @@
       </c>
       <c r="G14">
         <f t="shared" ref="G14:G18" si="0">$L$6*E14</f>
-        <v>22.276800000000001</v>
+        <v>21.542400000000001</v>
       </c>
       <c r="H14">
         <f t="shared" ref="H14:H18" si="1">$L$6*F14</f>
-        <v>-149.25456000000003</v>
+        <v>-144.33408</v>
       </c>
       <c r="I14">
         <f t="shared" ref="I14:I18" si="2">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J14">
         <f t="shared" ref="J14:J18" si="3">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L14">
         <f t="shared" ref="L14:L18" si="4">G14+I14</f>
-        <v>30.296448000000002</v>
+        <v>29.297664000000001</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:M18" si="5">H14+J14</f>
-        <v>-157.27420800000002</v>
+        <v>-152.08934400000001</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -7523,7 +7663,7 @@
       </c>
       <c r="C15">
         <f>(B4/2-2*F8)*F8</f>
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0.38</v>
@@ -7533,27 +7673,27 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>16.930368000000001</v>
+        <v>16.372223999999999</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>-89.998272</v>
+        <v>-87.031295999999998</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J15">
         <f t="shared" si="3"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
-        <v>24.950016000000002</v>
+        <v>24.127488</v>
       </c>
       <c r="M15">
         <f t="shared" si="5"/>
-        <v>-98.017920000000004</v>
+        <v>-94.786559999999994</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -7565,7 +7705,7 @@
       </c>
       <c r="C16">
         <f>(B5-2*F8)*F8</f>
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="E16">
         <v>0.3</v>
@@ -7575,27 +7715,27 @@
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>-22.276800000000001</v>
+        <v>-21.542400000000001</v>
       </c>
       <c r="I16">
         <f t="shared" si="2"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J16">
         <f t="shared" si="3"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L16">
         <f t="shared" si="4"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M16">
         <f t="shared" si="5"/>
-        <v>-30.296448000000002</v>
+        <v>-29.297664000000001</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -7607,7 +7747,7 @@
       </c>
       <c r="C17">
         <f>(B5-2*$F$8)*$F$8</f>
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="E17">
         <v>0.3</v>
@@ -7617,27 +7757,27 @@
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>-49.008960000000009</v>
+        <v>-47.393280000000004</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J17">
         <f t="shared" si="3"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L17">
         <f t="shared" si="4"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>-57.028608000000006</v>
+        <v>-55.148544000000001</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -7649,7 +7789,7 @@
       </c>
       <c r="C18">
         <f>($B$5*$B$4/2)-2*C13-2*C14-2*C15-C16-C17</f>
-        <v>624</v>
+        <v>756</v>
       </c>
       <c r="E18">
         <v>0.3</v>
@@ -7659,27 +7799,27 @@
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>-22.276800000000001</v>
+        <v>-21.542400000000001</v>
       </c>
       <c r="I18">
         <f t="shared" si="2"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J18">
         <f t="shared" si="3"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L18">
         <f t="shared" si="4"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M18">
         <f t="shared" si="5"/>
-        <v>-30.296448000000002</v>
+        <v>-29.297664000000001</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15">
@@ -7709,7 +7849,7 @@
       </c>
       <c r="C22">
         <f>F8*B6</f>
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E22">
         <v>0.83</v>
@@ -7719,27 +7859,27 @@
       </c>
       <c r="G22">
         <f>$L$6*E22</f>
-        <v>36.979488000000003</v>
+        <v>35.760384000000002</v>
       </c>
       <c r="H22">
         <f>$L$6*F22</f>
-        <v>-50.345568</v>
+        <v>-48.685823999999997</v>
       </c>
       <c r="I22">
         <f t="shared" ref="I22:I24" si="6">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J22">
         <f t="shared" ref="J22:J24" si="7">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L22">
         <f>G22+I22</f>
-        <v>44.999136000000007</v>
+        <v>43.515647999999999</v>
       </c>
       <c r="M22">
         <f>H22+J22</f>
-        <v>-58.365216000000004</v>
+        <v>-56.441087999999993</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -7751,7 +7891,7 @@
       </c>
       <c r="C23">
         <f>($B$5-2*$F$8)*($B$6)</f>
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="E23">
         <v>0.71</v>
@@ -7761,27 +7901,27 @@
       </c>
       <c r="G23">
         <f>$L$6*E23</f>
-        <v>31.633056</v>
+        <v>30.590208000000001</v>
       </c>
       <c r="H23">
         <f>$L$6*F23</f>
-        <v>-35.642880000000005</v>
+        <v>-34.467840000000002</v>
       </c>
       <c r="I23">
         <f t="shared" si="6"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J23">
         <f t="shared" si="7"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L23">
         <f>G23+I23</f>
-        <v>39.652704</v>
+        <v>38.345472000000001</v>
       </c>
       <c r="M23">
         <f>H23+J23</f>
-        <v>-43.662528000000009</v>
+        <v>-42.223104000000006</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15">
@@ -7798,7 +7938,7 @@
       </c>
       <c r="C26">
         <f>0.5*($B$6+$B$6+$F$8*TAN(RADIANS($B$8)))*$F$8</f>
-        <v>62.143593539448979</v>
+        <v>46.205771365940052</v>
       </c>
       <c r="E26">
         <v>0.83</v>
@@ -7808,27 +7948,27 @@
       </c>
       <c r="G26">
         <f>$L$6*E26</f>
-        <v>36.979488000000003</v>
+        <v>35.760384000000002</v>
       </c>
       <c r="H26">
         <f>$L$6*F26</f>
-        <v>-50.345568</v>
+        <v>-48.685823999999997</v>
       </c>
       <c r="I26">
         <f t="shared" ref="I26:I28" si="8">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J26">
         <f t="shared" ref="J26:J28" si="9">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L26">
         <f>G26+I26</f>
-        <v>44.999136000000007</v>
+        <v>43.515647999999999</v>
       </c>
       <c r="M26">
         <f>H26+J26</f>
-        <v>-58.365216000000004</v>
+        <v>-56.441087999999993</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -7837,7 +7977,7 @@
       </c>
       <c r="C27">
         <f>($B$6*$B$4)+0.5*$B$4/2*TAN(RADIANS(B8))*$B$4  - 2*C26</f>
-        <v>582.8924898935511</v>
+        <v>614.768134240569</v>
       </c>
       <c r="E27">
         <v>0.7</v>
@@ -7847,27 +7987,27 @@
       </c>
       <c r="G27">
         <f>$L$6*E27</f>
-        <v>31.187519999999999</v>
+        <v>30.15936</v>
       </c>
       <c r="H27">
         <f>$L$6*F27</f>
-        <v>-35.642880000000005</v>
+        <v>-34.467840000000002</v>
       </c>
       <c r="I27">
         <f t="shared" si="8"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J27">
         <f t="shared" si="9"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L27">
         <f>G27+I27</f>
-        <v>39.207167999999996</v>
+        <v>37.914624000000003</v>
       </c>
       <c r="M27">
         <f>H27+J27</f>
-        <v>-43.662528000000009</v>
+        <v>-42.223104000000006</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -7877,7 +8017,7 @@
       </c>
       <c r="C30">
         <f>B30*F8</f>
-        <v>1.0712277896312392</v>
+        <v>0.80342084222342947</v>
       </c>
     </row>
   </sheetData>
@@ -7886,6 +8026,903 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07C503-ABDA-4895-82E4-84650588D8A5}">
+  <dimension ref="A1:O45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="5">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4">
+        <f>MIN(H4,H5)</f>
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4">
+        <f>0.4*B7</f>
+        <v>8.1424555792624798</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N4">
+        <v>0.85</v>
+      </c>
+      <c r="O4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="5">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5">
+        <f>0.1*MIN(B4,B5)</f>
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.91</v>
+      </c>
+      <c r="O5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" thickBot="1">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="5">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6">
+        <f>MAX(H6:H7)</f>
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6">
+        <f>0.04*MIN(B4,B5)</f>
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="4">
+        <f>0.00256*B9*B9*L4*L3</f>
+        <v>44.553600000000003</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6">
+        <v>0.96</v>
+      </c>
+      <c r="O6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="12">
+        <f>$B$6+TAN($B$8 * 6.28 / 360)*$B$4/2</f>
+        <v>20.356138948156197</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" thickBot="1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="5">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4">
+        <f>MAX(F6,F4)</f>
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="5">
+        <v>150</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9">
+        <f>B7/B4</f>
+        <v>0.50890347370390487</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" ht="15">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15">
+      <c r="A12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="16">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13">
+        <f>F8*F8</f>
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>0.65</v>
+      </c>
+      <c r="F13">
+        <v>-1.7</v>
+      </c>
+      <c r="G13">
+        <f>$L$6*E13</f>
+        <v>28.959840000000003</v>
+      </c>
+      <c r="H13">
+        <f>$L$6*F13</f>
+        <v>-75.741120000000009</v>
+      </c>
+      <c r="I13">
+        <f>$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J13">
+        <f>-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L13">
+        <f>G13+I13</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="M13">
+        <f>H13+J13</f>
+        <v>-83.760768000000013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14">
+        <f>(B5-2*F8)*F8</f>
+        <v>208</v>
+      </c>
+      <c r="E14">
+        <v>0.3</v>
+      </c>
+      <c r="F14">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ref="G14:H33" si="0">$L$6*E14</f>
+        <v>13.36608</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>-49.008960000000009</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ref="I14:I33" si="1">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J14">
+        <f t="shared" ref="J14:J33" si="2">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:M33" si="3">G14+I14</f>
+        <v>21.385728</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>-57.028608000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15">
+        <f>C27-C13-C14-C16</f>
+        <v>231.74399999999997</v>
+      </c>
+      <c r="E15">
+        <v>0.3</v>
+      </c>
+      <c r="F15">
+        <v>-1.3</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>-57.919680000000007</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>-65.939328000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="14">
+        <f>0.5*((B5-2*C29-2*F8)+(B5-2*F8-2*C29-2*C30))*C30</f>
+        <v>344.25600000000003</v>
+      </c>
+      <c r="E16">
+        <v>0.3</v>
+      </c>
+      <c r="F16">
+        <v>-1</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>-44.553600000000003</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="3"/>
+        <v>-52.573248000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="B17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17">
+        <f>2*SUM(C13:C16)</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15">
+      <c r="A19" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="16">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20">
+        <f>F8*F8</f>
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>0.65</v>
+      </c>
+      <c r="F20">
+        <v>-1.7</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ref="G17:G20" si="4">$L$6*E20</f>
+        <v>28.959840000000003</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H17:H20" si="5">$L$6*F20</f>
+        <v>-75.741120000000009</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ref="L17:L20" si="6">G20+I20</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="M20">
+        <f t="shared" ref="M17:M20" si="7">H20+J20</f>
+        <v>-83.760768000000013</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21">
+        <f>(B4-2*$F$8)*$F$8</f>
+        <v>128</v>
+      </c>
+      <c r="E21">
+        <v>0.3</v>
+      </c>
+      <c r="F21">
+        <v>-1.23</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ref="G21:G23" si="8">$L$6*E21</f>
+        <v>13.36608</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ref="H21:H23" si="9">$L$6*F21</f>
+        <v>-54.800928000000006</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ref="L21:L23" si="10">G21+I21</f>
+        <v>21.385728</v>
+      </c>
+      <c r="M21">
+        <f t="shared" ref="M21:M23" si="11">H21+J21</f>
+        <v>-62.820576000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22">
+        <f>C28-C20-C21-C23</f>
+        <v>149.00166399999998</v>
+      </c>
+      <c r="E22">
+        <v>0.3</v>
+      </c>
+      <c r="F22">
+        <v>-1.4</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="8"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="9"/>
+        <v>-62.375039999999998</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="10"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="11"/>
+        <v>-70.394688000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="14">
+        <f>0.5*(B4-2*F8-2*C29)*C31</f>
+        <v>106.99833600000002</v>
+      </c>
+      <c r="E23">
+        <v>0.3</v>
+      </c>
+      <c r="F23">
+        <v>-1</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="8"/>
+        <v>13.36608</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="9"/>
+        <v>-44.553600000000003</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="10"/>
+        <v>21.385728</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="11"/>
+        <v>-52.573248000000007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24">
+        <f>2*SUM(C20:C23)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15">
+      <c r="B25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="1">
+        <f>C17+C24</f>
+        <v>2400</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <f>IF(C25=B4*B5,"OK","N.G.")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27">
+        <f>0.5*(2*B5-B4)*0.5*B4</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28">
+        <f>0.5*B4*0.5*B4</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29">
+        <f>1.414*F8</f>
+        <v>5.6559999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30">
+        <f>B4/2-2*F8</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31">
+        <f>0.5*B4-C29-F8</f>
+        <v>10.344000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15">
+      <c r="C34" s="1"/>
+    </row>
+    <row r="36" spans="1:13" ht="15">
+      <c r="A36" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37">
+        <f>F8*B6</f>
+        <v>60</v>
+      </c>
+      <c r="E37">
+        <v>0.83</v>
+      </c>
+      <c r="F37">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="G37">
+        <f>$L$6*E37</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="H37">
+        <f>$L$6*F37</f>
+        <v>-50.345568</v>
+      </c>
+      <c r="I37">
+        <f t="shared" ref="I37:I39" si="12">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J37">
+        <f t="shared" ref="J37:J39" si="13">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L37">
+        <f>G37+I37</f>
+        <v>44.999136000000007</v>
+      </c>
+      <c r="M37">
+        <f>H37+J37</f>
+        <v>-58.365216000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38">
+        <f>($B$5-2*$F$8)*($B$6)</f>
+        <v>780</v>
+      </c>
+      <c r="E38">
+        <v>0.71</v>
+      </c>
+      <c r="F38">
+        <v>-0.8</v>
+      </c>
+      <c r="G38">
+        <f>$L$6*E38</f>
+        <v>31.633056</v>
+      </c>
+      <c r="H38">
+        <f>$L$6*F38</f>
+        <v>-35.642880000000005</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="12"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="13"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L38">
+        <f>G38+I38</f>
+        <v>39.652704</v>
+      </c>
+      <c r="M38">
+        <f>H38+J38</f>
+        <v>-43.662528000000009</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15">
+      <c r="A40" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41">
+        <f>F8*B6</f>
+        <v>60</v>
+      </c>
+      <c r="E41">
+        <v>0.83</v>
+      </c>
+      <c r="F41">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="G41">
+        <f>$L$6*E41</f>
+        <v>36.979488000000003</v>
+      </c>
+      <c r="H41">
+        <f>$L$6*F41</f>
+        <v>-50.345568</v>
+      </c>
+      <c r="I41">
+        <f t="shared" ref="I41:I43" si="14">$L$6*$L$2</f>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J41">
+        <f t="shared" ref="J41:J43" si="15">-$L$6*$L$2</f>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L41">
+        <f>G41+I41</f>
+        <v>44.999136000000007</v>
+      </c>
+      <c r="M41">
+        <f>H41+J41</f>
+        <v>-58.365216000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42">
+        <f>(B4-2*F8)*B6</f>
+        <v>480</v>
+      </c>
+      <c r="E42">
+        <v>0.7</v>
+      </c>
+      <c r="F42">
+        <v>-0.8</v>
+      </c>
+      <c r="G42">
+        <f>$L$6*E42</f>
+        <v>31.187519999999999</v>
+      </c>
+      <c r="H42">
+        <f>$L$6*F42</f>
+        <v>-35.642880000000005</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="14"/>
+        <v>8.0196480000000001</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="15"/>
+        <v>-8.0196480000000001</v>
+      </c>
+      <c r="L42">
+        <f>G42+I42</f>
+        <v>39.207167999999996</v>
+      </c>
+      <c r="M42">
+        <f>H42+J42</f>
+        <v>-43.662528000000009</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="B45">
+        <f>TAN($B$8*6.28/360)</f>
+        <v>0.2678069474078098</v>
+      </c>
+      <c r="C45">
+        <f>B45*F8</f>
+        <v>1.0712277896312392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8320E2-F01C-4F60-9B3D-82EC74076ADF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/WindLoadCalculations/VerificationSpreadsheet.xlsx
+++ b/WindLoadCalculations/VerificationSpreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\ShearWallCalculator\WindLoadCalculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78B4F1C-D5B9-4837-9C78-02618DB4DFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C54B60-786A-40EA-8667-19CA86CBC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25455" yWindow="645" windowWidth="22905" windowHeight="14130" activeTab="3" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
+    <workbookView xWindow="-25455" yWindow="645" windowWidth="25125" windowHeight="14130" xr2:uid="{7D93B743-C6BA-493F-B145-C673A908EA6D}"/>
   </bookViews>
   <sheets>
     <sheet name="ASCE7-16 ExpC" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="148">
   <si>
     <t>TDI Data Values</t>
   </si>
@@ -391,9 +391,6 @@
     <t>Zone 3e-</t>
   </si>
   <si>
-    <t>&lt;--- EXCEEDS 60 ft forChapter30 Figures</t>
-  </si>
-  <si>
     <t>2e_B</t>
   </si>
   <si>
@@ -485,6 +482,9 @@
   </si>
   <si>
     <t>z</t>
+  </si>
+  <si>
+    <t>HipZones</t>
   </si>
 </sst>
 </file>
@@ -957,93 +957,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F035135-BEB2-4F94-BA52-74AFC5FDF7DD}">
-  <dimension ref="A1:BL81"/>
+  <dimension ref="A1:AX80"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="9" style="9"/>
+    <col min="31" max="31" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="2" customFormat="1" ht="23.25">
+    <row r="1" spans="1:50" s="2" customFormat="1" ht="23.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="BI1" s="8"/>
-      <c r="BJ1" s="8"/>
-    </row>
-    <row r="2" spans="1:64" ht="15">
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+    </row>
+    <row r="2" spans="1:50" ht="15">
       <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="AH2" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:64">
+    <row r="3" spans="1:50">
       <c r="A3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:64">
+    <row r="4" spans="1:50">
       <c r="A4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:64" ht="15">
+    <row r="5" spans="1:50" ht="15">
       <c r="A5" t="s">
         <v>40</v>
       </c>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="BF5" s="1" t="s">
+      <c r="AE5" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:64" ht="15">
+    <row r="7" spans="1:50" ht="15">
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="X7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="U7" t="s">
+        <v>110</v>
+      </c>
       <c r="Z7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE7" t="s">
         <v>109</v>
       </c>
-      <c r="AI7" s="1"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
-      <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="1"/>
-      <c r="AR7" s="1"/>
-      <c r="AS7" s="1"/>
-      <c r="AT7" s="1"/>
-      <c r="AU7" s="1"/>
-      <c r="AV7" s="1"/>
-      <c r="AW7" s="1"/>
-      <c r="BI7" s="10"/>
-      <c r="BJ7" s="10"/>
-      <c r="BK7" s="1"/>
-      <c r="BL7" s="1"/>
-    </row>
-    <row r="8" spans="1:64">
+    </row>
+    <row r="8" spans="1:50">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1068,23 +1062,20 @@
       <c r="I8" t="s">
         <v>19</v>
       </c>
-      <c r="M8" t="s">
-        <v>38</v>
+      <c r="U8" t="s">
+        <v>36</v>
       </c>
       <c r="Z8" t="s">
         <v>36</v>
       </c>
-      <c r="AE8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>37</v>
-      </c>
-      <c r="BG8" t="s">
+      <c r="AF8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:64">
+      <c r="AO8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1119,28 +1110,28 @@
         <v>35</v>
       </c>
       <c r="O9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="R9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="T9" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="U9" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="V9" t="s">
-        <v>113</v>
+        <v>12</v>
+      </c>
+      <c r="W9" t="s">
+        <v>13</v>
       </c>
       <c r="Y9" t="s">
         <v>14</v>
@@ -1155,16 +1146,28 @@
         <v>13</v>
       </c>
       <c r="AD9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>11</v>
       </c>
       <c r="AM9" t="s">
         <v>5</v>
@@ -1173,55 +1176,37 @@
         <v>6</v>
       </c>
       <c r="AO9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ9" t="s">
         <v>29</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AR9" t="s">
         <v>30</v>
       </c>
-      <c r="AQ9" t="s">
+      <c r="AS9" t="s">
         <v>31</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AT9" t="s">
         <v>32</v>
       </c>
-      <c r="AS9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>35</v>
-      </c>
       <c r="AU9" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="AV9" t="s">
-        <v>48</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>22</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>6</v>
-      </c>
-      <c r="BI9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:64">
+        <v>115</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50">
       <c r="A10">
         <v>40</v>
       </c>
@@ -1243,56 +1228,56 @@
       <c r="H10">
         <v>41.6</v>
       </c>
+      <c r="T10">
+        <v>41.8</v>
+      </c>
+      <c r="U10">
+        <v>-54.4</v>
+      </c>
+      <c r="V10">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="W10">
+        <v>-40.9</v>
+      </c>
       <c r="Y10">
         <v>41.8</v>
       </c>
       <c r="Z10">
+        <v>36.6</v>
+      </c>
+      <c r="AA10">
+        <v>41.8</v>
+      </c>
+      <c r="AB10">
         <v>-54.4</v>
       </c>
-      <c r="AA10">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="AB10">
-        <v>-40.9</v>
-      </c>
       <c r="AD10">
-        <v>41.8</v>
+        <v>15.9</v>
       </c>
       <c r="AE10">
-        <v>36.6</v>
+        <v>-44.9</v>
       </c>
       <c r="AF10">
-        <v>41.8</v>
+        <v>15.8</v>
       </c>
       <c r="AG10">
-        <v>-54.4</v>
-      </c>
-      <c r="BE10">
-        <v>15.9</v>
-      </c>
-      <c r="BF10">
-        <v>-44.9</v>
-      </c>
-      <c r="BG10">
+        <v>-49</v>
+      </c>
+      <c r="AH10" s="9">
         <v>15.8</v>
       </c>
-      <c r="BH10">
-        <v>-49</v>
-      </c>
-      <c r="BI10" s="9">
-        <v>15.8</v>
-      </c>
-      <c r="BJ10" s="9">
+      <c r="AI10" s="9">
         <v>-65.7</v>
       </c>
-      <c r="BK10">
+      <c r="AJ10">
         <v>16.899999999999999</v>
       </c>
-      <c r="BL10">
+      <c r="AK10">
         <v>-113.3</v>
       </c>
     </row>
-    <row r="11" spans="1:64">
+    <row r="11" spans="1:50">
       <c r="A11">
         <v>40</v>
       </c>
@@ -1314,6 +1299,18 @@
       <c r="H11">
         <v>48.1</v>
       </c>
+      <c r="T11">
+        <v>47.3</v>
+      </c>
+      <c r="U11">
+        <v>-58</v>
+      </c>
+      <c r="V11">
+        <v>42.3</v>
+      </c>
+      <c r="W11">
+        <v>-47.1</v>
+      </c>
       <c r="Y11">
         <v>47.3</v>
       </c>
@@ -1326,44 +1323,32 @@
       <c r="AB11">
         <v>-47.1</v>
       </c>
-      <c r="AD11">
-        <v>47.3</v>
-      </c>
-      <c r="AE11">
-        <v>-58</v>
+      <c r="AD11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>42</v>
       </c>
       <c r="AF11">
-        <v>42.3</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AG11">
-        <v>-47.1</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>42</v>
-      </c>
-      <c r="BG11">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="BH11">
         <v>-71.099999999999994</v>
       </c>
-      <c r="BI11" s="9">
+      <c r="AH11" s="9">
         <v>18.3</v>
       </c>
-      <c r="BJ11" s="9">
+      <c r="AI11" s="9">
         <v>-76</v>
       </c>
-      <c r="BK11">
+      <c r="AJ11">
         <v>18.3</v>
       </c>
-      <c r="BL11">
+      <c r="AK11">
         <v>-99.2</v>
       </c>
     </row>
-    <row r="12" spans="1:64">
+    <row r="12" spans="1:50">
       <c r="A12">
         <v>40</v>
       </c>
@@ -1385,6 +1370,18 @@
       <c r="H12">
         <v>52.4</v>
       </c>
+      <c r="T12">
+        <v>50.6</v>
+      </c>
+      <c r="U12">
+        <v>-59.4</v>
+      </c>
+      <c r="V12">
+        <v>46.1</v>
+      </c>
+      <c r="W12">
+        <v>-51.3</v>
+      </c>
       <c r="Y12">
         <v>50.6</v>
       </c>
@@ -1397,44 +1394,32 @@
       <c r="AB12">
         <v>-51.3</v>
       </c>
-      <c r="AD12">
-        <v>50.6</v>
-      </c>
-      <c r="AE12">
-        <v>-59.4</v>
-      </c>
-      <c r="AF12">
-        <v>46.1</v>
-      </c>
-      <c r="AG12">
-        <v>-51.3</v>
-      </c>
-      <c r="BE12" t="s">
+      <c r="AD12" t="s">
         <v>42</v>
       </c>
-      <c r="BF12" t="s">
+      <c r="AE12" t="s">
         <v>42</v>
       </c>
-      <c r="BG12" t="s">
+      <c r="AF12" t="s">
         <v>42</v>
       </c>
-      <c r="BH12" t="s">
+      <c r="AG12" t="s">
         <v>42</v>
       </c>
-      <c r="BI12" s="9">
+      <c r="AH12" s="9">
         <v>19.899999999999999</v>
       </c>
-      <c r="BJ12" s="9">
+      <c r="AI12" s="9">
         <v>-82.8</v>
       </c>
-      <c r="BK12">
+      <c r="AJ12">
         <v>19.899999999999999</v>
       </c>
-      <c r="BL12">
+      <c r="AK12">
         <v>-89.7</v>
       </c>
     </row>
-    <row r="13" spans="1:64">
+    <row r="13" spans="1:50">
       <c r="A13">
         <v>40</v>
       </c>
@@ -1451,76 +1436,76 @@
         <v>23</v>
       </c>
       <c r="G13">
-        <v>20.36</v>
+        <v>17.68</v>
       </c>
       <c r="H13">
-        <v>44.3</v>
+        <v>43</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
-      <c r="K13">
-        <v>21.3</v>
-      </c>
-      <c r="L13">
-        <v>-30.1</v>
-      </c>
-      <c r="M13">
-        <v>21.3</v>
-      </c>
-      <c r="N13">
-        <v>-30.1</v>
-      </c>
-      <c r="O13">
-        <v>25</v>
-      </c>
-      <c r="P13">
-        <v>-98.3</v>
-      </c>
-      <c r="Q13">
-        <v>21.3</v>
-      </c>
-      <c r="R13">
-        <v>-56</v>
-      </c>
-      <c r="S13">
-        <v>29.3</v>
-      </c>
       <c r="T13">
-        <v>-129.5</v>
+        <v>43.2</v>
       </c>
       <c r="U13">
-        <v>29.3</v>
+        <v>-56.2</v>
       </c>
       <c r="V13">
-        <v>-152.9</v>
+        <v>37.9</v>
+      </c>
+      <c r="W13">
+        <v>-42.2</v>
       </c>
       <c r="Y13">
-        <v>44.5</v>
+        <v>43.3</v>
       </c>
       <c r="Z13">
-        <v>-57.9</v>
+        <v>-56.4</v>
       </c>
       <c r="AA13">
-        <v>39</v>
+        <v>37.9</v>
       </c>
       <c r="AB13">
-        <v>-43.4</v>
-      </c>
-      <c r="AD13">
-        <v>44.6</v>
-      </c>
-      <c r="AE13">
-        <v>-58.1</v>
-      </c>
-      <c r="AF13">
-        <v>39</v>
-      </c>
-      <c r="AG13">
-        <v>-43.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:64">
+        <v>-42.2</v>
+      </c>
+      <c r="AM13">
+        <v>20.7</v>
+      </c>
+      <c r="AN13">
+        <v>-29.3</v>
+      </c>
+      <c r="AO13">
+        <v>20.7</v>
+      </c>
+      <c r="AP13">
+        <v>-29.3</v>
+      </c>
+      <c r="AQ13">
+        <v>24.3</v>
+      </c>
+      <c r="AR13">
+        <v>-95.4</v>
+      </c>
+      <c r="AS13">
+        <v>20.7</v>
+      </c>
+      <c r="AT13">
+        <v>-54.4</v>
+      </c>
+      <c r="AU13">
+        <v>28.5</v>
+      </c>
+      <c r="AV13">
+        <v>-125.7</v>
+      </c>
+      <c r="AW13">
+        <v>28.5</v>
+      </c>
+      <c r="AX13">
+        <v>-148.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50">
       <c r="A14">
         <v>40</v>
       </c>
@@ -1537,76 +1522,76 @@
         <v>23</v>
       </c>
       <c r="G14">
-        <v>26.55</v>
+        <v>20.77</v>
       </c>
       <c r="H14">
-        <v>46.9</v>
+        <v>44.5</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
-      <c r="K14">
-        <v>31.9</v>
-      </c>
-      <c r="L14">
-        <v>-45.9</v>
-      </c>
-      <c r="M14">
-        <v>31.9</v>
-      </c>
-      <c r="N14">
-        <v>-45.9</v>
-      </c>
-      <c r="O14">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="P14">
-        <v>-77.400000000000006</v>
-      </c>
-      <c r="Q14">
-        <v>31.9</v>
-      </c>
-      <c r="R14">
-        <v>-45.9</v>
-      </c>
-      <c r="S14">
-        <v>47.8</v>
-      </c>
       <c r="T14">
-        <v>-117.2</v>
+        <v>44.7</v>
       </c>
       <c r="U14">
-        <v>47.8</v>
+        <v>-57.9</v>
       </c>
       <c r="V14">
-        <v>-95.7</v>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="W14">
+        <v>-43.6</v>
       </c>
       <c r="Y14">
-        <v>47.1</v>
+        <v>44.8</v>
       </c>
       <c r="Z14">
-        <v>-61</v>
+        <v>-58.3</v>
       </c>
       <c r="AA14">
-        <v>41.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="AB14">
-        <v>-45.9</v>
-      </c>
-      <c r="AD14">
-        <v>47.2</v>
-      </c>
-      <c r="AE14">
-        <v>-61.4</v>
-      </c>
-      <c r="AF14">
-        <v>41.2</v>
-      </c>
-      <c r="AG14">
-        <v>-45.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:64">
+        <v>-43.6</v>
+      </c>
+      <c r="AM14">
+        <v>30.3</v>
+      </c>
+      <c r="AN14">
+        <v>-43.6</v>
+      </c>
+      <c r="AO14">
+        <v>30.3</v>
+      </c>
+      <c r="AP14">
+        <v>-43.6</v>
+      </c>
+      <c r="AQ14">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="AR14">
+        <v>-73.5</v>
+      </c>
+      <c r="AS14">
+        <v>30.3</v>
+      </c>
+      <c r="AT14">
+        <v>-43.6</v>
+      </c>
+      <c r="AU14">
+        <v>45.4</v>
+      </c>
+      <c r="AV14">
+        <v>-111.3</v>
+      </c>
+      <c r="AW14">
+        <v>45.3</v>
+      </c>
+      <c r="AX14">
+        <v>-90.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50">
       <c r="A15">
         <v>40</v>
       </c>
@@ -1623,76 +1608,76 @@
         <v>23</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H15">
-        <v>49.7</v>
+        <v>46.3</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
-      <c r="K15">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="L15">
-        <v>-48.7</v>
-      </c>
-      <c r="M15">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="N15">
-        <v>-48.7</v>
-      </c>
-      <c r="O15">
-        <v>39.4</v>
-      </c>
-      <c r="P15">
-        <v>-82</v>
-      </c>
-      <c r="Q15">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="R15">
-        <v>-48.7</v>
-      </c>
-      <c r="S15">
-        <v>50.7</v>
-      </c>
       <c r="T15">
-        <v>-124.2</v>
+        <v>46.4</v>
       </c>
       <c r="U15">
-        <v>50.7</v>
+        <v>-59.9</v>
       </c>
       <c r="V15">
-        <v>-101.4</v>
+        <v>40.700000000000003</v>
+      </c>
+      <c r="W15">
+        <v>-45.4</v>
       </c>
       <c r="Y15">
-        <v>49.8</v>
+        <v>46.6</v>
       </c>
       <c r="Z15">
-        <v>-64.3</v>
+        <v>-60.6</v>
       </c>
       <c r="AA15">
-        <v>43.7</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="AB15">
-        <v>-48.7</v>
-      </c>
-      <c r="AD15">
-        <v>50</v>
-      </c>
-      <c r="AE15">
-        <v>-65.099999999999994</v>
-      </c>
-      <c r="AF15">
-        <v>43.7</v>
-      </c>
-      <c r="AG15">
-        <v>-48.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:64">
+        <v>-45.4</v>
+      </c>
+      <c r="AM15">
+        <v>31.5</v>
+      </c>
+      <c r="AN15">
+        <v>-45.4</v>
+      </c>
+      <c r="AO15">
+        <v>31.5</v>
+      </c>
+      <c r="AP15">
+        <v>-45.4</v>
+      </c>
+      <c r="AQ15">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AR15">
+        <v>-76.400000000000006</v>
+      </c>
+      <c r="AS15">
+        <v>31.5</v>
+      </c>
+      <c r="AT15">
+        <v>-45.4</v>
+      </c>
+      <c r="AU15">
+        <v>47.2</v>
+      </c>
+      <c r="AV15">
+        <v>-115.7</v>
+      </c>
+      <c r="AW15">
+        <v>47.2</v>
+      </c>
+      <c r="AX15">
+        <v>-94.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50">
       <c r="A16">
         <v>40</v>
       </c>
@@ -1709,76 +1694,76 @@
         <v>23</v>
       </c>
       <c r="G16">
-        <v>35.36</v>
+        <v>32.68</v>
       </c>
       <c r="H16">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
-      <c r="K16">
-        <v>23.9</v>
-      </c>
-      <c r="L16">
-        <v>-33.9</v>
-      </c>
-      <c r="M16">
-        <v>23.9</v>
-      </c>
-      <c r="N16">
-        <v>-33.9</v>
-      </c>
-      <c r="O16">
-        <v>28.1</v>
-      </c>
-      <c r="P16">
-        <v>-110.4</v>
-      </c>
-      <c r="Q16">
-        <v>23.9</v>
-      </c>
-      <c r="R16">
-        <v>-62.9</v>
-      </c>
-      <c r="S16">
-        <v>33</v>
-      </c>
       <c r="T16">
-        <v>-145.5</v>
+        <v>48.2</v>
       </c>
       <c r="U16">
-        <v>33</v>
+        <v>-58.9</v>
       </c>
       <c r="V16">
-        <v>-171.8</v>
+        <v>43.1</v>
+      </c>
+      <c r="W16">
+        <v>-48</v>
       </c>
       <c r="Y16">
-        <v>49</v>
+        <v>48.2</v>
       </c>
       <c r="Z16">
-        <v>-59.9</v>
+        <v>-59.1</v>
       </c>
       <c r="AA16">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
       <c r="AB16">
-        <v>-48.8</v>
-      </c>
-      <c r="AD16">
-        <v>49</v>
-      </c>
-      <c r="AE16">
-        <v>-60</v>
-      </c>
-      <c r="AF16">
-        <v>43.8</v>
-      </c>
-      <c r="AG16">
-        <v>-48.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
+        <v>-48</v>
+      </c>
+      <c r="AM16">
+        <v>23.5</v>
+      </c>
+      <c r="AN16">
+        <v>-33.299999999999997</v>
+      </c>
+      <c r="AO16">
+        <v>23.5</v>
+      </c>
+      <c r="AP16">
+        <v>-33.299999999999997</v>
+      </c>
+      <c r="AQ16">
+        <v>27.6</v>
+      </c>
+      <c r="AR16">
+        <v>-108.6</v>
+      </c>
+      <c r="AS16">
+        <v>23.5</v>
+      </c>
+      <c r="AT16">
+        <v>-61.9</v>
+      </c>
+      <c r="AU16">
+        <v>32.4</v>
+      </c>
+      <c r="AV16">
+        <v>-143.1</v>
+      </c>
+      <c r="AW16">
+        <v>32.4</v>
+      </c>
+      <c r="AX16">
+        <v>-168.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50">
       <c r="A17">
         <v>40</v>
       </c>
@@ -1795,76 +1780,76 @@
         <v>23</v>
       </c>
       <c r="G17">
-        <v>41.55</v>
+        <v>35.770000000000003</v>
       </c>
       <c r="H17">
-        <v>51.5</v>
+        <v>49.9</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
-      <c r="K17">
-        <v>35</v>
-      </c>
-      <c r="L17">
-        <v>-50.5</v>
-      </c>
-      <c r="M17">
-        <v>35</v>
-      </c>
-      <c r="N17">
-        <v>-50.5</v>
-      </c>
-      <c r="O17">
-        <v>40.9</v>
-      </c>
-      <c r="P17">
-        <v>-85</v>
-      </c>
-      <c r="Q17">
-        <v>35</v>
-      </c>
-      <c r="R17">
-        <v>-50.5</v>
-      </c>
-      <c r="S17">
-        <v>52.5</v>
-      </c>
       <c r="T17">
-        <v>-128.80000000000001</v>
+        <v>49</v>
       </c>
       <c r="U17">
-        <v>52.5</v>
+        <v>-59.9</v>
       </c>
       <c r="V17">
-        <v>-105.2</v>
+        <v>43.9</v>
+      </c>
+      <c r="W17">
+        <v>-48.9</v>
       </c>
       <c r="Y17">
-        <v>50.6</v>
+        <v>49.1</v>
       </c>
       <c r="Z17">
-        <v>-61.8</v>
+        <v>-60.2</v>
       </c>
       <c r="AA17">
-        <v>45.3</v>
+        <v>43.9</v>
       </c>
       <c r="AB17">
-        <v>-50.5</v>
-      </c>
-      <c r="AD17">
-        <v>50.7</v>
-      </c>
-      <c r="AE17">
-        <v>-62.1</v>
-      </c>
-      <c r="AF17">
-        <v>45.3</v>
-      </c>
-      <c r="AG17">
-        <v>-50.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
+        <v>-48.9</v>
+      </c>
+      <c r="AM17">
+        <v>33.9</v>
+      </c>
+      <c r="AN17">
+        <v>-48.9</v>
+      </c>
+      <c r="AO17">
+        <v>33.9</v>
+      </c>
+      <c r="AP17">
+        <v>-48.9</v>
+      </c>
+      <c r="AQ17">
+        <v>39.6</v>
+      </c>
+      <c r="AR17">
+        <v>-82.4</v>
+      </c>
+      <c r="AS17">
+        <v>33.9</v>
+      </c>
+      <c r="AT17">
+        <v>-48.9</v>
+      </c>
+      <c r="AU17">
+        <v>50.9</v>
+      </c>
+      <c r="AV17">
+        <v>-124.8</v>
+      </c>
+      <c r="AW17">
+        <v>50.9</v>
+      </c>
+      <c r="AX17">
+        <v>-101.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50">
       <c r="A18">
         <v>40</v>
       </c>
@@ -1881,76 +1866,76 @@
         <v>23</v>
       </c>
       <c r="G18">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>53.6</v>
+        <v>51.1</v>
       </c>
       <c r="I18">
         <v>4</v>
       </c>
-      <c r="K18">
-        <v>36.4</v>
-      </c>
-      <c r="L18">
-        <v>-52.5</v>
-      </c>
-      <c r="M18">
-        <v>36.4</v>
-      </c>
-      <c r="N18">
-        <v>-52.5</v>
-      </c>
-      <c r="O18">
-        <v>42.5</v>
-      </c>
-      <c r="P18">
-        <v>-88.4</v>
-      </c>
-      <c r="Q18">
-        <v>36.4</v>
-      </c>
-      <c r="R18">
-        <v>-52.5</v>
-      </c>
-      <c r="S18">
-        <v>54.6</v>
-      </c>
       <c r="T18">
-        <v>-133.9</v>
+        <v>50.2</v>
       </c>
       <c r="U18">
-        <v>54.6</v>
+        <v>-61.1</v>
       </c>
       <c r="V18">
-        <v>-109.4</v>
+        <v>45</v>
+      </c>
+      <c r="W18">
+        <v>-50.1</v>
       </c>
       <c r="Y18">
-        <v>52.6</v>
+        <v>50.3</v>
       </c>
       <c r="Z18">
-        <v>-64.099999999999994</v>
+        <v>-61.6</v>
       </c>
       <c r="AA18">
-        <v>47.1</v>
+        <v>45</v>
       </c>
       <c r="AB18">
-        <v>-52.5</v>
-      </c>
-      <c r="AD18">
-        <v>52.7</v>
-      </c>
-      <c r="AE18">
-        <v>-64.599999999999994</v>
-      </c>
-      <c r="AF18">
-        <v>47.1</v>
-      </c>
-      <c r="AG18">
-        <v>-52.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
+        <v>-50.1</v>
+      </c>
+      <c r="AM18">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="AN18">
+        <v>-50.1</v>
+      </c>
+      <c r="AO18">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="AP18">
+        <v>-50.1</v>
+      </c>
+      <c r="AQ18">
+        <v>40.5</v>
+      </c>
+      <c r="AR18">
+        <v>-84.4</v>
+      </c>
+      <c r="AS18">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="AT18">
+        <v>-50.1</v>
+      </c>
+      <c r="AU18">
+        <v>52.1</v>
+      </c>
+      <c r="AV18">
+        <v>-127.7</v>
+      </c>
+      <c r="AW18">
+        <v>52.1</v>
+      </c>
+      <c r="AX18">
+        <v>-104.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50">
       <c r="A19">
         <v>40</v>
       </c>
@@ -1967,76 +1952,76 @@
         <v>23</v>
       </c>
       <c r="G19">
-        <v>50.36</v>
+        <v>47.68</v>
       </c>
       <c r="H19">
-        <v>53.6</v>
+        <v>53</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
-      <c r="K19">
-        <v>25.7</v>
-      </c>
-      <c r="L19">
-        <v>-36.5</v>
-      </c>
-      <c r="M19">
-        <v>25.7</v>
-      </c>
-      <c r="N19">
-        <v>-36.5</v>
-      </c>
-      <c r="O19">
-        <v>30.3</v>
-      </c>
-      <c r="P19">
-        <v>-119</v>
-      </c>
-      <c r="Q19">
-        <v>25.7</v>
-      </c>
-      <c r="R19">
-        <v>-67.8</v>
-      </c>
-      <c r="S19">
-        <v>35.5</v>
-      </c>
       <c r="T19">
-        <v>-156.69999999999999</v>
+        <v>51.2</v>
       </c>
       <c r="U19">
-        <v>35.5</v>
+        <v>-80</v>
       </c>
       <c r="V19">
-        <v>-185</v>
+        <v>46.7</v>
+      </c>
+      <c r="W19">
+        <v>-52</v>
       </c>
       <c r="Y19">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="Z19">
-        <v>-60.7</v>
+        <v>-60.1</v>
       </c>
       <c r="AA19">
-        <v>47.2</v>
+        <v>46.7</v>
       </c>
       <c r="AB19">
-        <v>-52.6</v>
-      </c>
-      <c r="AD19">
-        <v>51.8</v>
-      </c>
-      <c r="AE19">
-        <v>-60.8</v>
-      </c>
-      <c r="AF19">
-        <v>47.2</v>
-      </c>
-      <c r="AG19">
-        <v>-52.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
+        <v>-52</v>
+      </c>
+      <c r="AM19">
+        <v>25.4</v>
+      </c>
+      <c r="AN19">
+        <v>-36.1</v>
+      </c>
+      <c r="AO19">
+        <v>25.4</v>
+      </c>
+      <c r="AP19">
+        <v>-36.1</v>
+      </c>
+      <c r="AQ19">
+        <v>29.9</v>
+      </c>
+      <c r="AR19">
+        <v>-117.6</v>
+      </c>
+      <c r="AS19">
+        <v>25.4</v>
+      </c>
+      <c r="AT19">
+        <v>-67</v>
+      </c>
+      <c r="AU19">
+        <v>35.1</v>
+      </c>
+      <c r="AV19">
+        <v>-154.9</v>
+      </c>
+      <c r="AW19">
+        <v>35.1</v>
+      </c>
+      <c r="AX19">
+        <v>-182.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50">
       <c r="A20">
         <v>40</v>
       </c>
@@ -2053,76 +2038,76 @@
         <v>23</v>
       </c>
       <c r="G20">
-        <v>56.55</v>
+        <v>50.77</v>
       </c>
       <c r="H20">
-        <v>55</v>
+        <v>53.7</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
-      <c r="K20">
-        <v>37.4</v>
-      </c>
-      <c r="L20">
-        <v>-53.9</v>
-      </c>
-      <c r="M20">
-        <v>37.4</v>
-      </c>
-      <c r="N20">
-        <v>-53.9</v>
-      </c>
-      <c r="O20">
-        <v>43.6</v>
-      </c>
-      <c r="P20">
-        <v>-90.8</v>
-      </c>
-      <c r="Q20">
-        <v>37.4</v>
-      </c>
-      <c r="R20">
-        <v>-53.9</v>
-      </c>
-      <c r="S20">
-        <v>56.1</v>
-      </c>
       <c r="T20">
-        <v>-137.4</v>
+        <v>51.8</v>
       </c>
       <c r="U20">
-        <v>56.1</v>
+        <v>-60.6</v>
       </c>
       <c r="V20">
-        <v>-112.2</v>
+        <v>47.3</v>
+      </c>
+      <c r="W20">
+        <v>-52.7</v>
       </c>
       <c r="Y20">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="Z20">
-        <v>-62</v>
+        <v>-60.9</v>
       </c>
       <c r="AA20">
-        <v>48.4</v>
+        <v>47.3</v>
       </c>
       <c r="AB20">
-        <v>-53.9</v>
-      </c>
-      <c r="AD20">
-        <v>53.1</v>
-      </c>
-      <c r="AE20">
-        <v>-62.3</v>
-      </c>
-      <c r="AF20">
-        <v>48.4</v>
-      </c>
-      <c r="AG20">
-        <v>-53.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33">
+        <v>-52.7</v>
+      </c>
+      <c r="AM20">
+        <v>36.5</v>
+      </c>
+      <c r="AN20">
+        <v>-52.7</v>
+      </c>
+      <c r="AO20">
+        <v>36.5</v>
+      </c>
+      <c r="AP20">
+        <v>-52.7</v>
+      </c>
+      <c r="AQ20">
+        <v>42.6</v>
+      </c>
+      <c r="AR20">
+        <v>-88.7</v>
+      </c>
+      <c r="AS20">
+        <v>36.5</v>
+      </c>
+      <c r="AT20">
+        <v>-52.7</v>
+      </c>
+      <c r="AU20">
+        <v>54.8</v>
+      </c>
+      <c r="AV20">
+        <v>-134.30000000000001</v>
+      </c>
+      <c r="AW20">
+        <v>54.8</v>
+      </c>
+      <c r="AX20">
+        <v>-109.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50">
       <c r="A21">
         <v>40</v>
       </c>
@@ -2139,13 +2124,76 @@
         <v>23</v>
       </c>
       <c r="G21">
-        <v>65</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33">
+        <v>55</v>
+      </c>
+      <c r="H21" s="6">
+        <v>54.6</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="T21">
+        <v>52.6</v>
+      </c>
+      <c r="U21">
+        <v>-61.4</v>
+      </c>
+      <c r="V21">
+        <v>48.1</v>
+      </c>
+      <c r="W21">
+        <v>-53.5</v>
+      </c>
+      <c r="Y21">
+        <v>52.8</v>
+      </c>
+      <c r="Z21">
+        <v>-62</v>
+      </c>
+      <c r="AA21">
+        <v>48.1</v>
+      </c>
+      <c r="AB21">
+        <v>-53.5</v>
+      </c>
+      <c r="AM21">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AN21">
+        <v>-53.5</v>
+      </c>
+      <c r="AO21">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AP21">
+        <v>-53.5</v>
+      </c>
+      <c r="AQ21">
+        <v>43.3</v>
+      </c>
+      <c r="AR21">
+        <v>-90.2</v>
+      </c>
+      <c r="AS21">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AT21">
+        <v>-53.5</v>
+      </c>
+      <c r="AU21">
+        <v>55.7</v>
+      </c>
+      <c r="AV21">
+        <v>-136.6</v>
+      </c>
+      <c r="AW21">
+        <v>55.7</v>
+      </c>
+      <c r="AX21">
+        <v>-111.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50">
       <c r="A22">
         <v>40</v>
       </c>
@@ -2153,61 +2201,91 @@
         <v>60</v>
       </c>
       <c r="C22">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D22">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>60</v>
-      </c>
-      <c r="H22" s="6">
-        <v>55.6</v>
+        <v>17.68</v>
+      </c>
+      <c r="H22">
+        <v>43</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>37.799999999999997</v>
+        <v>20.7</v>
       </c>
       <c r="L22">
-        <v>-54.5</v>
+        <v>-50.8</v>
       </c>
       <c r="M22">
-        <v>37.799999999999997</v>
+        <v>20.7</v>
       </c>
       <c r="N22">
-        <v>-54.5</v>
+        <v>-59.7</v>
       </c>
       <c r="O22">
-        <v>44.1</v>
+        <v>20.7</v>
       </c>
       <c r="P22">
-        <v>-91.9</v>
+        <v>-69.2</v>
       </c>
       <c r="Q22">
-        <v>37.799999999999997</v>
+        <v>35</v>
       </c>
       <c r="R22">
-        <v>-54.5</v>
-      </c>
-      <c r="S22">
-        <v>56.8</v>
+        <v>-80.8</v>
       </c>
       <c r="T22">
-        <v>-139.1</v>
+        <v>43.3</v>
       </c>
       <c r="U22">
-        <v>56.8</v>
+        <v>-56.4</v>
       </c>
       <c r="V22">
-        <v>-113.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33">
+        <v>38.1</v>
+      </c>
+      <c r="W22">
+        <v>-42.3</v>
+      </c>
+      <c r="Y22">
+        <v>43.3</v>
+      </c>
+      <c r="Z22">
+        <v>-56.4</v>
+      </c>
+      <c r="AA22">
+        <v>37.9</v>
+      </c>
+      <c r="AB22">
+        <v>-42.2</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU22">
+        <v>35</v>
+      </c>
+      <c r="AV22">
+        <v>-80.8</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50">
       <c r="A23">
         <v>40</v>
       </c>
@@ -2218,16 +2296,70 @@
         <v>15</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
         <v>24</v>
       </c>
       <c r="G23">
-        <v>20.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33">
+        <v>20.77</v>
+      </c>
+      <c r="H23">
+        <v>44.5</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>21.4</v>
+      </c>
+      <c r="L23">
+        <v>-37.700000000000003</v>
+      </c>
+      <c r="M23">
+        <v>21.4</v>
+      </c>
+      <c r="N23">
+        <v>-43.6</v>
+      </c>
+      <c r="O23">
+        <v>21.4</v>
+      </c>
+      <c r="P23">
+        <v>-52.5</v>
+      </c>
+      <c r="Q23">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="R23">
+        <v>-67.900000000000006</v>
+      </c>
+      <c r="T23">
+        <v>44.8</v>
+      </c>
+      <c r="U23">
+        <v>-58.3</v>
+      </c>
+      <c r="V23">
+        <v>39.4</v>
+      </c>
+      <c r="W23">
+        <v>-43.8</v>
+      </c>
+      <c r="Y23">
+        <v>44.8</v>
+      </c>
+      <c r="Z23">
+        <v>-58.3</v>
+      </c>
+      <c r="AA23">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AB23">
+        <v>-43.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50">
       <c r="A24">
         <v>40</v>
       </c>
@@ -2238,13 +2370,70 @@
         <v>15</v>
       </c>
       <c r="D24">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:33">
+      <c r="G24">
+        <v>25</v>
+      </c>
+      <c r="H24">
+        <v>46.3</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>22.2</v>
+      </c>
+      <c r="L24">
+        <v>-49.6</v>
+      </c>
+      <c r="M24">
+        <v>22.2</v>
+      </c>
+      <c r="N24">
+        <v>-45.4</v>
+      </c>
+      <c r="O24">
+        <v>22.2</v>
+      </c>
+      <c r="P24">
+        <v>-54.6</v>
+      </c>
+      <c r="Q24">
+        <v>35.6</v>
+      </c>
+      <c r="R24">
+        <v>-96.9</v>
+      </c>
+      <c r="T24">
+        <v>46.6</v>
+      </c>
+      <c r="U24">
+        <v>-60.6</v>
+      </c>
+      <c r="V24">
+        <v>41</v>
+      </c>
+      <c r="W24">
+        <v>-45.5</v>
+      </c>
+      <c r="Y24">
+        <v>46.6</v>
+      </c>
+      <c r="Z24">
+        <v>-60.6</v>
+      </c>
+      <c r="AA24">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="AB24">
+        <v>-45.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50">
       <c r="A25">
         <v>40</v>
       </c>
@@ -2252,16 +2441,73 @@
         <v>60</v>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D25">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:33">
+      <c r="G25">
+        <v>32.68</v>
+      </c>
+      <c r="H25">
+        <v>49</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+      <c r="K25">
+        <v>23.5</v>
+      </c>
+      <c r="L25">
+        <v>-57.8</v>
+      </c>
+      <c r="M25">
+        <v>23.5</v>
+      </c>
+      <c r="N25">
+        <v>-87.2</v>
+      </c>
+      <c r="O25">
+        <v>23.5</v>
+      </c>
+      <c r="P25">
+        <v>-78.7</v>
+      </c>
+      <c r="Q25">
+        <v>39.9</v>
+      </c>
+      <c r="R25">
+        <v>-128.80000000000001</v>
+      </c>
+      <c r="T25">
+        <v>48.2</v>
+      </c>
+      <c r="U25">
+        <v>-59.1</v>
+      </c>
+      <c r="V25">
+        <v>43.1</v>
+      </c>
+      <c r="W25">
+        <v>-48</v>
+      </c>
+      <c r="Y25">
+        <v>48.2</v>
+      </c>
+      <c r="Z25">
+        <v>-59.1</v>
+      </c>
+      <c r="AA25">
+        <v>43.1</v>
+      </c>
+      <c r="AB25">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50">
       <c r="A26">
         <v>40</v>
       </c>
@@ -2272,13 +2518,70 @@
         <v>30</v>
       </c>
       <c r="D26">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:33">
+      <c r="G26">
+        <v>35.770000000000003</v>
+      </c>
+      <c r="H26">
+        <v>49.9</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <v>24</v>
+      </c>
+      <c r="L26">
+        <v>-42.3</v>
+      </c>
+      <c r="M26">
+        <v>24</v>
+      </c>
+      <c r="N26">
+        <v>-48.9</v>
+      </c>
+      <c r="O26">
+        <v>24</v>
+      </c>
+      <c r="P26">
+        <v>-58.9</v>
+      </c>
+      <c r="Q26">
+        <v>38.4</v>
+      </c>
+      <c r="R26">
+        <v>-76.2</v>
+      </c>
+      <c r="T26">
+        <v>49.1</v>
+      </c>
+      <c r="U26">
+        <v>-60.2</v>
+      </c>
+      <c r="V26">
+        <v>43.9</v>
+      </c>
+      <c r="W26">
+        <v>-48.9</v>
+      </c>
+      <c r="Y26">
+        <v>49.1</v>
+      </c>
+      <c r="Z26">
+        <v>-60.2</v>
+      </c>
+      <c r="AA26">
+        <v>43.9</v>
+      </c>
+      <c r="AB26">
+        <v>-48.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50">
       <c r="A27">
         <v>40</v>
       </c>
@@ -2289,13 +2592,70 @@
         <v>30</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:33">
+      <c r="G27">
+        <v>40</v>
+      </c>
+      <c r="H27">
+        <v>51.1</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <v>24.5</v>
+      </c>
+      <c r="L27">
+        <v>-54.8</v>
+      </c>
+      <c r="M27">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="N27">
+        <v>-107</v>
+      </c>
+      <c r="O27">
+        <v>24.5</v>
+      </c>
+      <c r="P27">
+        <v>-60.3</v>
+      </c>
+      <c r="Q27">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="R27">
+        <v>-107</v>
+      </c>
+      <c r="T27">
+        <v>50.3</v>
+      </c>
+      <c r="U27">
+        <v>-61.6</v>
+      </c>
+      <c r="V27">
+        <v>45</v>
+      </c>
+      <c r="W27">
+        <v>-50.1</v>
+      </c>
+      <c r="Y27">
+        <v>50.3</v>
+      </c>
+      <c r="Z27">
+        <v>-61.6</v>
+      </c>
+      <c r="AA27">
+        <v>45</v>
+      </c>
+      <c r="AB27">
+        <v>-50.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50">
       <c r="A28">
         <v>40</v>
       </c>
@@ -2303,16 +2663,73 @@
         <v>60</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D28">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:33">
+      <c r="G28">
+        <v>47.68</v>
+      </c>
+      <c r="H28">
+        <v>53</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="K28">
+        <v>25.4</v>
+      </c>
+      <c r="L28">
+        <v>-62.6</v>
+      </c>
+      <c r="M28">
+        <v>25.4</v>
+      </c>
+      <c r="N28">
+        <v>-94.5</v>
+      </c>
+      <c r="O28">
+        <v>25.4</v>
+      </c>
+      <c r="P28">
+        <v>-85.2</v>
+      </c>
+      <c r="Q28">
+        <v>43.2</v>
+      </c>
+      <c r="R28">
+        <v>-139.4</v>
+      </c>
+      <c r="T28">
+        <v>51.2</v>
+      </c>
+      <c r="U28">
+        <v>-60.1</v>
+      </c>
+      <c r="V28">
+        <v>46.7</v>
+      </c>
+      <c r="W28">
+        <v>-52</v>
+      </c>
+      <c r="Y28">
+        <v>51.2</v>
+      </c>
+      <c r="Z28">
+        <v>-60.1</v>
+      </c>
+      <c r="AA28">
+        <v>46.7</v>
+      </c>
+      <c r="AB28">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50">
       <c r="A29">
         <v>40</v>
       </c>
@@ -2323,13 +2740,70 @@
         <v>45</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="G29">
+        <v>50.77</v>
+      </c>
+      <c r="H29">
+        <v>53.7</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="K29">
+        <v>25.8</v>
+      </c>
+      <c r="L29">
+        <v>-45.5</v>
+      </c>
+      <c r="M29">
+        <v>25.8</v>
+      </c>
+      <c r="N29">
+        <v>-52.7</v>
+      </c>
+      <c r="O29">
+        <v>25.8</v>
+      </c>
+      <c r="P29">
+        <v>-63.4</v>
+      </c>
+      <c r="Q29">
+        <v>41.4</v>
+      </c>
+      <c r="R29">
+        <v>-82</v>
+      </c>
+      <c r="T29">
+        <v>51.9</v>
+      </c>
+      <c r="U29">
+        <v>-60.9</v>
+      </c>
+      <c r="V29">
+        <v>47.3</v>
+      </c>
+      <c r="W29">
+        <v>-52.7</v>
+      </c>
+      <c r="Y29">
+        <v>51.9</v>
+      </c>
+      <c r="Z29">
+        <v>-60.9</v>
+      </c>
+      <c r="AA29">
+        <v>47.3</v>
+      </c>
+      <c r="AB29">
+        <v>-52.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50">
       <c r="A30">
         <v>40</v>
       </c>
@@ -2340,208 +2814,318 @@
         <v>45</v>
       </c>
       <c r="D30">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:33">
-      <c r="A31">
-        <v>40</v>
-      </c>
-      <c r="B31">
-        <v>60</v>
-      </c>
-      <c r="C31">
+      <c r="G30">
+        <v>55</v>
+      </c>
+      <c r="H30">
+        <v>54.3</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="K30">
+        <v>26.2</v>
+      </c>
+      <c r="L30">
+        <v>-58.6</v>
+      </c>
+      <c r="M30">
+        <v>26.2</v>
+      </c>
+      <c r="N30">
+        <v>-53.5</v>
+      </c>
+      <c r="O30">
+        <v>26.2</v>
+      </c>
+      <c r="P30">
+        <v>-64.5</v>
+      </c>
+      <c r="Q30">
+        <v>42.1</v>
+      </c>
+      <c r="R30">
+        <v>-114.4</v>
+      </c>
+      <c r="T30">
+        <v>52.8</v>
+      </c>
+      <c r="U30">
+        <v>-62</v>
+      </c>
+      <c r="V30">
+        <v>48.1</v>
+      </c>
+      <c r="W30">
+        <v>-53.5</v>
+      </c>
+      <c r="Y30">
+        <v>52.8</v>
+      </c>
+      <c r="Z30">
+        <v>-62</v>
+      </c>
+      <c r="AA30">
+        <v>48.1</v>
+      </c>
+      <c r="AB30">
+        <v>-53.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50">
+      <c r="U32" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" t="s">
         <v>45</v>
       </c>
-      <c r="D31">
-        <v>45</v>
-      </c>
-      <c r="E31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:64">
+      <c r="H33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="U33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50">
       <c r="A34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="K34" t="s">
+        <v>5</v>
+      </c>
+      <c r="L34" t="s">
+        <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="N34" t="s">
+        <v>35</v>
+      </c>
+      <c r="O34" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>47</v>
+      </c>
+      <c r="R34" t="s">
+        <v>48</v>
+      </c>
+      <c r="T34" t="s">
+        <v>14</v>
+      </c>
+      <c r="U34" t="s">
+        <v>15</v>
+      </c>
+      <c r="V34" t="s">
+        <v>12</v>
+      </c>
+      <c r="W34" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>14</v>
       </c>
       <c r="Z34" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>21</v>
       </c>
       <c r="AE34" t="s">
-        <v>36</v>
+        <v>22</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>34</v>
       </c>
       <c r="AP34" t="s">
-        <v>37</v>
-      </c>
-      <c r="BG34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:64">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" t="s">
-        <v>46</v>
-      </c>
-      <c r="H35" t="s">
-        <v>41</v>
-      </c>
-      <c r="I35" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" t="s">
-        <v>6</v>
-      </c>
-      <c r="M35" t="s">
-        <v>34</v>
-      </c>
-      <c r="N35" t="s">
         <v>35</v>
       </c>
-      <c r="O35" t="s">
+      <c r="AQ34" t="s">
         <v>29</v>
       </c>
-      <c r="P35" t="s">
+      <c r="AR34" t="s">
         <v>30</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="AS34" t="s">
         <v>31</v>
       </c>
-      <c r="R35" t="s">
+      <c r="AT34" t="s">
         <v>32</v>
       </c>
-      <c r="S35" t="s">
+      <c r="AU34" t="s">
         <v>114</v>
       </c>
-      <c r="T35" t="s">
+      <c r="AV34" t="s">
         <v>115</v>
       </c>
-      <c r="U35" t="s">
+      <c r="AW34" t="s">
         <v>112</v>
       </c>
-      <c r="V35" t="s">
+      <c r="AX34" t="s">
         <v>113</v>
       </c>
-      <c r="Y35" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP35" t="s">
-        <v>30</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>31</v>
-      </c>
-      <c r="AR35" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU35" t="s">
-        <v>47</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>48</v>
-      </c>
-      <c r="BE35" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF35" t="s">
-        <v>22</v>
-      </c>
-      <c r="BG35" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH35" t="s">
-        <v>6</v>
-      </c>
-      <c r="BI35" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ35" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BK35" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:64">
+    </row>
+    <row r="35" spans="1:50">
+      <c r="A35">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>70</v>
+      </c>
+      <c r="C35">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>15</v>
+      </c>
+      <c r="H35">
+        <v>41.6</v>
+      </c>
+      <c r="T35">
+        <v>41.6</v>
+      </c>
+      <c r="U35">
+        <v>-53.2</v>
+      </c>
+      <c r="V35">
+        <v>36.6</v>
+      </c>
+      <c r="W35">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="Y35">
+        <v>41.6</v>
+      </c>
+      <c r="Z35">
+        <v>-53.2</v>
+      </c>
+      <c r="AA35">
+        <v>36.6</v>
+      </c>
+      <c r="AB35">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="AD35">
+        <v>15.8</v>
+      </c>
+      <c r="AE35">
+        <v>-25.3</v>
+      </c>
+      <c r="AF35">
+        <v>15.8</v>
+      </c>
+      <c r="AG35">
+        <v>-49</v>
+      </c>
+      <c r="AH35" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="AI35" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="AJ35">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AK35">
+        <v>-113.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:50">
       <c r="A36">
         <v>50</v>
       </c>
@@ -2549,7 +3133,7 @@
         <v>70</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2558,61 +3142,61 @@
         <v>20</v>
       </c>
       <c r="G36">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H36">
-        <v>41.6</v>
+        <v>48.1</v>
+      </c>
+      <c r="T36">
+        <v>46.9</v>
+      </c>
+      <c r="U36">
+        <v>-56.3</v>
+      </c>
+      <c r="V36">
+        <v>42.3</v>
+      </c>
+      <c r="W36">
+        <v>-47.1</v>
       </c>
       <c r="Y36">
-        <v>41.6</v>
+        <v>46.9</v>
       </c>
       <c r="Z36">
-        <v>-53.2</v>
+        <v>-56.3</v>
       </c>
       <c r="AA36">
-        <v>36.6</v>
+        <v>42.3</v>
       </c>
       <c r="AB36">
-        <v>-40.700000000000003</v>
-      </c>
-      <c r="AD36">
-        <v>41.6</v>
-      </c>
-      <c r="AE36">
-        <v>-53.2</v>
+        <v>-47.1</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>42</v>
       </c>
       <c r="AF36">
-        <v>36.6</v>
+        <v>18.3</v>
       </c>
       <c r="AG36">
-        <v>-40.700000000000003</v>
-      </c>
-      <c r="BE36">
-        <v>15.8</v>
-      </c>
-      <c r="BF36">
-        <v>-25.3</v>
-      </c>
-      <c r="BG36">
-        <v>15.8</v>
-      </c>
-      <c r="BH36">
-        <v>-49</v>
-      </c>
-      <c r="BI36" s="9">
-        <v>15.8</v>
-      </c>
-      <c r="BJ36" s="9">
-        <v>-65.7</v>
-      </c>
-      <c r="BK36">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="BL36">
-        <v>-113.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:64">
+        <v>-57.4</v>
+      </c>
+      <c r="AH36" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="AI36" s="9">
+        <v>-76</v>
+      </c>
+      <c r="AJ36">
+        <v>18.3</v>
+      </c>
+      <c r="AK36">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:50">
       <c r="A37">
         <v>50</v>
       </c>
@@ -2620,7 +3204,7 @@
         <v>70</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2629,61 +3213,61 @@
         <v>20</v>
       </c>
       <c r="G37">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H37">
-        <v>48.1</v>
+        <v>52.4</v>
+      </c>
+      <c r="T37">
+        <v>49.9</v>
+      </c>
+      <c r="U37">
+        <v>-57.6</v>
+      </c>
+      <c r="V37">
+        <v>46.1</v>
+      </c>
+      <c r="W37">
+        <v>-51.3</v>
       </c>
       <c r="Y37">
-        <v>46.9</v>
+        <v>49.9</v>
       </c>
       <c r="Z37">
-        <v>-56.3</v>
+        <v>-57.6</v>
       </c>
       <c r="AA37">
-        <v>42.3</v>
+        <v>46.1</v>
       </c>
       <c r="AB37">
-        <v>-47.1</v>
-      </c>
-      <c r="AD37">
-        <v>46.9</v>
-      </c>
-      <c r="AE37">
-        <v>-56.3</v>
-      </c>
-      <c r="AF37">
-        <v>42.3</v>
-      </c>
-      <c r="AG37">
-        <v>-47.1</v>
-      </c>
-      <c r="BE37" t="s">
+        <v>-51.3</v>
+      </c>
+      <c r="AD37" t="s">
         <v>42</v>
       </c>
-      <c r="BF37" t="s">
+      <c r="AE37" t="s">
         <v>42</v>
       </c>
-      <c r="BG37">
-        <v>18.3</v>
-      </c>
-      <c r="BH37">
-        <v>-57.4</v>
-      </c>
-      <c r="BI37" s="9">
-        <v>18.3</v>
-      </c>
-      <c r="BJ37" s="9">
-        <v>-76</v>
-      </c>
-      <c r="BK37">
-        <v>18.3</v>
-      </c>
-      <c r="BL37">
-        <v>-99.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:64">
+      <c r="AF37" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH37" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AI37" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="AJ37">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AK37">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50">
       <c r="A38">
         <v>50</v>
       </c>
@@ -2691,70 +3275,16 @@
         <v>70</v>
       </c>
       <c r="C38">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38">
-        <v>45</v>
-      </c>
-      <c r="H38">
-        <v>52.4</v>
-      </c>
-      <c r="Y38">
-        <v>49.9</v>
-      </c>
-      <c r="Z38">
-        <v>-57.6</v>
-      </c>
-      <c r="AA38">
-        <v>46.1</v>
-      </c>
-      <c r="AB38">
-        <v>-51.3</v>
-      </c>
-      <c r="AD38">
-        <v>49.9</v>
-      </c>
-      <c r="AE38">
-        <v>-57.6</v>
-      </c>
-      <c r="AF38">
-        <v>46.1</v>
-      </c>
-      <c r="AG38">
-        <v>-51.3</v>
-      </c>
-      <c r="BE38" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF38" t="s">
-        <v>42</v>
-      </c>
-      <c r="BG38" t="s">
-        <v>42</v>
-      </c>
-      <c r="BH38" t="s">
-        <v>42</v>
-      </c>
-      <c r="BI38" s="9">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="BJ38" s="9">
-        <v>-82.8</v>
-      </c>
-      <c r="BK38">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="BL38">
-        <v>-89.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:64">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50">
       <c r="A39">
         <v>50</v>
       </c>
@@ -2765,82 +3295,13 @@
         <v>15</v>
       </c>
       <c r="D39">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>23</v>
       </c>
-      <c r="G39">
-        <v>21.7</v>
-      </c>
-      <c r="H39">
-        <v>44.9</v>
-      </c>
-      <c r="I39">
-        <v>5</v>
-      </c>
-      <c r="K39">
-        <v>21.6</v>
-      </c>
-      <c r="L39">
-        <v>-30.5</v>
-      </c>
-      <c r="M39">
-        <v>21.6</v>
-      </c>
-      <c r="N39">
-        <v>-30.5</v>
-      </c>
-      <c r="O39">
-        <v>23.4</v>
-      </c>
-      <c r="P39">
-        <v>-88.9</v>
-      </c>
-      <c r="Q39">
-        <v>21.6</v>
-      </c>
-      <c r="R39">
-        <v>-53</v>
-      </c>
-      <c r="S39">
-        <v>27.8</v>
-      </c>
-      <c r="T39">
-        <v>-119.3</v>
-      </c>
-      <c r="U39">
-        <v>27.8</v>
-      </c>
-      <c r="V39">
-        <v>-139.80000000000001</v>
-      </c>
-      <c r="Y39">
-        <v>44.9</v>
-      </c>
-      <c r="Z39">
-        <v>57.2</v>
-      </c>
-      <c r="AA39">
-        <v>39.5</v>
-      </c>
-      <c r="AB39">
-        <v>-44</v>
-      </c>
-      <c r="AD39">
-        <v>44.9</v>
-      </c>
-      <c r="AE39">
-        <v>-57.2</v>
-      </c>
-      <c r="AF39">
-        <v>39.5</v>
-      </c>
-      <c r="AG39">
-        <v>-44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:64">
+    </row>
+    <row r="40" spans="1:50">
       <c r="A40">
         <v>50</v>
       </c>
@@ -2851,82 +3312,13 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
         <v>23</v>
       </c>
-      <c r="G40">
-        <v>29.43</v>
-      </c>
-      <c r="H40">
-        <v>47.9</v>
-      </c>
-      <c r="I40">
-        <v>5</v>
-      </c>
-      <c r="K40">
-        <v>32.6</v>
-      </c>
-      <c r="L40">
-        <v>-46.9</v>
-      </c>
-      <c r="M40">
-        <v>32.6</v>
-      </c>
-      <c r="N40">
-        <v>-46.9</v>
-      </c>
-      <c r="O40">
-        <v>35</v>
-      </c>
-      <c r="P40">
-        <v>-72.8</v>
-      </c>
-      <c r="Q40">
-        <v>32.6</v>
-      </c>
-      <c r="R40">
-        <v>-46.9</v>
-      </c>
-      <c r="S40">
-        <v>45.3</v>
-      </c>
-      <c r="T40">
-        <v>-110.8</v>
-      </c>
-      <c r="U40">
-        <v>45.3</v>
-      </c>
-      <c r="V40">
-        <v>-90.8</v>
-      </c>
-      <c r="Y40">
-        <v>47.8</v>
-      </c>
-      <c r="Z40">
-        <v>-60.6</v>
-      </c>
-      <c r="AA40">
-        <v>42.2</v>
-      </c>
-      <c r="AB40">
-        <v>-46.9</v>
-      </c>
-      <c r="AD40">
-        <v>47.9</v>
-      </c>
-      <c r="AE40">
-        <v>-61.3</v>
-      </c>
-      <c r="AF40">
-        <v>42.2</v>
-      </c>
-      <c r="AG40">
-        <v>-46.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:64">
+    </row>
+    <row r="41" spans="1:50">
       <c r="A41">
         <v>50</v>
       </c>
@@ -2934,85 +3326,16 @@
         <v>70</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D41">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
       </c>
-      <c r="G41">
-        <v>40</v>
-      </c>
-      <c r="H41">
-        <v>51.1</v>
-      </c>
-      <c r="I41">
-        <v>5</v>
-      </c>
-      <c r="K41">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="L41">
-        <v>-50.1</v>
-      </c>
-      <c r="M41">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="N41">
-        <v>-50.1</v>
-      </c>
-      <c r="O41">
-        <v>37.299999999999997</v>
-      </c>
-      <c r="P41">
-        <v>-77.7</v>
-      </c>
-      <c r="Q41">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="R41">
-        <v>-50.1</v>
-      </c>
-      <c r="S41">
-        <v>48.4</v>
-      </c>
-      <c r="T41">
-        <v>-118.2</v>
-      </c>
-      <c r="U41">
-        <v>48.4</v>
-      </c>
-      <c r="V41">
-        <v>-96.9</v>
-      </c>
-      <c r="Y41">
-        <v>50.8</v>
-      </c>
-      <c r="Z41">
-        <v>-64.099999999999994</v>
-      </c>
-      <c r="AA41">
-        <v>45</v>
-      </c>
-      <c r="AB41">
-        <v>-50.1</v>
-      </c>
-      <c r="AD41">
-        <v>51.1</v>
-      </c>
-      <c r="AE41">
-        <v>-65.400000000000006</v>
-      </c>
-      <c r="AF41">
-        <v>45</v>
-      </c>
-      <c r="AG41">
-        <v>-50.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:64">
+    </row>
+    <row r="42" spans="1:50">
       <c r="A42">
         <v>50</v>
       </c>
@@ -3023,82 +3346,13 @@
         <v>30</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
       </c>
-      <c r="G42">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="H42">
-        <v>50.2</v>
-      </c>
-      <c r="I42">
-        <v>5</v>
-      </c>
-      <c r="K42">
-        <v>24.1</v>
-      </c>
-      <c r="L42">
-        <v>-34.1</v>
-      </c>
-      <c r="M42">
-        <v>24.1</v>
-      </c>
-      <c r="N42">
-        <v>-34.1</v>
-      </c>
-      <c r="O42">
-        <v>26.1</v>
-      </c>
-      <c r="P42">
-        <v>-99.3</v>
-      </c>
-      <c r="Q42">
-        <v>24.1</v>
-      </c>
-      <c r="R42">
-        <v>-59.2</v>
-      </c>
-      <c r="S42">
-        <v>31</v>
-      </c>
-      <c r="T42">
-        <v>-133.19999999999999</v>
-      </c>
-      <c r="U42">
-        <v>31</v>
-      </c>
-      <c r="V42">
-        <v>-156.1</v>
-      </c>
-      <c r="Y42">
-        <v>48.9</v>
-      </c>
-      <c r="Z42">
-        <v>-58.5</v>
-      </c>
-      <c r="AA42">
-        <v>44.2</v>
-      </c>
-      <c r="AB42">
-        <v>-49.2</v>
-      </c>
-      <c r="AD42">
-        <v>48.9</v>
-      </c>
-      <c r="AE42">
-        <v>-58.7</v>
-      </c>
-      <c r="AF42">
-        <v>44.2</v>
-      </c>
-      <c r="AG42">
-        <v>-49.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:64">
+    </row>
+    <row r="43" spans="1:50">
       <c r="A43">
         <v>50</v>
       </c>
@@ -3109,82 +3363,13 @@
         <v>30</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
       </c>
-      <c r="G43">
-        <v>44.43</v>
-      </c>
-      <c r="H43">
-        <v>52.2</v>
-      </c>
-      <c r="I43">
-        <v>5</v>
-      </c>
-      <c r="K43">
-        <v>35.5</v>
-      </c>
-      <c r="L43">
-        <v>-51.2</v>
-      </c>
-      <c r="M43">
-        <v>35.5</v>
-      </c>
-      <c r="N43">
-        <v>-51.2</v>
-      </c>
-      <c r="O43">
-        <v>38.1</v>
-      </c>
-      <c r="P43">
-        <v>-79.400000000000006</v>
-      </c>
-      <c r="Q43">
-        <v>35.5</v>
-      </c>
-      <c r="R43">
-        <v>-51.2</v>
-      </c>
-      <c r="S43">
-        <v>49.5</v>
-      </c>
-      <c r="T43">
-        <v>-120.8</v>
-      </c>
-      <c r="U43">
-        <v>49.5</v>
-      </c>
-      <c r="V43">
-        <v>-99.1</v>
-      </c>
-      <c r="Y43">
-        <v>50.8</v>
-      </c>
-      <c r="Z43">
-        <v>-60.7</v>
-      </c>
-      <c r="AA43">
-        <v>46</v>
-      </c>
-      <c r="AB43">
-        <v>-51.2</v>
-      </c>
-      <c r="AD43">
-        <v>50.9</v>
-      </c>
-      <c r="AE43">
-        <v>-61.1</v>
-      </c>
-      <c r="AF43">
-        <v>46</v>
-      </c>
-      <c r="AG43">
-        <v>-51.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:64">
+    </row>
+    <row r="44" spans="1:50">
       <c r="A44">
         <v>50</v>
       </c>
@@ -3192,85 +3377,16 @@
         <v>70</v>
       </c>
       <c r="C44">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D44">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
       </c>
-      <c r="G44">
-        <v>55</v>
-      </c>
-      <c r="H44">
-        <v>54.6</v>
-      </c>
-      <c r="I44">
-        <v>5</v>
-      </c>
-      <c r="K44">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="L44">
-        <v>-53.5</v>
-      </c>
-      <c r="M44">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="N44">
-        <v>-53.5</v>
-      </c>
-      <c r="O44">
-        <v>39.9</v>
-      </c>
-      <c r="P44">
-        <v>-83</v>
-      </c>
-      <c r="Q44">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="R44">
-        <v>-53.5</v>
-      </c>
-      <c r="S44">
-        <v>51.7</v>
-      </c>
-      <c r="T44">
-        <v>-126.4</v>
-      </c>
-      <c r="U44">
-        <v>51.7</v>
-      </c>
-      <c r="V44">
-        <v>-103.6</v>
-      </c>
-      <c r="Y44">
-        <v>53.1</v>
-      </c>
-      <c r="Z44">
-        <v>-63.1</v>
-      </c>
-      <c r="AA44">
-        <v>48.1</v>
-      </c>
-      <c r="AB44">
-        <v>-53.5</v>
-      </c>
-      <c r="AD44">
-        <v>53.3</v>
-      </c>
-      <c r="AE44">
-        <v>-63.9</v>
-      </c>
-      <c r="AF44">
-        <v>48.1</v>
-      </c>
-      <c r="AG44">
-        <v>-53.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:64">
+    </row>
+    <row r="45" spans="1:50">
       <c r="A45">
         <v>50</v>
       </c>
@@ -3281,82 +3397,13 @@
         <v>45</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
-      <c r="G45">
-        <v>51.7</v>
-      </c>
-      <c r="H45">
-        <v>53.9</v>
-      </c>
-      <c r="I45">
-        <v>5</v>
-      </c>
-      <c r="K45">
-        <v>25.9</v>
-      </c>
-      <c r="L45">
-        <v>-36.700000000000003</v>
-      </c>
-      <c r="M45">
-        <v>25.9</v>
-      </c>
-      <c r="N45">
-        <v>-36.700000000000003</v>
-      </c>
-      <c r="O45">
-        <v>28</v>
-      </c>
-      <c r="P45">
-        <v>-106.8</v>
-      </c>
-      <c r="Q45">
-        <v>25.9</v>
-      </c>
-      <c r="R45">
-        <v>-63.6</v>
-      </c>
-      <c r="S45">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="T45">
-        <v>143.19999999999999</v>
-      </c>
-      <c r="U45">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="V45">
-        <v>-167.8</v>
-      </c>
-      <c r="Y45">
-        <v>51.4</v>
-      </c>
-      <c r="Z45">
-        <v>-59.2</v>
-      </c>
-      <c r="AA45">
-        <v>47.5</v>
-      </c>
-      <c r="AB45">
-        <v>-52.9</v>
-      </c>
-      <c r="AD45">
-        <v>51.4</v>
-      </c>
-      <c r="AE45">
-        <v>-59.3</v>
-      </c>
-      <c r="AF45">
-        <v>47.5</v>
-      </c>
-      <c r="AG45">
-        <v>-52.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:64">
+    </row>
+    <row r="46" spans="1:50">
       <c r="A46">
         <v>50</v>
       </c>
@@ -3367,82 +3414,14 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
       </c>
-      <c r="G46">
-        <v>59.43</v>
-      </c>
-      <c r="H46">
-        <v>55.5</v>
-      </c>
-      <c r="I46">
-        <v>5</v>
-      </c>
-      <c r="K46">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="L46">
-        <v>-54.4</v>
-      </c>
-      <c r="M46">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="N46">
-        <v>-54.4</v>
-      </c>
-      <c r="O46">
-        <v>40.5</v>
-      </c>
-      <c r="P46">
-        <v>-84.4</v>
-      </c>
-      <c r="Q46">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="R46">
-        <v>-54.4</v>
-      </c>
-      <c r="S46">
-        <v>52.6</v>
-      </c>
-      <c r="T46">
-        <v>-128.5</v>
-      </c>
-      <c r="U46">
-        <v>52.6</v>
-      </c>
-      <c r="V46">
-        <v>-105.3</v>
-      </c>
-      <c r="Y46">
-        <v>52.8</v>
-      </c>
-      <c r="Z46">
-        <v>-60.9</v>
-      </c>
-      <c r="AA46">
-        <v>48.9</v>
-      </c>
-      <c r="AB46">
-        <v>-54.4</v>
-      </c>
-      <c r="AD46">
-        <v>52.9</v>
-      </c>
-      <c r="AE46">
-        <v>-61</v>
-      </c>
-      <c r="AF46">
-        <v>48.9</v>
-      </c>
-      <c r="AG46">
-        <v>-54.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:64">
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="1:50">
       <c r="A47">
         <v>50</v>
       </c>
@@ -3450,22 +3429,73 @@
         <v>70</v>
       </c>
       <c r="C47">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G47">
-        <v>70</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:64">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="H47">
+        <v>43.4</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="K47">
+        <v>20.8</v>
+      </c>
+      <c r="L47">
+        <v>-51.2</v>
+      </c>
+      <c r="M47">
+        <v>20.8</v>
+      </c>
+      <c r="N47">
+        <v>-55.5</v>
+      </c>
+      <c r="O47">
+        <v>20.8</v>
+      </c>
+      <c r="P47">
+        <v>-64.2</v>
+      </c>
+      <c r="Q47">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="R47">
+        <v>-76.8</v>
+      </c>
+      <c r="T47">
+        <v>43.4</v>
+      </c>
+      <c r="U47">
+        <v>-55.5</v>
+      </c>
+      <c r="V47">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="W47">
+        <v>-42.5</v>
+      </c>
+      <c r="Y47">
+        <v>43.4</v>
+      </c>
+      <c r="Z47">
+        <v>-55.5</v>
+      </c>
+      <c r="AA47">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AB47">
+        <v>-42.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:50">
       <c r="A48">
         <v>50</v>
       </c>
@@ -3476,13 +3506,70 @@
         <v>15</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:64">
+      <c r="G48">
+        <v>22.22</v>
+      </c>
+      <c r="H48">
+        <v>45.1</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="K48">
+        <v>21.7</v>
+      </c>
+      <c r="L48">
+        <v>-33.4</v>
+      </c>
+      <c r="M48">
+        <v>21.7</v>
+      </c>
+      <c r="N48">
+        <v>-44.2</v>
+      </c>
+      <c r="O48">
+        <v>21.7</v>
+      </c>
+      <c r="P48">
+        <v>-53.3</v>
+      </c>
+      <c r="Q48">
+        <v>31.8</v>
+      </c>
+      <c r="R48">
+        <v>-62.6</v>
+      </c>
+      <c r="T48">
+        <v>45.1</v>
+      </c>
+      <c r="U48">
+        <v>-57.8</v>
+      </c>
+      <c r="V48">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="W48">
+        <v>-44.2</v>
+      </c>
+      <c r="Y48">
+        <v>45.1</v>
+      </c>
+      <c r="Z48">
+        <v>-57.8</v>
+      </c>
+      <c r="AA48">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="AB48">
+        <v>-44.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:50">
       <c r="A49">
         <v>50</v>
       </c>
@@ -3493,13 +3580,70 @@
         <v>15</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:64">
+      <c r="G49">
+        <v>27.5</v>
+      </c>
+      <c r="H49">
+        <v>47.2</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="K49">
+        <v>22.7</v>
+      </c>
+      <c r="L49">
+        <v>-44.8</v>
+      </c>
+      <c r="M49">
+        <v>22.7</v>
+      </c>
+      <c r="N49">
+        <v>-46.3</v>
+      </c>
+      <c r="O49">
+        <v>22.7</v>
+      </c>
+      <c r="P49">
+        <v>-55.7</v>
+      </c>
+      <c r="Q49">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="R49">
+        <v>-81.400000000000006</v>
+      </c>
+      <c r="T49">
+        <v>47.2</v>
+      </c>
+      <c r="U49">
+        <v>-60.4</v>
+      </c>
+      <c r="V49">
+        <v>41.6</v>
+      </c>
+      <c r="W49">
+        <v>-46.3</v>
+      </c>
+      <c r="Y49">
+        <v>47.2</v>
+      </c>
+      <c r="Z49">
+        <v>-60.4</v>
+      </c>
+      <c r="AA49">
+        <v>41.6</v>
+      </c>
+      <c r="AB49">
+        <v>-46.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:50">
       <c r="A50">
         <v>50</v>
       </c>
@@ -3507,16 +3651,73 @@
         <v>70</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D50">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="51" spans="1:64">
+      <c r="G50">
+        <v>33.35</v>
+      </c>
+      <c r="H50">
+        <v>49.2</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="K50">
+        <v>23.6</v>
+      </c>
+      <c r="L50">
+        <v>-58</v>
+      </c>
+      <c r="M50">
+        <v>23.6</v>
+      </c>
+      <c r="N50">
+        <v>-71.2</v>
+      </c>
+      <c r="O50">
+        <v>23.6</v>
+      </c>
+      <c r="P50">
+        <v>-72.8</v>
+      </c>
+      <c r="Q50">
+        <v>36.5</v>
+      </c>
+      <c r="R50">
+        <v>-106.1</v>
+      </c>
+      <c r="T50">
+        <v>47.9</v>
+      </c>
+      <c r="U50">
+        <v>-57.5</v>
+      </c>
+      <c r="V50">
+        <v>43.3</v>
+      </c>
+      <c r="W50">
+        <v>-48.2</v>
+      </c>
+      <c r="Y50">
+        <v>47.9</v>
+      </c>
+      <c r="Z50">
+        <v>-57.5</v>
+      </c>
+      <c r="AA50">
+        <v>43.3</v>
+      </c>
+      <c r="AB50">
+        <v>-48.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:50">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3527,13 +3728,70 @@
         <v>30</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E51" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="52" spans="1:64">
+      <c r="G51">
+        <v>37.22</v>
+      </c>
+      <c r="H51">
+        <v>50.3</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="K51">
+        <v>24.2</v>
+      </c>
+      <c r="L51">
+        <v>-37.200000000000003</v>
+      </c>
+      <c r="M51">
+        <v>24.2</v>
+      </c>
+      <c r="N51">
+        <v>-49.3</v>
+      </c>
+      <c r="O51">
+        <v>24.2</v>
+      </c>
+      <c r="P51">
+        <v>-59.4</v>
+      </c>
+      <c r="Q51">
+        <v>35.5</v>
+      </c>
+      <c r="R51">
+        <v>-69.8</v>
+      </c>
+      <c r="T51">
+        <v>49.1</v>
+      </c>
+      <c r="U51">
+        <v>-58.9</v>
+      </c>
+      <c r="V51">
+        <v>44.3</v>
+      </c>
+      <c r="W51">
+        <v>-49.3</v>
+      </c>
+      <c r="Y51">
+        <v>49.1</v>
+      </c>
+      <c r="Z51">
+        <v>-58.9</v>
+      </c>
+      <c r="AA51">
+        <v>44.3</v>
+      </c>
+      <c r="AB51">
+        <v>-49.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:50">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3544,13 +3802,70 @@
         <v>30</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:64">
+      <c r="G52">
+        <v>42.5</v>
+      </c>
+      <c r="H52">
+        <v>51.8</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="K52">
+        <v>24.8</v>
+      </c>
+      <c r="L52">
+        <v>-49.1</v>
+      </c>
+      <c r="M52">
+        <v>24.8</v>
+      </c>
+      <c r="N52">
+        <v>-50.7</v>
+      </c>
+      <c r="O52">
+        <v>24.8</v>
+      </c>
+      <c r="P52">
+        <v>-61.1</v>
+      </c>
+      <c r="Q52">
+        <v>36.5</v>
+      </c>
+      <c r="R52">
+        <v>-89.2</v>
+      </c>
+      <c r="T52">
+        <v>50.5</v>
+      </c>
+      <c r="U52">
+        <v>-60.5</v>
+      </c>
+      <c r="V52">
+        <v>45.5</v>
+      </c>
+      <c r="W52">
+        <v>-50.7</v>
+      </c>
+      <c r="Y52">
+        <v>50.5</v>
+      </c>
+      <c r="Z52">
+        <v>-60.5</v>
+      </c>
+      <c r="AA52">
+        <v>45.5</v>
+      </c>
+      <c r="AB52">
+        <v>-50.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:50">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3558,16 +3873,73 @@
         <v>70</v>
       </c>
       <c r="C53">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D53">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:64">
+      <c r="G53">
+        <v>48.35</v>
+      </c>
+      <c r="H53">
+        <v>53.2</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="K53">
+        <v>25.5</v>
+      </c>
+      <c r="L53">
+        <v>-62.7</v>
+      </c>
+      <c r="M53">
+        <v>25.5</v>
+      </c>
+      <c r="N53">
+        <v>-84</v>
+      </c>
+      <c r="O53">
+        <v>25.5</v>
+      </c>
+      <c r="P53">
+        <v>-78.7</v>
+      </c>
+      <c r="Q53">
+        <v>39.4</v>
+      </c>
+      <c r="R53">
+        <v>-131</v>
+      </c>
+      <c r="T53">
+        <v>50.7</v>
+      </c>
+      <c r="U53">
+        <v>-58.4</v>
+      </c>
+      <c r="V53">
+        <v>46.8</v>
+      </c>
+      <c r="W53">
+        <v>-52.1</v>
+      </c>
+      <c r="Y53">
+        <v>50.7</v>
+      </c>
+      <c r="Z53">
+        <v>-58.4</v>
+      </c>
+      <c r="AA53">
+        <v>46.8</v>
+      </c>
+      <c r="AB53">
+        <v>-52.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:50">
       <c r="A54">
         <v>50</v>
       </c>
@@ -3578,13 +3950,70 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:64">
+      <c r="G54">
+        <v>52.22</v>
+      </c>
+      <c r="H54">
+        <v>54</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="K54">
+        <v>25.9</v>
+      </c>
+      <c r="L54">
+        <v>-39.9</v>
+      </c>
+      <c r="M54">
+        <v>25.9</v>
+      </c>
+      <c r="N54">
+        <v>-53</v>
+      </c>
+      <c r="O54">
+        <v>25.9</v>
+      </c>
+      <c r="P54">
+        <v>-63.8</v>
+      </c>
+      <c r="Q54">
+        <v>38.1</v>
+      </c>
+      <c r="R54">
+        <v>-74.900000000000006</v>
+      </c>
+      <c r="T54">
+        <v>51.5</v>
+      </c>
+      <c r="U54">
+        <v>-59.4</v>
+      </c>
+      <c r="V54">
+        <v>47.6</v>
+      </c>
+      <c r="W54">
+        <v>-53</v>
+      </c>
+      <c r="Y54">
+        <v>51.5</v>
+      </c>
+      <c r="Z54">
+        <v>-59.4</v>
+      </c>
+      <c r="AA54">
+        <v>47.6</v>
+      </c>
+      <c r="AB54">
+        <v>-59.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:50">
       <c r="A55">
         <v>50</v>
       </c>
@@ -3595,208 +4024,318 @@
         <v>45</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="56" spans="1:64">
-      <c r="A56">
-        <v>50</v>
-      </c>
-      <c r="B56">
-        <v>70</v>
-      </c>
-      <c r="C56">
+      <c r="G55">
+        <v>57.5</v>
+      </c>
+      <c r="H55">
+        <v>55.2</v>
+      </c>
+      <c r="I55">
+        <v>5</v>
+      </c>
+      <c r="K55">
+        <v>26.5</v>
+      </c>
+      <c r="L55">
+        <v>-52.4</v>
+      </c>
+      <c r="M55">
+        <v>26.5</v>
+      </c>
+      <c r="N55">
+        <v>-54</v>
+      </c>
+      <c r="O55">
+        <v>26.5</v>
+      </c>
+      <c r="P55">
+        <v>-65.099999999999994</v>
+      </c>
+      <c r="Q55">
+        <v>38.9</v>
+      </c>
+      <c r="R55">
+        <v>-95.1</v>
+      </c>
+      <c r="T55">
+        <v>52.6</v>
+      </c>
+      <c r="U55">
+        <v>-60.6</v>
+      </c>
+      <c r="V55">
+        <v>48.5</v>
+      </c>
+      <c r="W55">
+        <v>-54</v>
+      </c>
+      <c r="Y55">
+        <v>52.6</v>
+      </c>
+      <c r="Z55">
+        <v>-60.6</v>
+      </c>
+      <c r="AA55">
+        <v>48.5</v>
+      </c>
+      <c r="AB55">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:50">
+      <c r="U57" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:50">
+      <c r="A58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" t="s">
         <v>45</v>
       </c>
-      <c r="D56">
-        <v>45</v>
-      </c>
-      <c r="E56" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:64">
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" t="s">
+        <v>19</v>
+      </c>
+      <c r="U58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:50">
       <c r="A59" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H59" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="K59" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" t="s">
+        <v>6</v>
       </c>
       <c r="M59" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="N59" t="s">
+        <v>35</v>
+      </c>
+      <c r="O59" t="s">
+        <v>31</v>
+      </c>
+      <c r="P59" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>47</v>
+      </c>
+      <c r="R59" t="s">
+        <v>48</v>
+      </c>
+      <c r="T59" t="s">
+        <v>14</v>
+      </c>
+      <c r="U59" t="s">
+        <v>15</v>
+      </c>
+      <c r="V59" t="s">
+        <v>12</v>
+      </c>
+      <c r="W59" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>14</v>
       </c>
       <c r="Z59" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>21</v>
       </c>
       <c r="AE59" t="s">
-        <v>36</v>
+        <v>22</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH59" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI59" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO59" t="s">
+        <v>34</v>
       </c>
       <c r="AP59" t="s">
-        <v>37</v>
-      </c>
-      <c r="BG59" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:64">
-      <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" t="s">
-        <v>43</v>
-      </c>
-      <c r="G60" t="s">
-        <v>46</v>
-      </c>
-      <c r="H60" t="s">
-        <v>41</v>
-      </c>
-      <c r="I60" t="s">
-        <v>18</v>
-      </c>
-      <c r="K60" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" t="s">
-        <v>6</v>
-      </c>
-      <c r="M60" t="s">
-        <v>34</v>
-      </c>
-      <c r="N60" t="s">
         <v>35</v>
       </c>
-      <c r="O60" t="s">
+      <c r="AQ59" t="s">
         <v>29</v>
       </c>
-      <c r="P60" t="s">
+      <c r="AR59" t="s">
         <v>30</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="AS59" t="s">
         <v>31</v>
       </c>
-      <c r="R60" t="s">
+      <c r="AT59" t="s">
         <v>32</v>
       </c>
-      <c r="S60" t="s">
+      <c r="AU59" t="s">
         <v>114</v>
       </c>
-      <c r="T60" t="s">
+      <c r="AV59" t="s">
         <v>115</v>
       </c>
-      <c r="U60" t="s">
+      <c r="AW59" t="s">
         <v>112</v>
       </c>
-      <c r="V60" t="s">
+      <c r="AX59" t="s">
         <v>113</v>
       </c>
-      <c r="Y60" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA60" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB60" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE60" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN60" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO60" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP60" t="s">
-        <v>30</v>
-      </c>
-      <c r="AQ60" t="s">
-        <v>31</v>
-      </c>
-      <c r="AR60" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT60" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU60" t="s">
-        <v>47</v>
-      </c>
-      <c r="AV60" t="s">
-        <v>48</v>
-      </c>
-      <c r="BE60" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF60" t="s">
-        <v>22</v>
-      </c>
-      <c r="BG60" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH60" t="s">
-        <v>6</v>
-      </c>
-      <c r="BI60" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="BJ60" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BK60" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:64">
+    </row>
+    <row r="60" spans="1:50">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60">
+        <v>80</v>
+      </c>
+      <c r="C60">
+        <v>15</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60">
+        <v>15</v>
+      </c>
+      <c r="H60">
+        <v>41.6</v>
+      </c>
+      <c r="T60">
+        <v>41.3</v>
+      </c>
+      <c r="U60">
+        <v>-52</v>
+      </c>
+      <c r="V60">
+        <v>36.6</v>
+      </c>
+      <c r="W60">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="Y60">
+        <v>41.3</v>
+      </c>
+      <c r="Z60">
+        <v>-52</v>
+      </c>
+      <c r="AA60">
+        <v>36.6</v>
+      </c>
+      <c r="AB60">
+        <v>-52</v>
+      </c>
+      <c r="AD60">
+        <v>15.8</v>
+      </c>
+      <c r="AE60">
+        <v>-24.1</v>
+      </c>
+      <c r="AF60">
+        <v>15.8</v>
+      </c>
+      <c r="AG60">
+        <v>-49</v>
+      </c>
+      <c r="AH60" s="9">
+        <v>15.8</v>
+      </c>
+      <c r="AI60" s="9">
+        <v>-65.7</v>
+      </c>
+      <c r="AJ60">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AK60">
+        <v>-113.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:50">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3804,7 +4343,7 @@
         <v>80</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3813,61 +4352,61 @@
         <v>20</v>
       </c>
       <c r="G61">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H61">
-        <v>41.6</v>
+        <v>48.1</v>
+      </c>
+      <c r="T61">
+        <v>46.5</v>
+      </c>
+      <c r="U61">
+        <v>-54.5</v>
+      </c>
+      <c r="V61">
+        <v>42.3</v>
+      </c>
+      <c r="W61">
+        <v>-47.1</v>
       </c>
       <c r="Y61">
-        <v>41.3</v>
+        <v>46.5</v>
       </c>
       <c r="Z61">
-        <v>-52</v>
+        <v>-54.5</v>
       </c>
       <c r="AA61">
-        <v>36.6</v>
+        <v>42.3</v>
       </c>
       <c r="AB61">
-        <v>-40.700000000000003</v>
-      </c>
-      <c r="AD61">
-        <v>41.3</v>
-      </c>
-      <c r="AE61">
-        <v>-52</v>
+        <v>-47.1</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>42</v>
       </c>
       <c r="AF61">
-        <v>36.6</v>
+        <v>18.3</v>
       </c>
       <c r="AG61">
-        <v>-52</v>
-      </c>
-      <c r="BE61">
-        <v>15.8</v>
-      </c>
-      <c r="BF61">
-        <v>-24.1</v>
-      </c>
-      <c r="BG61">
-        <v>15.8</v>
-      </c>
-      <c r="BH61">
-        <v>-49</v>
-      </c>
-      <c r="BI61" s="9">
-        <v>15.8</v>
-      </c>
-      <c r="BJ61" s="9">
-        <v>-65.7</v>
-      </c>
-      <c r="BK61">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="BL61">
-        <v>-113.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:64">
+        <v>-56.7</v>
+      </c>
+      <c r="AH61" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="AI61" s="9">
+        <v>-76</v>
+      </c>
+      <c r="AJ61">
+        <v>18.3</v>
+      </c>
+      <c r="AK61">
+        <v>-99.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:50">
       <c r="A62">
         <v>60</v>
       </c>
@@ -3875,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="C62">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3884,61 +4423,61 @@
         <v>20</v>
       </c>
       <c r="G62">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H62">
-        <v>48.1</v>
+        <v>52.4</v>
+      </c>
+      <c r="T62">
+        <v>49.3</v>
+      </c>
+      <c r="U62">
+        <v>-56.5</v>
+      </c>
+      <c r="V62">
+        <v>46.1</v>
+      </c>
+      <c r="W62">
+        <v>-51.3</v>
       </c>
       <c r="Y62">
-        <v>46.5</v>
+        <v>49.3</v>
       </c>
       <c r="Z62">
-        <v>-54.5</v>
+        <v>-56.5</v>
       </c>
       <c r="AA62">
-        <v>42.3</v>
+        <v>46.1</v>
       </c>
       <c r="AB62">
-        <v>-47.1</v>
-      </c>
-      <c r="AD62">
-        <v>46.5</v>
-      </c>
-      <c r="AE62">
-        <v>-54.5</v>
+        <v>-51.3</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>42</v>
       </c>
       <c r="AF62">
-        <v>42.3</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="AG62">
-        <v>-47.1</v>
-      </c>
-      <c r="BE62" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF62" t="s">
-        <v>42</v>
-      </c>
-      <c r="BG62">
-        <v>18.3</v>
-      </c>
-      <c r="BH62">
-        <v>-56.7</v>
-      </c>
-      <c r="BI62" s="9">
-        <v>18.3</v>
-      </c>
-      <c r="BJ62" s="9">
-        <v>-76</v>
-      </c>
-      <c r="BK62">
-        <v>18.3</v>
-      </c>
-      <c r="BL62">
-        <v>-99.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:64">
+        <v>-73.8</v>
+      </c>
+      <c r="AH62" s="9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AI62" s="9">
+        <v>-82.8</v>
+      </c>
+      <c r="AJ62">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AK62">
+        <v>-89.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:50">
       <c r="A63">
         <v>60</v>
       </c>
@@ -3946,70 +4485,16 @@
         <v>80</v>
       </c>
       <c r="C63">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63">
-        <v>45</v>
-      </c>
-      <c r="H63">
-        <v>52.4</v>
-      </c>
-      <c r="Y63">
-        <v>49.3</v>
-      </c>
-      <c r="Z63">
-        <v>-56.5</v>
-      </c>
-      <c r="AA63">
-        <v>46.1</v>
-      </c>
-      <c r="AB63">
-        <v>-51.3</v>
-      </c>
-      <c r="AD63">
-        <v>49.3</v>
-      </c>
-      <c r="AE63">
-        <v>-56.5</v>
-      </c>
-      <c r="AF63">
-        <v>46.1</v>
-      </c>
-      <c r="AG63">
-        <v>-51.3</v>
-      </c>
-      <c r="BE63" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF63" t="s">
-        <v>42</v>
-      </c>
-      <c r="BG63">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="BH63">
-        <v>-73.8</v>
-      </c>
-      <c r="BI63" s="9">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="BJ63" s="9">
-        <v>-82.8</v>
-      </c>
-      <c r="BK63">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="BL63">
-        <v>-89.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:64">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:50">
       <c r="A64">
         <v>60</v>
       </c>
@@ -4020,82 +4505,13 @@
         <v>15</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E64" t="s">
         <v>23</v>
       </c>
-      <c r="G64">
-        <v>23.04</v>
-      </c>
-      <c r="H64">
-        <v>45.5</v>
-      </c>
-      <c r="I64">
-        <v>6</v>
-      </c>
-      <c r="K64">
-        <v>21.8</v>
-      </c>
-      <c r="L64">
-        <v>-30.9</v>
-      </c>
-      <c r="M64">
-        <v>21.8</v>
-      </c>
-      <c r="N64">
-        <v>-30.9</v>
-      </c>
-      <c r="O64">
-        <v>21.8</v>
-      </c>
-      <c r="P64">
-        <v>-79.2</v>
-      </c>
-      <c r="Q64">
-        <v>21.8</v>
-      </c>
-      <c r="R64">
-        <v>-53.7</v>
-      </c>
-      <c r="S64">
-        <v>27</v>
-      </c>
-      <c r="T64">
-        <v>-111.3</v>
-      </c>
-      <c r="U64">
-        <v>27</v>
-      </c>
-      <c r="V64">
-        <v>-129.69999999999999</v>
-      </c>
-      <c r="Y64">
-        <v>45.1</v>
-      </c>
-      <c r="Z64">
-        <v>-56.4</v>
-      </c>
-      <c r="AA64">
-        <v>40</v>
-      </c>
-      <c r="AB64">
-        <v>-44.6</v>
-      </c>
-      <c r="AD64">
-        <v>45.2</v>
-      </c>
-      <c r="AE64">
-        <v>-56.9</v>
-      </c>
-      <c r="AF64">
-        <v>40</v>
-      </c>
-      <c r="AG64">
-        <v>-44.6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33">
+    </row>
+    <row r="65" spans="1:28">
       <c r="A65">
         <v>60</v>
       </c>
@@ -4106,82 +4522,13 @@
         <v>15</v>
       </c>
       <c r="D65">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
         <v>23</v>
       </c>
-      <c r="G65">
-        <v>32.32</v>
-      </c>
-      <c r="H65">
-        <v>48.9</v>
-      </c>
-      <c r="I65">
-        <v>6</v>
-      </c>
-      <c r="K65">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="L65">
-        <v>-47.9</v>
-      </c>
-      <c r="M65">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="N65">
-        <v>-47.9</v>
-      </c>
-      <c r="O65">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="P65">
-        <v>-68</v>
-      </c>
-      <c r="Q65">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="R65">
-        <v>-47.9</v>
-      </c>
-      <c r="S65">
-        <v>42.7</v>
-      </c>
-      <c r="T65">
-        <v>-105.8</v>
-      </c>
-      <c r="U65">
-        <v>42.7</v>
-      </c>
-      <c r="V65">
-        <v>-86.9</v>
-      </c>
-      <c r="Y65">
-        <v>48.4</v>
-      </c>
-      <c r="Z65">
-        <v>-60.1</v>
-      </c>
-      <c r="AA65">
-        <v>43</v>
-      </c>
-      <c r="AB65">
-        <v>-47.9</v>
-      </c>
-      <c r="AD65">
-        <v>48.6</v>
-      </c>
-      <c r="AE65">
-        <v>-61.1</v>
-      </c>
-      <c r="AF65">
-        <v>43</v>
-      </c>
-      <c r="AG65">
-        <v>-47.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:33">
+    </row>
+    <row r="66" spans="1:28">
       <c r="A66">
         <v>60</v>
       </c>
@@ -4189,85 +4536,16 @@
         <v>80</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D66">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
         <v>23</v>
       </c>
-      <c r="G66">
-        <v>45</v>
-      </c>
-      <c r="H66">
-        <v>52.4</v>
-      </c>
-      <c r="I66">
-        <v>6</v>
-      </c>
-      <c r="K66">
-        <v>35.6</v>
-      </c>
-      <c r="L66">
-        <v>-72.900000000000006</v>
-      </c>
-      <c r="M66">
-        <v>35.6</v>
-      </c>
-      <c r="N66">
-        <v>-51.3</v>
-      </c>
-      <c r="O66">
-        <v>35.6</v>
-      </c>
-      <c r="P66">
-        <v>-72.900000000000006</v>
-      </c>
-      <c r="Q66">
-        <v>35.6</v>
-      </c>
-      <c r="R66">
-        <v>-51.3</v>
-      </c>
-      <c r="S66">
-        <v>45.7</v>
-      </c>
-      <c r="T66">
-        <v>-113.5</v>
-      </c>
-      <c r="U66">
-        <v>45.7</v>
-      </c>
-      <c r="V66">
-        <v>-93.2</v>
-      </c>
-      <c r="Y66">
-        <v>51.7</v>
-      </c>
-      <c r="Z66">
-        <v>-63.9</v>
-      </c>
-      <c r="AA66">
-        <v>46.1</v>
-      </c>
-      <c r="AB66">
-        <v>-51.3</v>
-      </c>
-      <c r="AD66">
-        <v>52.1</v>
-      </c>
-      <c r="AE66">
-        <v>-65.5</v>
-      </c>
-      <c r="AF66">
-        <v>46.1</v>
-      </c>
-      <c r="AG66">
-        <v>-51.3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:33">
+    </row>
+    <row r="67" spans="1:28">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4278,82 +4556,13 @@
         <v>30</v>
       </c>
       <c r="D67">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
         <v>23</v>
       </c>
-      <c r="G67">
-        <v>38.04</v>
-      </c>
-      <c r="H67">
-        <v>50.6</v>
-      </c>
-      <c r="I67">
-        <v>6</v>
-      </c>
-      <c r="K67">
-        <v>24.3</v>
-      </c>
-      <c r="L67">
-        <v>-34.4</v>
-      </c>
-      <c r="M67">
-        <v>24.3</v>
-      </c>
-      <c r="N67">
-        <v>-34.4</v>
-      </c>
-      <c r="O67">
-        <v>24.3</v>
-      </c>
-      <c r="P67">
-        <v>-88</v>
-      </c>
-      <c r="Q67">
-        <v>24.3</v>
-      </c>
-      <c r="R67">
-        <v>-59.7</v>
-      </c>
-      <c r="S67">
-        <v>30</v>
-      </c>
-      <c r="T67">
-        <v>-123.7</v>
-      </c>
-      <c r="U67">
-        <v>30</v>
-      </c>
-      <c r="V67">
-        <v>-144.19999999999999</v>
-      </c>
-      <c r="Y67">
-        <v>48.8</v>
-      </c>
-      <c r="Z67">
-        <v>-57</v>
-      </c>
-      <c r="AA67">
-        <v>44.5</v>
-      </c>
-      <c r="AB67">
-        <v>-49.5</v>
-      </c>
-      <c r="AD67">
-        <v>48.8</v>
-      </c>
-      <c r="AE67">
-        <v>-57.3</v>
-      </c>
-      <c r="AF67">
-        <v>44.5</v>
-      </c>
-      <c r="AG67">
-        <v>-49.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:33">
+    </row>
+    <row r="68" spans="1:28">
       <c r="A68">
         <v>60</v>
       </c>
@@ -4364,82 +4573,13 @@
         <v>30</v>
       </c>
       <c r="D68">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E68" t="s">
         <v>23</v>
       </c>
-      <c r="G68">
-        <v>47.32</v>
-      </c>
-      <c r="H68">
-        <v>52.9</v>
-      </c>
-      <c r="I68">
-        <v>6</v>
-      </c>
-      <c r="K68">
-        <v>36</v>
-      </c>
-      <c r="L68">
-        <v>-51.9</v>
-      </c>
-      <c r="M68">
-        <v>36</v>
-      </c>
-      <c r="N68">
-        <v>-51.9</v>
-      </c>
-      <c r="O68">
-        <v>36</v>
-      </c>
-      <c r="P68">
-        <v>-73.7</v>
-      </c>
-      <c r="Q68">
-        <v>36</v>
-      </c>
-      <c r="R68">
-        <v>-51.9</v>
-      </c>
-      <c r="S68">
-        <v>46.2</v>
-      </c>
-      <c r="T68">
-        <v>-114.7</v>
-      </c>
-      <c r="U68">
-        <v>46.2</v>
-      </c>
-      <c r="V68">
-        <v>-94.2</v>
-      </c>
-      <c r="Y68">
-        <v>51</v>
-      </c>
-      <c r="Z68">
-        <v>-59.4</v>
-      </c>
-      <c r="AA68">
-        <v>46.6</v>
-      </c>
-      <c r="AB68">
-        <v>-51.9</v>
-      </c>
-      <c r="AD68">
-        <v>51.1</v>
-      </c>
-      <c r="AE68">
-        <v>-60</v>
-      </c>
-      <c r="AF68">
-        <v>46.6</v>
-      </c>
-      <c r="AG68">
-        <v>-51.9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:33">
+    </row>
+    <row r="69" spans="1:28">
       <c r="A69">
         <v>60</v>
       </c>
@@ -4447,85 +4587,16 @@
         <v>80</v>
       </c>
       <c r="C69">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D69">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
         <v>23</v>
       </c>
-      <c r="G69">
-        <v>60</v>
-      </c>
-      <c r="H69">
-        <v>55.6</v>
-      </c>
-      <c r="I69">
-        <v>6</v>
-      </c>
-      <c r="K69">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="L69">
-        <v>-54.5</v>
-      </c>
-      <c r="M69">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="N69">
-        <v>-54.5</v>
-      </c>
-      <c r="O69">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="P69">
-        <v>-77.400000000000006</v>
-      </c>
-      <c r="Q69">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="R69">
-        <v>-54.5</v>
-      </c>
-      <c r="S69">
-        <v>48.6</v>
-      </c>
-      <c r="T69">
-        <v>-120.6</v>
-      </c>
-      <c r="U69">
-        <v>48.6</v>
-      </c>
-      <c r="V69">
-        <v>-99</v>
-      </c>
-      <c r="Y69">
-        <v>53.5</v>
-      </c>
-      <c r="Z69">
-        <v>-61.9</v>
-      </c>
-      <c r="AA69">
-        <v>49</v>
-      </c>
-      <c r="AB69">
-        <v>-54.5</v>
-      </c>
-      <c r="AD69">
-        <v>53.8</v>
-      </c>
-      <c r="AE69">
-        <v>-63.1</v>
-      </c>
-      <c r="AF69">
-        <v>49</v>
-      </c>
-      <c r="AG69">
-        <v>-54.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:33">
+    </row>
+    <row r="70" spans="1:28">
       <c r="A70">
         <v>60</v>
       </c>
@@ -4536,82 +4607,14 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
         <v>23</v>
       </c>
-      <c r="G70">
-        <v>53.04</v>
-      </c>
-      <c r="H70">
-        <v>54.2</v>
-      </c>
-      <c r="I70">
-        <v>6</v>
-      </c>
-      <c r="K70">
-        <v>26</v>
-      </c>
-      <c r="L70">
-        <v>-36.9</v>
-      </c>
-      <c r="M70">
-        <v>26</v>
-      </c>
-      <c r="N70">
-        <v>-36.9</v>
-      </c>
-      <c r="O70">
-        <v>26</v>
-      </c>
-      <c r="P70">
-        <v>-94.3</v>
-      </c>
-      <c r="Q70">
-        <v>26</v>
-      </c>
-      <c r="R70">
-        <v>-64</v>
-      </c>
-      <c r="S70">
-        <v>32.1</v>
-      </c>
-      <c r="T70">
-        <v>-132.6</v>
-      </c>
-      <c r="U70">
-        <v>32.1</v>
-      </c>
-      <c r="V70">
-        <v>-154.6</v>
-      </c>
-      <c r="Y70">
-        <v>51</v>
-      </c>
-      <c r="Z70">
-        <v>-58.4</v>
-      </c>
-      <c r="AA70">
-        <v>47.7</v>
-      </c>
-      <c r="AB70">
-        <v>-53.1</v>
-      </c>
-      <c r="AD70">
-        <v>51</v>
-      </c>
-      <c r="AE70">
-        <v>-58.5</v>
-      </c>
-      <c r="AF70">
-        <v>47.7</v>
-      </c>
-      <c r="AG70">
-        <v>-53.1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:33">
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" spans="1:28">
       <c r="A71">
         <v>60</v>
       </c>
@@ -4619,22 +4622,16 @@
         <v>80</v>
       </c>
       <c r="C71">
+        <v>40</v>
+      </c>
+      <c r="D71">
         <v>45</v>
-      </c>
-      <c r="D71">
-        <v>30</v>
       </c>
       <c r="E71" t="s">
         <v>23</v>
       </c>
-      <c r="G71">
-        <v>62.32</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="72" spans="1:33">
+    </row>
+    <row r="72" spans="1:28">
       <c r="A72">
         <v>60</v>
       </c>
@@ -4642,85 +4639,73 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D72">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G72">
-        <v>57.32</v>
+        <v>19.02</v>
       </c>
       <c r="H72">
-        <v>55.1</v>
+        <v>43.7</v>
       </c>
       <c r="I72">
         <v>6</v>
       </c>
       <c r="K72">
-        <v>37.5</v>
+        <v>21</v>
       </c>
       <c r="L72">
-        <v>-54</v>
+        <v>-51.6</v>
       </c>
       <c r="M72">
-        <v>37.5</v>
+        <v>21</v>
       </c>
       <c r="N72">
-        <v>-54</v>
+        <v>-55.9</v>
       </c>
       <c r="O72">
-        <v>37.5</v>
+        <v>21</v>
       </c>
       <c r="P72">
-        <v>-76.7</v>
+        <v>-64.7</v>
       </c>
       <c r="Q72">
-        <v>37.5</v>
+        <v>29.7</v>
       </c>
       <c r="R72">
-        <v>-54</v>
-      </c>
-      <c r="S72">
-        <v>48.1</v>
+        <v>-73.7</v>
       </c>
       <c r="T72">
-        <v>-119.4</v>
+        <v>43.4</v>
       </c>
       <c r="U72">
-        <v>48.1</v>
+        <v>-54.6</v>
       </c>
       <c r="V72">
-        <v>-98.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="W72">
+        <v>-42.8</v>
       </c>
       <c r="Y72">
-        <v>52.2</v>
+        <v>43.4</v>
       </c>
       <c r="Z72">
-        <v>-60</v>
+        <v>-54.6</v>
       </c>
       <c r="AA72">
-        <v>48.5</v>
+        <v>38.4</v>
       </c>
       <c r="AB72">
-        <v>-54</v>
-      </c>
-      <c r="AD72">
-        <v>52.3</v>
-      </c>
-      <c r="AE72">
-        <v>-60.2</v>
-      </c>
-      <c r="AF72">
-        <v>48.5</v>
-      </c>
-      <c r="AG72">
-        <v>-54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:33">
+        <v>-42.8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28">
       <c r="A73">
         <v>60</v>
       </c>
@@ -4731,13 +4716,70 @@
         <v>15</v>
       </c>
       <c r="D73">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E73" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="74" spans="1:33">
+      <c r="G73">
+        <v>23.66</v>
+      </c>
+      <c r="H73">
+        <v>45.7</v>
+      </c>
+      <c r="I73">
+        <v>6</v>
+      </c>
+      <c r="K73">
+        <v>22</v>
+      </c>
+      <c r="L73">
+        <v>-31.1</v>
+      </c>
+      <c r="M73">
+        <v>22</v>
+      </c>
+      <c r="N73">
+        <v>-44.8</v>
+      </c>
+      <c r="O73">
+        <v>22</v>
+      </c>
+      <c r="P73">
+        <v>-54</v>
+      </c>
+      <c r="Q73">
+        <v>29.7</v>
+      </c>
+      <c r="R73">
+        <v>-59.3</v>
+      </c>
+      <c r="T73">
+        <v>45.5</v>
+      </c>
+      <c r="U73">
+        <v>-57.2</v>
+      </c>
+      <c r="V73">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="W73">
+        <v>-44.8</v>
+      </c>
+      <c r="Y73">
+        <v>45.5</v>
+      </c>
+      <c r="Z73">
+        <v>-57.2</v>
+      </c>
+      <c r="AA73">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="AB73">
+        <v>-44.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28">
       <c r="A74">
         <v>60</v>
       </c>
@@ -4748,13 +4790,70 @@
         <v>15</v>
       </c>
       <c r="D74">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="75" spans="1:33">
+      <c r="G74">
+        <v>30</v>
+      </c>
+      <c r="H74">
+        <v>48.1</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="K74">
+        <v>23.1</v>
+      </c>
+      <c r="L74">
+        <v>-42.4</v>
+      </c>
+      <c r="M74">
+        <v>23.1</v>
+      </c>
+      <c r="N74">
+        <v>-47.1</v>
+      </c>
+      <c r="O74">
+        <v>23.1</v>
+      </c>
+      <c r="P74">
+        <v>-56.7</v>
+      </c>
+      <c r="Q74">
+        <v>31.3</v>
+      </c>
+      <c r="R74">
+        <v>-71.400000000000006</v>
+      </c>
+      <c r="T74">
+        <v>47.8</v>
+      </c>
+      <c r="U74">
+        <v>-60.1</v>
+      </c>
+      <c r="V74">
+        <v>42.3</v>
+      </c>
+      <c r="W74">
+        <v>-47.1</v>
+      </c>
+      <c r="Y74">
+        <v>47.8</v>
+      </c>
+      <c r="Z74">
+        <v>-60.1</v>
+      </c>
+      <c r="AA74">
+        <v>42.3</v>
+      </c>
+      <c r="AB74">
+        <v>-47.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28">
       <c r="A75">
         <v>60</v>
       </c>
@@ -4762,16 +4861,73 @@
         <v>80</v>
       </c>
       <c r="C75">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D75">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="76" spans="1:33">
+      <c r="G75">
+        <v>34.020000000000003</v>
+      </c>
+      <c r="H75">
+        <v>49.4</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
+      <c r="K75">
+        <v>23.7</v>
+      </c>
+      <c r="L75">
+        <v>-58.3</v>
+      </c>
+      <c r="M75">
+        <v>23.7</v>
+      </c>
+      <c r="N75">
+        <v>-66.5</v>
+      </c>
+      <c r="O75">
+        <v>23.7</v>
+      </c>
+      <c r="P75">
+        <v>-73.099999999999994</v>
+      </c>
+      <c r="Q75">
+        <v>33.5</v>
+      </c>
+      <c r="R75">
+        <v>-90.3</v>
+      </c>
+      <c r="T75">
+        <v>47.7</v>
+      </c>
+      <c r="U75">
+        <v>-56</v>
+      </c>
+      <c r="V75">
+        <v>43.5</v>
+      </c>
+      <c r="W75">
+        <v>-48.4</v>
+      </c>
+      <c r="Y75">
+        <v>47.7</v>
+      </c>
+      <c r="Z75">
+        <v>-56</v>
+      </c>
+      <c r="AA75">
+        <v>43.5</v>
+      </c>
+      <c r="AB75">
+        <v>-48.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28">
       <c r="A76">
         <v>60</v>
       </c>
@@ -4782,13 +4938,70 @@
         <v>30</v>
       </c>
       <c r="D76">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E76" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="77" spans="1:33">
+      <c r="G76">
+        <v>38.659999999999997</v>
+      </c>
+      <c r="H76">
+        <v>50.7</v>
+      </c>
+      <c r="I76">
+        <v>6</v>
+      </c>
+      <c r="K76">
+        <v>24.3</v>
+      </c>
+      <c r="L76">
+        <v>-34.5</v>
+      </c>
+      <c r="M76">
+        <v>24.3</v>
+      </c>
+      <c r="N76">
+        <v>-49.7</v>
+      </c>
+      <c r="O76">
+        <v>24.3</v>
+      </c>
+      <c r="P76">
+        <v>-59.9</v>
+      </c>
+      <c r="Q76">
+        <v>33</v>
+      </c>
+      <c r="R76">
+        <v>-65.7</v>
+      </c>
+      <c r="T76">
+        <v>49</v>
+      </c>
+      <c r="U76">
+        <v>-57.5</v>
+      </c>
+      <c r="V76">
+        <v>44.6</v>
+      </c>
+      <c r="W76">
+        <v>-49.7</v>
+      </c>
+      <c r="Y76">
+        <v>49</v>
+      </c>
+      <c r="Z76">
+        <v>-57.5</v>
+      </c>
+      <c r="AA76">
+        <v>44.6</v>
+      </c>
+      <c r="AB76">
+        <v>-49.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28">
       <c r="A77">
         <v>60</v>
       </c>
@@ -4799,13 +5012,70 @@
         <v>30</v>
       </c>
       <c r="D77">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:33">
+      <c r="G77">
+        <v>45</v>
+      </c>
+      <c r="H77">
+        <v>52.4</v>
+      </c>
+      <c r="I77">
+        <v>6</v>
+      </c>
+      <c r="K77">
+        <v>25.1</v>
+      </c>
+      <c r="L77">
+        <v>-46.2</v>
+      </c>
+      <c r="M77">
+        <v>25.1</v>
+      </c>
+      <c r="N77">
+        <v>-51.3</v>
+      </c>
+      <c r="O77">
+        <v>25.1</v>
+      </c>
+      <c r="P77">
+        <v>-61.8</v>
+      </c>
+      <c r="Q77">
+        <v>34</v>
+      </c>
+      <c r="R77">
+        <v>-77.8</v>
+      </c>
+      <c r="T77">
+        <v>50.6</v>
+      </c>
+      <c r="U77">
+        <v>-59.4</v>
+      </c>
+      <c r="V77">
+        <v>46.1</v>
+      </c>
+      <c r="W77">
+        <v>-51.3</v>
+      </c>
+      <c r="Y77">
+        <v>50.6</v>
+      </c>
+      <c r="Z77">
+        <v>-59.4</v>
+      </c>
+      <c r="AA77">
+        <v>46.1</v>
+      </c>
+      <c r="AB77">
+        <v>-51.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28">
       <c r="A78">
         <v>60</v>
       </c>
@@ -4813,16 +5083,73 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D78">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:33">
+      <c r="G78">
+        <v>49.02</v>
+      </c>
+      <c r="H78">
+        <v>53.3</v>
+      </c>
+      <c r="I78">
+        <v>6</v>
+      </c>
+      <c r="K78">
+        <v>25.6</v>
+      </c>
+      <c r="L78">
+        <v>-62.9</v>
+      </c>
+      <c r="M78">
+        <v>25.6</v>
+      </c>
+      <c r="N78">
+        <v>-84.3</v>
+      </c>
+      <c r="O78">
+        <v>2.6</v>
+      </c>
+      <c r="P78">
+        <v>-78.900000000000006</v>
+      </c>
+      <c r="Q78">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="R78">
+        <v>-123.5</v>
+      </c>
+      <c r="T78">
+        <v>50.2</v>
+      </c>
+      <c r="U78">
+        <v>-57.6</v>
+      </c>
+      <c r="V78">
+        <v>46.9</v>
+      </c>
+      <c r="W78">
+        <v>-52.3</v>
+      </c>
+      <c r="Y78">
+        <v>50.2</v>
+      </c>
+      <c r="Z78">
+        <v>-57.6</v>
+      </c>
+      <c r="AA78">
+        <v>46.9</v>
+      </c>
+      <c r="AB78">
+        <v>-52.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28">
       <c r="A79">
         <v>60</v>
       </c>
@@ -4833,13 +5160,70 @@
         <v>45</v>
       </c>
       <c r="D79">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E79" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="1:33">
+      <c r="G79">
+        <v>53.66</v>
+      </c>
+      <c r="H79">
+        <v>54.4</v>
+      </c>
+      <c r="I79">
+        <v>6</v>
+      </c>
+      <c r="K79">
+        <v>26.1</v>
+      </c>
+      <c r="L79">
+        <v>-37</v>
+      </c>
+      <c r="M79">
+        <v>26.1</v>
+      </c>
+      <c r="N79">
+        <v>-53.3</v>
+      </c>
+      <c r="O79">
+        <v>26.1</v>
+      </c>
+      <c r="P79">
+        <v>-64.099999999999994</v>
+      </c>
+      <c r="Q79">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="R79">
+        <v>-70.400000000000006</v>
+      </c>
+      <c r="T79">
+        <v>51.2</v>
+      </c>
+      <c r="U79">
+        <v>-58.7</v>
+      </c>
+      <c r="V79">
+        <v>47.8</v>
+      </c>
+      <c r="W79">
+        <v>-53.3</v>
+      </c>
+      <c r="Y79">
+        <v>51.2</v>
+      </c>
+      <c r="Z79">
+        <v>-58.7</v>
+      </c>
+      <c r="AA79">
+        <v>47.8</v>
+      </c>
+      <c r="AB79">
+        <v>-53.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28">
       <c r="A80">
         <v>60</v>
       </c>
@@ -4850,27 +5234,67 @@
         <v>45</v>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E80" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81">
-        <v>60</v>
-      </c>
-      <c r="B81">
-        <v>80</v>
-      </c>
-      <c r="C81">
-        <v>45</v>
-      </c>
-      <c r="D81">
-        <v>45</v>
-      </c>
-      <c r="E81" t="s">
-        <v>24</v>
+      <c r="G80">
+        <v>60</v>
+      </c>
+      <c r="H80">
+        <v>55.6</v>
+      </c>
+      <c r="I80">
+        <v>6</v>
+      </c>
+      <c r="K80">
+        <v>26.7</v>
+      </c>
+      <c r="L80">
+        <v>-49.1</v>
+      </c>
+      <c r="M80">
+        <v>26.7</v>
+      </c>
+      <c r="N80">
+        <v>-54.5</v>
+      </c>
+      <c r="O80">
+        <v>26.7</v>
+      </c>
+      <c r="P80">
+        <v>-65.7</v>
+      </c>
+      <c r="Q80">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="R80">
+        <v>-82.6</v>
+      </c>
+      <c r="T80">
+        <v>52.4</v>
+      </c>
+      <c r="U80">
+        <v>-60.1</v>
+      </c>
+      <c r="V80">
+        <v>49</v>
+      </c>
+      <c r="W80">
+        <v>-54.5</v>
+      </c>
+      <c r="Y80">
+        <v>52.4</v>
+      </c>
+      <c r="Z80">
+        <v>-60.1</v>
+      </c>
+      <c r="AA80">
+        <v>49</v>
+      </c>
+      <c r="AB80">
+        <v>-54.5</v>
       </c>
     </row>
   </sheetData>
@@ -7339,7 +7763,7 @@
         <v>77</v>
       </c>
       <c r="O3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15">
@@ -7357,14 +7781,14 @@
       </c>
       <c r="F4">
         <f>MIN(H4,H5)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
       </c>
       <c r="H4">
         <f>0.4*B7</f>
-        <v>0</v>
+        <v>7.071227789631239</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -7406,7 +7830,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1">
@@ -7458,8 +7882,8 @@
         <v>58</v>
       </c>
       <c r="B7" s="7">
-        <f>D7</f>
-        <v>0</v>
+        <f>0.5*($B$6 + $B$6+TAN($B$8 * 6.28 / 360)*$B$4/2)</f>
+        <v>17.678069474078097</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
@@ -7495,7 +7919,7 @@
       </c>
       <c r="F8" s="4">
         <f>MAX(F6,F4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
         <v>1</v>
@@ -7579,7 +8003,7 @@
       </c>
       <c r="C13">
         <f>F8*F8</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0.48</v>
@@ -7621,21 +8045,21 @@
       </c>
       <c r="C14">
         <f>F8*F8</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="F14">
-        <v>-3.35</v>
+        <v>-3.27</v>
       </c>
       <c r="G14">
         <f t="shared" ref="G14:G18" si="0">$L$6*E14</f>
-        <v>21.542400000000001</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="H14">
         <f t="shared" ref="H14:H18" si="1">$L$6*F14</f>
-        <v>-144.33408</v>
+        <v>-140.88729599999999</v>
       </c>
       <c r="I14">
         <f t="shared" ref="I14:I18" si="2">$L$6*$L$2</f>
@@ -7647,11 +8071,11 @@
       </c>
       <c r="L14">
         <f t="shared" ref="L14:L18" si="4">G14+I14</f>
-        <v>29.297664000000001</v>
+        <v>28.435967999999999</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:M18" si="5">H14+J14</f>
-        <v>-152.08934400000001</v>
+        <v>-148.64256</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -7663,7 +8087,7 @@
       </c>
       <c r="C15">
         <f>(B4/2-2*F8)*F8</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>0.38</v>
@@ -7705,7 +8129,7 @@
       </c>
       <c r="C16">
         <f>(B5-2*F8)*F8</f>
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="E16">
         <v>0.3</v>
@@ -7747,13 +8171,13 @@
       </c>
       <c r="C17">
         <f>(B5-2*$F$8)*$F$8</f>
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>0.3</v>
       </c>
       <c r="F17">
-        <v>-1.1000000000000001</v>
+        <v>-1.08</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
@@ -7761,7 +8185,7 @@
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>-47.393280000000004</v>
+        <v>-46.531584000000002</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
@@ -7777,7 +8201,7 @@
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>-55.148544000000001</v>
+        <v>-54.286848000000006</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -7789,7 +8213,7 @@
       </c>
       <c r="C18">
         <f>($B$5*$B$4/2)-2*C13-2*C14-2*C15-C16-C17</f>
-        <v>756</v>
+        <v>624</v>
       </c>
       <c r="E18">
         <v>0.3</v>
@@ -7849,7 +8273,7 @@
       </c>
       <c r="C22">
         <f>F8*B6</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>0.83</v>
@@ -7891,17 +8315,17 @@
       </c>
       <c r="C23">
         <f>($B$5-2*$F$8)*($B$6)</f>
-        <v>810</v>
+        <v>780</v>
       </c>
       <c r="E23">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="F23">
         <v>-0.8</v>
       </c>
       <c r="G23">
         <f>$L$6*E23</f>
-        <v>30.590208000000001</v>
+        <v>30.15936</v>
       </c>
       <c r="H23">
         <f>$L$6*F23</f>
@@ -7917,7 +8341,7 @@
       </c>
       <c r="L23">
         <f>G23+I23</f>
-        <v>38.345472000000001</v>
+        <v>37.914624000000003</v>
       </c>
       <c r="M23">
         <f>H23+J23</f>
@@ -7938,7 +8362,7 @@
       </c>
       <c r="C26">
         <f>0.5*($B$6+$B$6+$F$8*TAN(RADIANS($B$8)))*$F$8</f>
-        <v>46.205771365940052</v>
+        <v>62.143593539448979</v>
       </c>
       <c r="E26">
         <v>0.83</v>
@@ -7977,7 +8401,7 @@
       </c>
       <c r="C27">
         <f>($B$6*$B$4)+0.5*$B$4/2*TAN(RADIANS(B8))*$B$4  - 2*C26</f>
-        <v>614.768134240569</v>
+        <v>582.8924898935511</v>
       </c>
       <c r="E27">
         <v>0.7</v>
@@ -8017,7 +8441,7 @@
       </c>
       <c r="C30">
         <f>B30*F8</f>
-        <v>0.80342084222342947</v>
+        <v>1.0712277896312392</v>
       </c>
     </row>
   </sheetData>
@@ -8037,7 +8461,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -8067,7 +8491,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="5">
         <v>40</v>
@@ -8087,7 +8511,7 @@
       </c>
       <c r="H4">
         <f>0.4*B7</f>
-        <v>8.1424555792624798</v>
+        <v>7.071227789631239</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
@@ -8096,18 +8520,18 @@
         <v>77</v>
       </c>
       <c r="L4" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N4">
-        <v>0.85</v>
+        <v>0.88</v>
+      </c>
+      <c r="N4" t="s">
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" s="5">
         <v>60</v>
@@ -8126,10 +8550,10 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="O5" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1">
@@ -8164,16 +8588,16 @@
       </c>
       <c r="L6" s="4">
         <f>0.00256*B9*B9*L4*L3</f>
-        <v>44.553600000000003</v>
+        <v>43.084800000000001</v>
       </c>
       <c r="M6" t="s">
         <v>41</v>
       </c>
       <c r="N6">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1">
@@ -8181,8 +8605,8 @@
         <v>58</v>
       </c>
       <c r="B7" s="12">
-        <f>$B$6+TAN($B$8 * 6.28 / 360)*$B$4/2</f>
-        <v>20.356138948156197</v>
+        <f>0.5*($B$6 + $B$6+TAN($B$8 * 6.28 / 360)*$B$4/2)</f>
+        <v>17.678069474078097</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>1</v>
@@ -8195,6 +8619,12 @@
       </c>
       <c r="I7" t="s">
         <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.91</v>
+      </c>
+      <c r="O7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1">
@@ -8217,6 +8647,12 @@
       <c r="G8" t="s">
         <v>1</v>
       </c>
+      <c r="N8">
+        <v>0.96</v>
+      </c>
+      <c r="O8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
@@ -8229,11 +8665,11 @@
         <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F9">
         <f>B7/B4</f>
-        <v>0.50890347370390487</v>
+        <v>0.44195173685195244</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -8264,7 +8700,7 @@
     </row>
     <row r="12" spans="1:15" ht="15">
       <c r="A12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
         <v>66</v>
@@ -8313,32 +8749,32 @@
       </c>
       <c r="G13">
         <f>$L$6*E13</f>
-        <v>28.959840000000003</v>
+        <v>28.005120000000002</v>
       </c>
       <c r="H13">
         <f>$L$6*F13</f>
-        <v>-75.741120000000009</v>
+        <v>-73.244159999999994</v>
       </c>
       <c r="I13">
         <f>$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J13">
         <f>-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L13">
         <f>G13+I13</f>
-        <v>36.979488000000003</v>
+        <v>35.760384000000002</v>
       </c>
       <c r="M13">
         <f>H13+J13</f>
-        <v>-83.760768000000013</v>
+        <v>-80.999423999999991</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s">
         <v>103</v>
@@ -8355,35 +8791,35 @@
       </c>
       <c r="G14">
         <f t="shared" ref="G14:H33" si="0">$L$6*E14</f>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>-49.008960000000009</v>
+        <v>-47.393280000000004</v>
       </c>
       <c r="I14">
         <f t="shared" ref="I14:I33" si="1">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J14">
         <f t="shared" ref="J14:J33" si="2">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L14">
         <f t="shared" ref="L14:M33" si="3">G14+I14</f>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M14">
         <f t="shared" si="3"/>
-        <v>-57.028608000000006</v>
+        <v>-55.148544000000001</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15">
         <f>C27-C13-C14-C16</f>
@@ -8397,35 +8833,35 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H15">
         <f t="shared" si="0"/>
-        <v>-57.919680000000007</v>
+        <v>-56.010240000000003</v>
       </c>
       <c r="I15">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M15">
         <f t="shared" si="3"/>
-        <v>-65.939328000000003</v>
+        <v>-63.765504000000007</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" s="14">
         <f>0.5*((B5-2*C29-2*F8)+(B5-2*F8-2*C29-2*C30))*C30</f>
@@ -8439,32 +8875,32 @@
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H16">
         <f t="shared" si="0"/>
-        <v>-44.553600000000003</v>
+        <v>-43.084800000000001</v>
       </c>
       <c r="I16">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J16">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M16">
         <f t="shared" si="3"/>
-        <v>-52.573248000000007</v>
+        <v>-50.840063999999998</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="B17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17">
         <f>2*SUM(C13:C16)</f>
@@ -8473,7 +8909,7 @@
     </row>
     <row r="19" spans="1:13" ht="15">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -8488,42 +8924,42 @@
         <v>16</v>
       </c>
       <c r="E20">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="F20">
         <v>-1.7</v>
       </c>
       <c r="G20">
         <f t="shared" ref="G17:G20" si="4">$L$6*E20</f>
-        <v>28.959840000000003</v>
+        <v>27.143424</v>
       </c>
       <c r="H20">
         <f t="shared" ref="H17:H20" si="5">$L$6*F20</f>
-        <v>-75.741120000000009</v>
+        <v>-73.244159999999994</v>
       </c>
       <c r="I20">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J20">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L20">
         <f t="shared" ref="L17:L20" si="6">G20+I20</f>
-        <v>36.979488000000003</v>
+        <v>34.898688</v>
       </c>
       <c r="M20">
         <f t="shared" ref="M17:M20" si="7">H20+J20</f>
-        <v>-83.760768000000013</v>
+        <v>-80.999423999999991</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21">
         <f>(B4-2*$F$8)*$F$8</f>
@@ -8533,39 +8969,39 @@
         <v>0.3</v>
       </c>
       <c r="F21">
-        <v>-1.23</v>
+        <v>-1.22</v>
       </c>
       <c r="G21">
         <f t="shared" ref="G21:G23" si="8">$L$6*E21</f>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H21">
         <f t="shared" ref="H21:H23" si="9">$L$6*F21</f>
-        <v>-54.800928000000006</v>
+        <v>-52.563456000000002</v>
       </c>
       <c r="I21">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J21">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L21">
         <f t="shared" ref="L21:L23" si="10">G21+I21</f>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M21">
         <f t="shared" ref="M21:M23" si="11">H21+J21</f>
-        <v>-62.820576000000003</v>
+        <v>-60.318719999999999</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C22">
         <f>C28-C20-C21-C23</f>
@@ -8575,39 +9011,39 @@
         <v>0.3</v>
       </c>
       <c r="F22">
-        <v>-1.4</v>
+        <v>-1.43</v>
       </c>
       <c r="G22">
         <f t="shared" si="8"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H22">
         <f t="shared" si="9"/>
-        <v>-62.375039999999998</v>
+        <v>-61.611263999999998</v>
       </c>
       <c r="I22">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J22">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L22">
         <f t="shared" si="10"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M22">
         <f t="shared" si="11"/>
-        <v>-70.394688000000002</v>
+        <v>-69.366528000000002</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="14">
         <f>0.5*(B4-2*F8-2*C29)*C31</f>
@@ -8621,32 +9057,32 @@
       </c>
       <c r="G23">
         <f t="shared" si="8"/>
-        <v>13.36608</v>
+        <v>12.92544</v>
       </c>
       <c r="H23">
         <f t="shared" si="9"/>
-        <v>-44.553600000000003</v>
+        <v>-43.084800000000001</v>
       </c>
       <c r="I23">
         <f t="shared" si="1"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J23">
         <f t="shared" si="2"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L23">
         <f t="shared" si="10"/>
-        <v>21.385728</v>
+        <v>20.680703999999999</v>
       </c>
       <c r="M23">
         <f t="shared" si="11"/>
-        <v>-52.573248000000007</v>
+        <v>-50.840063999999998</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="B24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24">
         <f>2*SUM(C20:C23)</f>
@@ -8655,7 +9091,7 @@
     </row>
     <row r="25" spans="1:13" ht="15">
       <c r="B25" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" s="1">
         <f>C17+C24</f>
@@ -8668,10 +9104,10 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C27">
         <f>0.5*(2*B5-B4)*0.5*B4</f>
@@ -8680,10 +9116,10 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
         <v>138</v>
-      </c>
-      <c r="B28" t="s">
-        <v>139</v>
       </c>
       <c r="C28">
         <f>0.5*B4*0.5*B4</f>
@@ -8692,10 +9128,10 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" t="s">
         <v>124</v>
-      </c>
-      <c r="B29" t="s">
-        <v>125</v>
       </c>
       <c r="C29">
         <f>1.414*F8</f>
@@ -8704,10 +9140,10 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" t="s">
         <v>126</v>
-      </c>
-      <c r="B30" t="s">
-        <v>127</v>
       </c>
       <c r="C30">
         <f>B4/2-2*F8</f>
@@ -8716,10 +9152,10 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C31">
         <f>0.5*B4-C29-F8</f>
@@ -8753,27 +9189,27 @@
       </c>
       <c r="G37">
         <f>$L$6*E37</f>
-        <v>36.979488000000003</v>
+        <v>35.760384000000002</v>
       </c>
       <c r="H37">
         <f>$L$6*F37</f>
-        <v>-50.345568</v>
+        <v>-48.685823999999997</v>
       </c>
       <c r="I37">
         <f t="shared" ref="I37:I39" si="12">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J37">
         <f t="shared" ref="J37:J39" si="13">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L37">
         <f>G37+I37</f>
-        <v>44.999136000000007</v>
+        <v>43.515647999999999</v>
       </c>
       <c r="M37">
         <f>H37+J37</f>
-        <v>-58.365216000000004</v>
+        <v>-56.441087999999993</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -8795,27 +9231,27 @@
       </c>
       <c r="G38">
         <f>$L$6*E38</f>
-        <v>31.633056</v>
+        <v>30.590208000000001</v>
       </c>
       <c r="H38">
         <f>$L$6*F38</f>
-        <v>-35.642880000000005</v>
+        <v>-34.467840000000002</v>
       </c>
       <c r="I38">
         <f t="shared" si="12"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J38">
         <f t="shared" si="13"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L38">
         <f>G38+I38</f>
-        <v>39.652704</v>
+        <v>38.345472000000001</v>
       </c>
       <c r="M38">
         <f>H38+J38</f>
-        <v>-43.662528000000009</v>
+        <v>-42.223104000000006</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15">
@@ -8842,27 +9278,27 @@
       </c>
       <c r="G41">
         <f>$L$6*E41</f>
-        <v>36.979488000000003</v>
+        <v>35.760384000000002</v>
       </c>
       <c r="H41">
         <f>$L$6*F41</f>
-        <v>-50.345568</v>
+        <v>-48.685823999999997</v>
       </c>
       <c r="I41">
         <f t="shared" ref="I41:I43" si="14">$L$6*$L$2</f>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J41">
         <f t="shared" ref="J41:J43" si="15">-$L$6*$L$2</f>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L41">
         <f>G41+I41</f>
-        <v>44.999136000000007</v>
+        <v>43.515647999999999</v>
       </c>
       <c r="M41">
         <f>H41+J41</f>
-        <v>-58.365216000000004</v>
+        <v>-56.441087999999993</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -8884,27 +9320,27 @@
       </c>
       <c r="G42">
         <f>$L$6*E42</f>
-        <v>31.187519999999999</v>
+        <v>30.15936</v>
       </c>
       <c r="H42">
         <f>$L$6*F42</f>
-        <v>-35.642880000000005</v>
+        <v>-34.467840000000002</v>
       </c>
       <c r="I42">
         <f t="shared" si="14"/>
-        <v>8.0196480000000001</v>
+        <v>7.7552640000000004</v>
       </c>
       <c r="J42">
         <f t="shared" si="15"/>
-        <v>-8.0196480000000001</v>
+        <v>-7.7552640000000004</v>
       </c>
       <c r="L42">
         <f>G42+I42</f>
-        <v>39.207167999999996</v>
+        <v>37.914624000000003</v>
       </c>
       <c r="M42">
         <f>H42+J42</f>
-        <v>-43.662528000000009</v>
+        <v>-42.223104000000006</v>
       </c>
     </row>
     <row r="45" spans="1:13">
